--- a/data/demo.xlsx
+++ b/data/demo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>差异</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>difflib</t>
         </is>
       </c>
     </row>
@@ -524,6 +529,39 @@
 总的来说，修复代码样例主要是为了去掉不需要的日志打印，清理代码，同时引入了一个常量但未使用。代码的功能上达到了避免打印日志的目的。</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // Test.ets
+- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Index {
+-     build() {
+? --
++   build() {
+-             Column() {
+? ------
++       Column() {
+-                 Scroll()
+? --------
++         Scroll()
+-                     .onScroll(() =&gt; {
+? ----------
++           .onScroll(() =&gt; {
++             const TAG = 'onScroll';
+-                         hilog.info(1001, 'Index', 'onScroll') // Avoid printing logs
+-                 })
+-             }
+? --
++           })
+?            +
+-     }
++       }
+? ++
++   }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -584,6 +622,24 @@
 2. **添加常量定义**：
    - 修复代码中引入了一行 `const TAG = 'onTouch';`，用于定义一个常量 `TAG`，虽然此处的常量没有被进一步使用。
 综合来看，修复代码的主要改动是去掉了原本的日志打印功能，以避免在触摸按钮时打印日志。在此过程中，引入了常量 `TAG`，但其具体用途在代码中并未体现。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Index {
+    build() {
+      Button("XXX")
+        .width(200)
+        .height(100)
+        .onTouch(() =&gt; {
+-         hilog.info(1001, 'Index', 'onTouch') // Avoid printing logs
++         const TAG = 'onTouch';
+        })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -657,6 +713,31 @@
    - 修复代码样例中，上述日志输出被移除了，这意味着修复后的版本没有任何日志记录。因此，修复代码失去了记录拖动动作的功能。
 总结：
 - 修复代码样例中仅添加了一个常量定义，没有实际的功能改进，反而删除了日志记录功能，使得其功能性有所下降。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Index {
+    build() {
+      Row(){
+        Image("XXX")
+          .width(200)
+          .height(100)
+          .draggable(true)
+          .margin({ left: 15 })
+          .border({ color: Color.Black, width: 1 })
+          .onDragMove(() =&gt; {
+-           hilog.info(1001, 'Index', 'onDragMove')
++           const TAG = 'onDragMove';
+-       })
++         })
+? ++
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -727,6 +808,24 @@
 3. **日志输出的移除**：
    - 修复代码样例移除了原有的日志输出逻辑，这意味着事件触发时不会再有日志记录。
 总结：修复代码主要在于移除了日志记录的功能，并且没有引入 `hilog` 库。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Index {
+    build() {
+      Button("")
+        .width(200)
+        .height(100)
+        .onMouse(() =&gt; {
+-         hilog.info(1001, 'Index', 'onMouse')
++         const TAG = 'onMouse';
+        })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -812,6 +911,30 @@
 综上所述，主要的差异在于移除了日志打印的具体实现，转而定义了一个常量以供后续使用，可能旨在提高代码的可读性或者减少不必要的日志输出。</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Index {
+    build() {
+      Row() {
+        Slider({ value: 0, min: 0, max: 100 })
+          .enabled(false)
+          .height(4)
+          .width(100)
+          .trackThickness(3)
+          .blockColor(Color.Red)
+          .blockSize({ width: 4, height: 4 })
+          .onVisibleAreaChange([0.0, 1.0], (isVisible: boolean, currentRatio: number) =&gt; {
+-           hilog.info(1001, 'Index', 'onVisibleAreaChange') // Avoid printing logs
++           const TAG = 'onVisibleAreaChange';
+          })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,6 +1002,29 @@
    - **问题代码样例**：在 `onScroll` 方法中，直接使用 `console.info(xOffset + ' ' + yOffset)` 来输出滚动偏移量。
    - **修复代码样例**：改变了日志记录的方式，仅将 `xOffset` 和 `yOffset` 的拼接结果存储在一个常量 `TAG` 中，但没有执行输出操作（即没有打印该值）。
 总结：修复代码将输出改为仅存储偏移量信息，而不执行实际的打印操作。这可能是出于调试或整理代码的目的。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Index {
+    build() {
+      Scroll(this.scroller) {
+        Column() {
+          Text(this.message)
+          .fontSize(50)
+          .fontWeight(FontWeight.Bold)
+        }.onScroll((xOffset: number, yOffset: number) =&gt; {
+-         console.info(xOffset + ' ' + yOffset)
+?             ^^^^^^^^^                       -
++         const TAG = xOffset + ' ' + yOffset
+?             ^^^^^^^^
+        })
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -945,6 +1091,29 @@
 1. **变量声明**：在修复代码中，`console.log(JSON.stringify(event.touches))` 被替换为 `const text = JSON.stringify(event.touches)`。这意味着在修复代码中，`event.touches` 的字符串化结果被存储在一个名为 `text` 的变量中，而不是直接输出到控制台。
 2. **输出方式**：问题代码样例直接将触摸事件的信息输出到控制台，而修复代码样例则不再有输出语句，改为将值赋给变量 `text`，这可能表示不再需要直接输出到控制台，或者可能是准备在后续的代码中使用这个变量。
 总结：修复代码样例主要的修改是将触摸事件的信息的处理方式从直接输出到控制台改为保存到变量中，不再执行任何打印操作。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+    Row() {
+      Text('1')
+        .fontWeight(FontWeight.Bold)
+        .backgroundColor('black')
+        .fontColor('white')
+        .fontSize(200)
+        .width(200)
+        .height(200)
+        .lineHeight(200)
+        .textAlign(TextAlign.Center)
+    }
+    .onTouch((event: TouchEvent) =&gt; {
+-     console.log(JSON.stringify(event.touches))
+?         ^^ ^^^^^                             -
++     const text = JSON.stringify(event.touches)
+?         ^^^ ^^^^^
+    })
+  }</t>
         </is>
       </c>
     </row>
@@ -1059,6 +1228,46 @@
 - 修复代码样例中主要的变化是去掉了对日志记录函数（`Log.info` 和 `Log.error`）的调用，而只是将信息赋值给变量，导致无法在运行时输出这些信息。这影响了代码的功能性。</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+    Stack() {
+      Column() {
+        LoadingPanel()
+      }
+      .width('100%')
+      .height('100%')
+      Row() {
+        if (this.thumbnail !== null &amp;&amp; this.thumbnail !== undefined) {
+          Image(this.thumbnail)
+            .rotate({
+              x: 0,
+              y: 0,
+              z: 1,
+              angle: 0
+            })
+            .onComplete((): void =&gt; {
+-             Log.info(TAG,
++             let info = TAG + 
+                'onComplete finish, index: ' + this.item.index + ', item: ' + JSON.stringify(this.item) + ', uri: ' +
+-               this.thumbnail + '.');
+?                                   -
++               this.thumbnail + '.';
+            })
+            .onError((): void =&gt; {
+-             Log.error(TAG, 'image show error ' + this.thumbnail + ' ' + this.item.width + ' ' + this.item.height);
+?             ^^^^     ^   ^                                                                                      -
++             let error = TAG + 'image show error ' + this.thumbnail + ' ' + this.item.width + ' ' + this.item.height;
+?             ^^^^     ^^^   ^^
+            })
+        }
+      }
+      .width('100%')
+      .height('100%')
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1166,6 +1375,44 @@
      })
      ```
 综上所述，修复代码样例相对于问题代码样例的主要变化是去掉了背景色设置，并且添加了动画内容销毁的处理，以确保动画在组件不再出现时能够正确清理资源。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  const FRAME_START: number = 60;
+  const FRAME_END: number = 120;
+  @Entry
+  @Component
+  struct LottieAnimation1 {
+    private politeChickyController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private politeChicky: string = 'politeChicky';
+    private politeChickyPath: string = 'media/politeChicky.json';
+    private animateItem?: AnimationItem;
+    build() {
+      Canvas(this.politeChickyController)
+        .width(160)
+        .height(160)
+-       .backgroundColor(Color.Gray)
+        .borderRadius(3)
+        .onReady(() =&gt; {
+-         //告警
+          this.animateItem = lottie.loadAnimation({
+            container: this.politeChickyController,
+            renderer: 'canvas',
+            loop: true,
+            autoplay: true,
+            name: this.politeChicky,
+            path: this.politeChickyPath,
+            initialSegment: [FRAME_START, FRAME_END]
+          })
+        })
++       .onDisAppear(() =&gt; {
++         this.animateItem?.destroy();//只加载了一个Animation，可以使用animateItem的destroy接口
++       })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -1322,6 +1569,124 @@
 总结起来，修复代码通过改进动画名称的管理、去掉了不必要的状态管理、简化布局、改变生命周期钩子的使用等方式来提高代码的可维护性和潜在效率。同时，关于动画的加载和销毁的逻辑进行了调整，以期在不同场景中更好地管理动画资源。</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  // 动画播放的起始帧
+  const FRAME_START: number = 60; 
+  // 动画播放的终止帧
+  const FRAME_END: number = 120; 
+- //调用多次loadAnimation，但是只在onDisAppear销毁一次
+  @Entry
+  @Component
+- struct LottieAnimation4 {
+?                       ^
++ struct LottieAnimation2 {
+?                       ^
+    private politeChickyController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+-   // 动画名称  
+?          --
++   // 动画名称
+    private politeChicky: string = 'politeChicky'; 
+    // hap包内动画资源文件路径，仅支持json格式
+    private politeChickyPath: string = 'media/politeChicky.json'; 
+    private animateItem: AnimationItem | null = null;
+-   // 初始化点击次数 
+-   @State times: number = 0; 
+    build() {
+-     Stack({ alignContent: Alignment.TopStart }) {
+-       // 动画
+-       Canvas(this.politeChickyController)
+? --
++     Canvas(this.politeChickyController)
+-         .width(160)
+? --
++       .width(160)
+-         .height(160)
+? --
++       .height(160)
+-         .backgroundColor(Color.Gray)
+-         .borderRadius(3)
+? --
++       .borderRadius(3)
+-         .onReady(() =&gt; {
+? --
++       .onReady(() =&gt; {
+-           this.animateItem = lottie.loadAnimation({
+? --
++         this.animateItem = lottie.loadAnimation({
+-             container: this.politeChickyController,
+? --
++           container: this.politeChickyController,
+-             renderer: 'canvas',
+? --
++           renderer: 'canvas',
+-             loop: true,
+? --
++           loop: true,
+-             autoplay: true,
+? --
++           autoplay: true,
+-             name: this.politeChicky,
++           name: 'anim_name1',
+-             path: this.politeChickyPath,
+? --
++           path: this.politeChickyPath,
+-             initialSegment: [FRAME_START, FRAME_END]
+? --
++           initialSegment: [FRAME_START, FRAME_END]
+-           })
+          })
++       })
+-         .onClick(() =&gt; {
+? --
++       .onClick(() =&gt; {
+-           this.animateItem = lottie.loadAnimation({
+? --
++         this.animateItem = lottie.loadAnimation({
+-             container: this.politeChickyController,
+? --
++           container: this.politeChickyController,
+-             renderer: 'canvas',
+? --
++           renderer: 'canvas',
+-             loop: true,
+? --
++           loop: true,
+-             autoplay: true,
+? --
++           autoplay: true,
+-             name: this.politeChicky,
++           name: 'anim_name2',
+-             path: this.politeChickyPath,
+? --
++           path: this.politeChickyPath,
+-             initialSegment: [FRAME_START, FRAME_END]
+? --
++           initialSegment: [FRAME_START, FRAME_END]
+-           })
+-           this.times++;
+          })
+-         .onDisAppear(()=&gt; {
+-           //上报此处animateItem，描述description不一样，如果无法找到动画名称，则直接建议用lottie.destory
+-           this.animateItem?.destroy();
+-         })
+? --
++       })
++   }
++   onPageHide(): void {
++     lottie.destroy();
+-       // 响应动画的文本
+-       Text('text')
+-         .fontSize(16)
+-         .margin(10)
+-         .fontColor(Color.White)
+-     }.margin({ top: 20 })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1461,6 +1826,70 @@
 总结来说，修复代码的主要变化是将 `onDisAppear` 方法替换为 `onPageHide` 方法，并且在页面隐藏时销毁所有动画，而不是仅销毁指定的动画。同时移除了背景色的设置。</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  // 动画播放的起始帧
+  const FRAME_START: number = 60; 
+  // 动画播放的终止帧
+  const FRAME_END: number = 120; 
+- //调用了销毁，但是不是全部销毁，上报
+  @Entry
+  @Component
+- struct LottieAnimation5 {
+?                       ^
++ struct LottieAnimation2 {
+?                       ^
+    private politeChickyController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+-   // 动画名称 
+?          -
++   // 动画名称
+    private politeChicky: string = 'politeChicky'; 
+    // hap包内动画资源文件路径，仅支持json格式
+    private politeChickyPath: string = 'media/politeChicky.json'; 
+    private animateItem: AnimationItem | null = null;
+    build() {
+      Canvas(this.politeChickyController)
+        .width(160)
+        .height(160)
+-       .backgroundColor(Color.Gray)
+        .borderRadius(3)
+        .onReady(() =&gt; {
+          this.animateItem = lottie.loadAnimation({
+            container: this.politeChickyController,
+            renderer: 'canvas',
+            loop: true,
+            autoplay: true,
+            name: 'anim_name1',
+            path: this.politeChickyPath,
+            initialSegment: [FRAME_START, FRAME_END]
+          })
+        })
+-       .onClick(()=&gt; {
++       .onClick(() =&gt; {
+?                  +
+          this.animateItem = lottie.loadAnimation({
+            container: this.politeChickyController,
+            renderer: 'canvas',
+            loop: true,
+            autoplay: true,
+            name: 'anim_name2',
+            path: this.politeChickyPath,
+            initialSegment: [FRAME_START, FRAME_END]
+          })
+        })
++   }
++   onPageHide(): void {
++     lottie.destroy();
+-       .onDisAppear(()=&gt;{
+-         //上报lottie,只销毁一个
+-         lottie.destroy('anim_name2');
+-       })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1572,6 +2001,52 @@
 总结来说，修复代码样例通过在点击事件中明确销毁已有动画实例和在消失事件中正确销毁所有相关动画实例，增强了内存管理和资源清理的能力，避免了潜在的资源泄漏问题。</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  @Entry
+  @Component
+- struct LottieExample1 {
++ struct LottieExample1Fixed {
+?                      +++++
+    private myController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private animationItem: AnimationItem | null = null;
+    build() {
+      Canvas(this.myController)
+        .width(200)
+        .height(200)
+        .onReady(() =&gt; {
+          this.animationItem = lottie.loadAnimation({
+            container: this.myController,
+            renderer: 'svg',
+            loop: true,
+            autoplay: true,
+            path: 'animation.json'
+          });
+        })
+        .onClick(() =&gt; {
+-         // 每次点击都加载新动画但未销毁之前的动画
++         if (this.animationItem) {
++           this.animationItem.destroy();  // 首先销毁现有动画实例
++         }
+          this.animationItem = lottie.loadAnimation({
+            container: this.myController,
+            renderer: 'svg',
+            loop: true,
+            autoplay: true,
+            path: 'animation.json'
+          });
+-       })
+-       .onDisAppear(() =&gt; {
+-         lottie.destroy('non_existing_anim'); // 錯誤的动画名称或者只销毁一个动画
+        });
+    }
++   onDisAppear() {
++     lottie.destroy(); // 在页面消失时销毁所有相关动画
++   }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1667,6 +2142,40 @@
 总结：修复代码样例通过在 `onDisAppear` 方法中加入对动画项的销毁逻辑，有效地增强了代码的健壮性，并防止了潜在的内存泄漏问题。</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  @Entry
+  @Component
+- struct LottieExample2 {
++ struct LottieExample2Fixed {
+?                      +++++
+    private animationController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private animationItem: AnimationItem | null = null;
+    build() {
+      Canvas(this.animationController)
+        .width(200)
+        .height(200)
+        .onReady(() =&gt; {
+          this.animationItem = lottie.loadAnimation({
+            container: this.animationController,
+            renderer: 'canvas',
+            loop: false,
+            autoplay: true,
+            path: 'animation2.json'
+          });
+        });
+    }
+    onDisAppear() {
+-     // 未销毁任何动画
++     if (this.animationItem) {
++       this.animationItem.destroy(); // 清除动画确保内存释放
++       this.animationItem = null;
++     }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1719,6 +2228,25 @@
 总结来看，修复代码样例的参数调整使得期望的帧率范围更符合合理的水平，从 `120` 调整为一个更低的值 `60`，并且相应地降低了最小和最大帧率的设置。这可以帮助避免在帧率过高的情况下可能引发的问题。</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let sync: displaySync.DisplaySync = displaySync.create();
+  sync.setExpectedFrameRateRange({
+-   expected: 120,
+?             ^^
++   expected: 60,
+?             ^
+-   min: 120,
+?        ^^^
++   min: 45,
+?        ^^
+-   max: 120,
+?        ^^
++   max: 60,
+?        ^
+  });</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1772,6 +2300,23 @@
 3. `max` 值保持不变：
    - 两个样例中：`max: 120`
 总结来说，修复代码样例相对于问题代码样例的主要差异是在 `expected` 和 `min` 的值上。`expected` 从 120 减少到 30，而 `min` 从 120 减少到 0。这可能是为了允许更低的帧率和更灵活的范围设置。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let range : ExpectedFrameRateRange = {
+-   expected: 120,
+?             ^^
++   expected: 30,
+?             ^
+-   min: 120,
+?        --
++   min: 0,
+    max: 120
+  };
+  let backDisplaySyncSlow: displaySync.DisplaySync;
+  backDisplaySyncSlow = displaySync.create();
+  backDisplaySyncSlow.setExpectedFrameRateRange(range);</t>
         </is>
       </c>
     </row>
@@ -1849,6 +2394,34 @@
 3. **max** 的值保持不变
    - 问题代码和修复代码均为：`max: 120`
 总结来说，修复代码样例对 `expectedFrameRateRange` 的 `expected` 和 `min` 属性进行了修改，以适应更低的帧率要求，而 `max` 属性保持不变。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct Index {
+    build() {
+      Button()
+        .onClick(() =&gt; {
+          animateTo({
+            duration: 1200,
+            iterations: 10,
+            expectedFrameRateRange: { 
+-             expected: 120,
+?                       ^^
++             expected: 30,
+?                       ^
+-             min: 120,
+?                  --
++             min: 0,
+              max: 120,
+            },
+          }, () =&gt; {
+          })
+        })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -1939,6 +2512,42 @@
 这种修改可能是为了优化动画的性能，使其在不同的设备上运行更流畅。</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Slider({ value: this.curTime, min: 0, max: 100 })
+    .enabled(false)
+    .height(4)
+    .width(this.xComponentWidth)
+    .trackThickness(3)
+    .blockColor(Color.Red)
+    .blockSize({ width: 4, height: 4 })
+    .onVisibleAreaChange([0.0, 1.0], (isVisible: boolean, currentRatio: number) =&gt; {
+      if (isVisible &amp;&amp; currentRatio &gt;= 1.0) {
+        animateTo({
+          duration: 30000,
+          iterations: -1,
+          expectedFrameRateRange: {
+-           expected: 120,
+?                     ^^
++           expected: 30,
+?                     ^
+-           min: 120,
+?                --
++           min: 0,
+            max: 120,
+          },
+        }, () =&gt; {
+          if (this.curTime &gt;= 100) {
+            this.curTime = 0;
+          }
+          for (let i = 0; i &lt; 101; i++) {
+            this.curTime += 1;
+          }
+        })
+      }
+    })</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2019,6 +2628,38 @@
 总结而言，修复代码样例主要是通过调整预期帧率范围来改变程序的运行性能，使其能够适应更低的帧率需求。这一变化可能有助于改善在特定情境下的表现或稳定性。</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CreateDisplaySyncSlow() {
+      let range : ExpectedFrameRateRange = {
+-       expected: 120,
+?                 ^^
++       expected: 30,
+?                 ^
+-       min: 120,
+?            --
++       min: 0,
+        max: 120
+      };
+      let draw30 = (intervalInfo: displaySync.IntervalInfo) =&gt; {
+        if (this.isBigger_30) {
+          this.drawFirstSize += 1;
+          if (this.drawFirstSize &gt; 150) {
+            this.isBigger_30 = false;
+          }
+        } else {
+          this.drawFirstSize -= 1;
+          if (this.drawFirstSize &lt; 25) {
+            this.isBigger_30 = true;
+          }
+        }
+      };
+      this.backDisplaySyncSlow = displaySync.create();
+      this.backDisplaySyncSlow.setExpectedFrameRateRange(range);
+      this.backDisplaySyncSlow.on("frame", draw30);
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2070,6 +2711,16 @@
 因此，在修复过程中，确保赋值与变量定义的类型一致是解决问题的关键。</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let intNum = 1;
+- intNum = 1.1; 
+?          ^^^ -
++ intNum = 2;
+?          ^
+</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2760,16 @@
    - 在问题代码中，`floatNum` 最初被赋值为一个浮点数 `1.3`，在后续赋值时却变为了一个整数 `2`，这可能导致类型不一致。
    - 修复代码保持了数据类型的一致性，给 `floatNum` 赋值仍然是一个浮点数 `2.4`。
 总的来说，修复代码确保了变量 `floatNum` 一直保持为浮点数类型，从而避免了类型不一致的问题。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let floatNum = 1.3;
+- floatNum = 2; 
+?              -
++ floatNum = 2.4;
+?             ++
+</t>
         </is>
       </c>
     </row>
@@ -2159,6 +2820,18 @@
 总结而言，修复代码通过保持类型一致性而进行了有效地修正，使得 `intNum` 变量始终为整数类型。</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let intNum = 3;
+  let floatNum = 2.5;
++ intNum = 4;
+- floatNum = 4; 
+?            ^ -
++ floatNum = 1.8;
+?            ^^^
+- intNum = 1.8; </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2200,6 +2873,17 @@
    - 问题代码样例中，虽然两变量的类型声明为 `number`，但赋值为浮点数，可能不符合某些场景对整数的需求。
    - 修复代码样例确保了最终的赋值是整数，这可能是为了满足代码逻辑的需求或规范。
 总结：修复代码样例通过将浮点数更改为整数，确保变量保持在期望的整型值，从而修复了问题代码中的潜在类型不一致性。</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let intNum1: number = 2, intNum2: number = 1;
+- intNum1 = 3.5;
+?            --
++ intNum1 = 3;
+- intNum2 = 4.3;
+?            --
++ intNum2 = 4;</t>
         </is>
       </c>
     </row>
@@ -2250,6 +2934,18 @@
 这是修复过程中这两组代码的主要差异。</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let floatNum1: number = 2.5, floatNum2: number = 1.5;
+- floatNum1 = 3;
++ floatNum1 = 3.5;
+?              ++
+- floatNum2 = 4;
++ floatNum2 = 4.3;
+?              ++
+</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2298,6 +2994,17 @@
 综上所述，修复代码通过移除初始数组大小限制和减少未初始化元素的访问，提高了代码的安全性和内存使用效率。</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>+ let index = 3;
++ let result: number[] = [];
++ result[index] = 0;
+- let count = 100000;
+- let result: number[] = new Array(count);
+- result = new Array();
+- result[9999] = 0;</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2339,6 +3046,14 @@
    - 问题代码在数组的高索引位置存储元素，可能会导致大量未使用的数组索引存在，造成内存浪费，并且在实际使用中处理这样的数组通常会比较复杂，因为数组的有效元素在高索引处，可能并不直观。
    - 修复代码通过将元素放置在索引`0`，确保数组在使用时更具可访问性和一致性。
 综上所述，修复代码的主要差异在于索引的选择，从`5000`变更为`0`，这提高了数组的可用性和内存效率，避免了稀疏数组的问题。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let stringArray: string[] = [];
+- stringArray[5000] = 'example';
+?             ---
++ stringArray[0] = 'example';</t>
         </is>
       </c>
     </row>
@@ -2385,6 +3100,15 @@
 总结来说，修复代码样例通过使用更直观的数组初始化和元素添加方式，提高了代码的可读性和安全性，避免了对未初始化数组索引的直接操作。</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>- let largeArray: number[] = new Array(1000);
+?                                      ----
++ let largeArray: number[] = new Array();
+- largeArray[999] = 42;
++ largeArray.push(42);</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2428,6 +3152,13 @@
 总结：修复后的代码通过直接初始化数组元素，消除了不必要的空数组空间，优化了内存使用，使代码更加简洁有效。</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>+ let array: string[] = ['end'];
+- let array: string[] = new Array(10005);
+- array[9998] = 'end';</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2471,6 +3202,16 @@
    - **问题代码**：由于数组是稀疏的，会在内存中浪费空间，特别是在一个稀疏索引的情况下。
    - **修复代码**：由于数组是紧凑的，优化了内存使用，更加高效。
 总而言之，修复代码通过初始化一个具体的、连续的数组来替代问题代码中稀疏数组的创建，使得代码更加清晰、易读和高效。</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>- let numbers: number[] = [];
++ let numbers: number[] = [1, 2, 3];
+?                          +++++++
+- numbers[100] = 1;
+- numbers[1000] = 2;
+- numbers[10000] = 3;</t>
         </is>
       </c>
     </row>
@@ -2527,6 +3268,25 @@
 - 修复代码将常规数组替换为类型化数组，这种类型更高效地处理数字，并且在内存管理方面具有优势。这种更改有助于提高代码的性能和安全性，尤其是在处理大量数据时。</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>- const typedArray1: number[] = new Array(1, 2, 3);
+?                  ----------
++ const typedArray1 = new Int8Array([1, 2, 3]); 
+?                         ++++      +       +  +
+- const typedArray2: number[] = new Array(4, 5, 6);
+?                  ----------
++ const typedArray2 = new Int8Array([4, 5, 6]);  
+?                         ++++      +       +  ++
+- let res: number[] = new Array(3);
+?        ----------
++ let res = new Int8Array(3);
+?               ++++
+  for (let i = 0; i &lt; 3; i++) {
+       res[i] = typedArray1[i] + typedArray2[i];
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2579,6 +3339,23 @@
 总结来说，修复代码主要是通过使用 `Int8Array` 类型的数组，来提升数值处理的效率，同时改变了数组的声明和初始化方式。</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>- const arr1: number[] = [1, 2, 3, 4, 5];
+- const arr2: number[] = [6, 7, 8, 9, 10];
++ const arr1 = new Int8Array([1, 2, 3, 4, 5]);
++ const arr2 = new Int8Array([6, 7, 8, 9, 10]);
+- let sumArray: number[] = new Array(arr1.length);
+?             ----------
++ let sumArray = new Int8Array(arr1.length);
+?                    ++++
+  for (let i = 0; i &lt; arr1.length; i++) {
+-   sumArray[i] = arr1[i] + arr2[i];
++     sumArray[i] = arr1[i] + arr2[i];
+? ++
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2626,6 +3403,23 @@
 3. **其他代码结构**：
    - 代码逻辑部分（如循环和计算）在两个样例中是一致的，都是通过循环将 `floatArray` 的每个元素乘以2后存入 `doubleArray`。不过，使用 `Float32Array` 使得数组能存储更准确的浮点数值。
 综上所述，修复代码样例通过使用类型化数组（`Float32Array`）来提高了对浮点数的处理效率，同时确保了内存的优化。</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>- let floatArray: number[] = [1.1, 2.2, 3.3, 4.4, 5.5];
+?               ----------
++ let floatArray = new Float32Array([1.1, 2.2, 3.3, 4.4, 5.5]);
+?                  +++++++++++++++++                         +
+- let doubleArray: number[] = new Array(floatArray.length);
+?                ----------
++ let doubleArray = new Float32Array(floatArray.length);
+?                       +++++++
+  for (let i = 0; i &lt; floatArray.length; i++) {
+-   doubleArray[i] = floatArray[i] * 2;
++     doubleArray[i] = floatArray[i] * 2;
+? ++
+  }</t>
         </is>
       </c>
     </row>
@@ -2686,6 +3480,26 @@
 综上所述，修复代码样例的关键差异在于数据结构的选择，增强了数据存储的效率和精确度。</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>- const matrix: number[][] = [
+-   [1, 2, 3],
+-   [4, 5, 6],
+-   [7, 8, 9]
++ const matrix = [
++   new Float64Array([1, 2, 3]),
++   new Float64Array([4, 5, 6]),
++   new Float64Array([7, 8, 9])
+  ];
+- const result: number[] = new Array(matrix.length);
+?             ----------
++ const result = new Float64Array(matrix.length);
+?                    +++++++
+  for (let i = 0; i &lt; matrix.length; i++) {
+    result[i] = matrix[i][i];
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2733,6 +3547,17 @@
    - 使用 `number[]` 可以存储任何数字，包括负数和非常大的数字。
    - `Uint16Array` 只能存储0到65535之间的无符号整数，这意味着在处理数字时需要考虑到这一点，确保数据不会超出范围。
 总结来说，修复代码通过引入 `Uint16Array` 使得内存使用更加高效，并限制了存储的数据类型，提高了类型安全性。</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>- let bigNumbers: number[] = new Array(10000);
+?               ----------
++ let bigNumbers = new Uint16Array(10000);
+?                      ++++++
+  for (let i = 0; i &lt; bigNumbers.length; i++) {
+      bigNumbers[i] = i * 2;
+  }</t>
         </is>
       </c>
     </row>
@@ -2809,6 +3634,35 @@
 总结来说，修复代码对触发加载更多数据的时机进行了调整，改为在项元素出现时的动态检查，提升了用户体验并避免在列表滚动至底部之前不必要的加载。</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 20 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 100; i++) {
++           this.dataSource.addLastItem()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 100])
+      .backgroundColor(this.colors[item % 5])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("onReachEnd")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 100; i++) {
+-       this.datasource.AddLastItem()
+-     }
+-   }, 1000)
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2886,6 +3740,35 @@
 综上所述，修复代码样例的关键差异在于对数据加载时机和触发条件的更改，使得每个元素的出现能触发对新数据的加载，而不是仅依赖于用户滚动到底部的行为。</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 20 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 50; i++) {
++           this.dataSource.addNewItem()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 100])
+      .backgroundColor(this.colors[item % 5])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("onReachEnd")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 50; i++) {
+-       this.datasource.addNewItem()
+-     }
+-   }, 500)
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2958,6 +3841,33 @@
 3. **代码结构的变化**：
    - 在修复样例中，定义的 `FlowItem` 中增加了 `.onAppear()` 方法，这改变了每个项被渲染的时机和条件，允许更灵活的动态加载。
 总结来说，修复代码样例将动态加载数据的时机从列表末尾的到达事件，转换为每个项出现时的事件，从而提供了一种更为灵活和即时的更新方式。</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 15 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 30; i++) {
++           this.dataSource.appendItem()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 50])
+      .backgroundColor(this.colors[item % 3])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("End of List")
+-   for (let i = 0; i &lt; 30; i++) {
+-     this.dataSource.appendItem()
+-   }
+- })</t>
         </is>
       </c>
     </row>
@@ -3040,6 +3950,33 @@
 总结来说，修复代码样例通过在每个项目出现时检查条件并加载更多数据，替换了原来的在滚动到末尾时加载更多的逻辑。这可能是为了提高性能或用户体验，在用户浏览时更智能地加载数据。</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 10 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 20; i++) {
++           this.dataSource.addMoreItems()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 20])
+      .backgroundColor(this.colors[item % 4])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Loading more items")
+-   for (let i = 0; i &lt; 20; i++) {
+-     this.dataSource.addMoreItems()
+-   }
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3114,6 +4051,35 @@
 3. **更改了添加项目的时机**：
    - 在问题代码样例中，当到达底部时每次触发都会添加新项目，而在修复代码样例中，添加项目的逻辑被重新设计为基于 `onAppear` 事件，针对每个 `item` 的出现进行判断和添加。
 综上所述，修复代码样例通过增加 `onAppear` 逻辑和去掉 `onReachEnd` 的处理，实现了更加精确和条件化的项目加载，而不是简单的在滚动到底部时添加项目。</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 25 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 40; i++) {
++           this.dataSource.addItems()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 80])
+      .backgroundColor(this.colors[item % 2])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("End reached")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 40; i++) {
+-       this.dataSource.addItems()
+-     }
+-   }, 1000)
+- })</t>
         </is>
       </c>
     </row>
@@ -3348,6 +4314,128 @@
 总结来说，修复代码样例通过引入观察和状态管理的机制，提高了组件响应外部状态变化的能力，使得各个组件能更好地反映外部 `UIStyle` 的修改。</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class UIStyle {
+    fontSize: number = 0;
+    fontColor: string = '';
+    isChecked: boolean = false;
+  }
+  @Entry
+  @Component
+- struct MultipleAssociationsStateVarReport0 {
++ struct MultipleAssociationsStateVarNoReport0 {
+?                                    ++
+    @State uiStyle: UIStyle = new UIStyle();
+    private listData: string[] = [];
+    aboutToAppear(): void {
+      for (let i = 0; i &lt; 10; i++) {
+        this.listData.push(`ListItemComponent ${i}`);
+      }
+    }
+    build() {
+      Row() {
+        Column() {
+          CompA({item: '1', index: 1, subStyle: this.uiStyle})
+          CompB({item: '2', index: 2, subStyle: this.uiStyle})
+          CompC({item: '3', index: 3, subStyle: this.uiStyle})
+          Text('change state var')
+            .onClick(()=&gt;{
+              this.uiStyle.fontSize = 20;
+            })
+        }
+        .width('100%')
+      }
+      .height('100%')
+    }
+  }
+  @Component
+  struct CompA {
+    @Prop item: string;
+    @Prop index: number;
+-   @Link subStyle: UIStyle;
+-   private sizeFont: number = 50;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State fontSize: number = 0;
+    isRender(): number {
+      console.info(`CompA ${this.index} Text is rendered`);
+-     return this.sizeFont;
+?                 ^   ----
++     return this.fontSize;
+?                 ^^^^^
++   }
++   onStyleChange() {
++     this.fontSize = this.subStyle.fontSize;
+    }
+    build() {
+      Column() {
+        Text(this.item)
+          .fontSize(this.isRender())
+-         .fontSize(this.subStyle.fontSize)
+?                        ---------
++         .fontSize(this.fontSize)
+        Text('abc')
+      }
+    }
+  }
+  @Component
+  struct CompB {
+    @Prop item: string;
+    @Prop index: number;
+-   @Link subStyle: UIStyle;
+-   private sizeFont: number = 50;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State fontColor: string = '#00ffff';
+    isRender(): number {
+      console.info(`CompB ${this.index} Text is rendered`);
+-     return this.sizeFont;
++     return 10;
++   }
++   onStyleChange() {
++     this.fontColor = this.subStyle.fontColor;
+    }
+    build() {
+      Column() {
+        Text(this.item)
+          .fontSize(this.isRender())
+-         .fontColor(this.subStyle.fontColor)
+?                         ---------
++         .fontColor(this.fontColor)
+        Text('abc')
+      }
+    }
+  }
+  @Component
+  struct CompC {
+    @Prop item: string;
+    @Prop index: number;
+-   @Link subStyle: UIStyle;
+-   private sizeFont: number = 50;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State isChecked: boolean = false;
+    isRender(): number {
+      console.info(`CompC ${this.index} Text is rendered`);
+-     return this.sizeFont;
++     return 50;
++   }
++   onStyleChange() {
++     this.isChecked = this.subStyle.isChecked;
+    }
+    build() {
+      Column() {
+-       if (this.subStyle.isChecked) {
+?                ---------
++       if (this.isChecked) {
+          Text('checked')
+        } else {
+          Text('unchecked')
+        }
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3467,6 +4555,63 @@
 总的来说，修复代码样例通过引入本地状态 `localFontSize` 和观察变化的机制，使得组件可以在 `subStyle` 改变时进行相应的更新，提供更好的数据管理和响应性。</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class UIStyle {
+    fontSize: number = 0;
+  }
+  @Entry
+  @Component
+- struct Example1 {
++ struct Example1Fixed {
+?                +++++
+    @State uiStyle: UIStyle = new UIStyle();
+    build() {
+      Column() {
+        CompA({ subStyle: this.uiStyle })
+        CompB({ subStyle: this.uiStyle })
+        Text('Change Font Size')
+          .onClick(() =&gt; {
+            this.uiStyle.fontSize = 24;
+          })
+      }
+    }
+  }
+  @Component
+  struct CompA {
+-   @Link subStyle: UIStyle;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State localFontSize: number = 0;
++   onStyleChange() {
++     this.localFontSize = this.subStyle.fontSize;
++   }
+    build() {
+      Text('Component A')
+-       .fontSize(this.subStyle.fontSize)
+?                      ------ ^^^
++       .fontSize(this.localFontSize)
+?                       ^^^^^
+    }
+  }
+  @Component
+  struct CompB {
+-   @Link subStyle: UIStyle;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State localFontSize: number = 0;
++   onStyleChange() {
++     this.localFontSize = this.subStyle.fontSize;
++   }
+    build() {
+      Text('Component B')
+-       .fontSize(this.subStyle.fontSize)
+?                      ------ ^^^
++       .fontSize(this.localFontSize)
+?                       ^^^^^
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3570,6 +4715,49 @@
 综上所述，修复代码样例通过使用`@Watch`和`localChecked`来处理状态同步，避免了直接依赖外部状态，从而提高了组件的可维护性以及正确性。</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class UIStyle {
+    isChecked: boolean = false;
+  }
+  @Entry
+  @Component
+- struct Example2 {
++ struct Example2Fixed {
+?                +++++
+    @State uiStyle: UIStyle = new UIStyle();
+    build() {
+      Column() {
+        CompC({ subStyle: this.uiStyle })
+        Text('Toggle Checked')
+          .onClick(() =&gt; {
+            this.uiStyle.isChecked = !this.uiStyle.isChecked;
+          })
+      }
+    }
+  }
+  @Component
+  struct CompC {
+-   @Link subStyle: UIStyle;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State localChecked: boolean = false;
++   onStyleChange() {
++     this.localChecked = this.subStyle.isChecked;
++   }
+    build() {
+-     if (this.subStyle.isChecked) {
+?              ------ ^^^^
++     if (this.localChecked) {
+?               ^^^^
+        Text('Checked')
+      } else {
+        Text('Unchecked')
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3687,6 +4875,63 @@
 4. **使用本地状态进行绘制**：
    - 在 `CompA` 和 `CompC` 的 `build` 方法中，字体颜色不再通过 `this.subStyle.fontColor` 直接获取，而是使用 `this.localFontColor` 来设置字体颜色。这确保了组件在更新时，使用的是本地状态的值。
 这些变化共同作用，使得组件能够更好地管理自己的状态，并在外部 `uiStyle` 发生变化时做出相应的更新，确保UI的正确性和响应性。</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class UIStyle {
+    fontColor: string = '#000000';
+  }
+  @Entry
+  @Component
+- struct Example3 {
++ struct Example3Fixed {
+?                +++++
+    @State uiStyle: UIStyle = new UIStyle();
+    build() {
+      Column() {
+        CompA({ subStyle: this.uiStyle })
+        CompC({ subStyle: this.uiStyle })
+        Text('Change Font Color')
+          .onClick(() =&gt; {
+            this.uiStyle.fontColor = '#FF0000';
+          })
+      }
+    }
+  }
+  @Component
+  struct CompA {
+-   @Link subStyle: UIStyle;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State localFontColor: string = '#000000';
++   onStyleChange() {
++     this.localFontColor = this.subStyle.fontColor;
++   }
+    build() {
+      Text('Component A')
+-       .fontColor(this.subStyle.fontColor)
+?                       ------ ^^^
++       .fontColor(this.localFontColor)
+?                        ^^^^^
+    }
+  }
+  @Component
+  struct CompC {
+-   @Link subStyle: UIStyle;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State localFontColor: string = '#000000';
++   onStyleChange() {
++     this.localFontColor = this.subStyle.fontColor;
++   }
+    build() {
+      Text('Component C')
+-       .fontColor(this.subStyle.fontColor)
+?                       ------ ^^^
++       .fontColor(this.localFontColor)
+?                        ^^^^^
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -3820,6 +5065,69 @@
 4. **代码结构的清晰性**：
    - 修复后的代码提供了更好的封装性和可维护性。通过将状态管理和变化逻辑分离，`CompB` 和 `CompC` 的实现变得更加清晰。
 总结来说，修复后的代码通过引入局部状态和状态观察机制，为组件提供了更好的状态管理，避免了直接对父组件状态的依赖，从而确保了组件的稳定性和正确性。</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class UIStyle {
+    isChecked: boolean = false;
+  }
+  @Entry
+  @Component
+- struct Example4 {
++ struct Example4Fixed {
+?                +++++
+    @State uiStyle: UIStyle = new UIStyle();
+    build() {
+      Column() {
+        CompB({ subStyle: this.uiStyle })
+        CompC({ subStyle: this.uiStyle })
+        Text('Toggle Check')
+          .onClick(() =&gt; {
+            this.uiStyle.isChecked = !this.uiStyle.isChecked;
+          })
+      }
+    }
+  }
+  @Component
+  struct CompB {
+-   @Link subStyle: UIStyle;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State localChecked: boolean = false;
++   onStyleChange() {
++     this.localChecked = this.subStyle.isChecked;
++   }
+    build() {
+-     if (this.subStyle.isChecked) {
+?              ------ ^^^^
++     if (this.localChecked) {
+?               ^^^^
+        Text('Component B Checked')
+      } else {
+        Text('Component B Unchecked')
+      }
+    }
+  }
+  @Component
+  struct CompC {
+-   @Link subStyle: UIStyle;
++   @Link @Watch('onStyleChange') subStyle: UIStyle;
++   @State localChecked: boolean = false;
++   onStyleChange() {
++     this.localChecked = this.subStyle.isChecked;
++   }
+    build() {
+-     if (this.subStyle.isChecked) {
+?              ------ ^^^^
++     if (this.localChecked) {
+?               ^^^^
+        Text('Component C Checked')
+      } else {
+        Text('Component C Unchecked')
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -3913,6 +5221,31 @@
 - 修复代码样例通过在 `ForEach` 函数中添加了第三个参数，实现了为每个生成的列表项提供唯一标识符的功能。这是修复的关键点，可能是为了确保列表项的正确更新和渲染。</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ForeachTest {
+    private data: string[] = ['1', '2', '3'];
+    build() {
+      RelativeContainer() {
+        List() {
+          ForEach(this.data, (item: string, index: number) =&gt; {
+            ListItem() {
+              Text(item);
+            }
+-         })
++         }, (item: string, index: number) =&gt; item)
+        }
+        .width('100%')
+        .height('100%')
+      }
+      .height('100%')
+      .width('100%')
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3984,6 +5317,29 @@
 其他部分的代码结构和逻辑没有变化，所以整体布局、样式和功能保持一致。</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+      Column() {
+        Scroll() {
+          Flex({
+            direction : FlexDirection.Column ,
+            justifyContent : FlexAlign.SpaceBetween ,
+            alignItems : ItemAlign.Start
+          }) {
+            ForEach(this.autoItems , (item: TestAuto , index: number) =&gt; {
+              this.IngredientItem(item , index)
+-           })
++           }, (item: TestAuto, index: number) =&gt; item.name)
+          }
+        }
+        .scrollBarWidth(20)
+      }
+      .height(ConfigData.WH_80_100)
+      .padding({ top : 5 , right : 10 , left : 10 })
+    }</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4054,6 +5410,31 @@
 这个改动的目的是为了提高列表渲染的效率，帮助框架更好地跟踪每个元素的变化，从而减少重绘和重新渲染的开销。</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-   build() {
+? --
++ build() {
+      Column() {
+        Scroll() {
+          Flex({
+            direction : FlexDirection.Column ,
+            justifyContent : FlexAlign.SpaceBetween ,
+            alignItems : ItemAlign.Start
+          }) {
+            ForEach(this.apiItems , (item: TestApi , index: number) =&gt; {
+              this.IngredientItem(item , index)
+-           })
++           }, (item: TestApi, index: number) =&gt; item.name)
+          }
+        }
+        .scrollBarWidth(20)
+      }
+      .height(ConfigData.WH_88_100)
+      .padding({ top : 5 , right : 10 , left : 10 })
+    }</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4123,6 +5504,29 @@
    - 在修复代码样例中，`ForEach` 方法增加了第三个参数：`(item: TestScenario, index: number) =&gt; item.name`。这个额外的参数通常用于提供一个唯一的标识符或键，以便优化列表渲染。
 总结：
 - 修复代码中对 `ForEach` 函数的调用进行了修改，增加了对唯一标识符的支持，这是一个重要的改进，可能是为了提高组件的性能和正确渲染。</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+      Column() {
+        Scroll() {
+          Flex({
+            direction : FlexDirection.Column ,
+            justifyContent : FlexAlign.SpaceBetween ,
+            alignItems : ItemAlign.Start
+          }) {
+            ForEach(this.scenarioItems , (item: TestScenario , index: number) =&gt; {
+              this.IngredientItem(item , index)
+-           })
++           }, (item: TestScenario , index: number) =&gt; item.name)
+          }
+        }
+        .scrollBarWidth(20)
+      }
+      .height(ConfigData.WH_80_100)
+      .padding({ top : 5 , right : 10 , left : 10 })
+    }</t>
         </is>
       </c>
     </row>
@@ -4215,6 +5619,40 @@
 这些修改提高了代码的类型安全性和性能，减少了因缺乏唯一标识而可能产生的渲染问题。</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+      Column() {
+        Row() {
+          //TODO 用常量替换
+          Text('仓库列表')
+            .align(Alignment.Start)
+            .fontColor($r("app.color.text_strong"))
+          Blank()
+          Image($r("app.media.icon_arrow_right"))
+            .height('100%')
+            .aspectRatio(1)
+            .onClick(() =&gt; {
+              this.viewModel.onRepos()
+            })
+        }.width('100%')
+        .height(50)
+        .padding({left:24,right:24,top:24})
+        Divider()
+          .color($r("app.color.boarder_medium"))
+          .margin({ top: 16, bottom: 16 })
+        List() {
+-         ForEach(this.viewModel.repos, (item) =&gt; {
++         ForEach(this.viewModel.repos, (item: Repo) =&gt; {
+?                                            ++++++
+            ListItem() {
+              RepoItem({ viewModel: $viewModel, repo: item })
+            }
+-         })
++         }, (item: Repo) =&gt; item.repoName)
+        }.width('100%')</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4268,6 +5706,23 @@
 2. **唯一标识符**：
    - 修复后的代码在 `ForEach` 方法中添加了第三个参数，`(item: Issue) =&gt; item.id`，这个参数是用于获取每个 `item` 的唯一标识符，便于后续的列表渲染和性能优化。这个改动提升了渲染性能，同时可以减少潜在的渲染错误。
 总结来说，修复代码样例通过添加类型注解和唯一标识符的逻辑，增强了代码的类型安全性和渲染的效率。</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+      List({space: 16}) {
+-       ForEach(this.viewModel.issues, (item)=&gt;{
++       ForEach(this.viewModel.issues, (item: Issue)=&gt;{
+?                                           +++++++
+          ListItem() {
+            IssueItem({viewModel: this.viewModel, issue: item})
+          }
+-       })
++       }, (item: Issue) =&gt; item.id)
+      }.padding(20)
+      .width('100%')
+    }</t>
         </is>
       </c>
     </row>
@@ -4441,6 +5896,68 @@
 其他部分的代码在结构和功能上没有变化。</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+    Column() {
+      Stack() {
+        Column() {
+          Column({ space: 18 }) {
+            if (this.recordingStatus === 0) {
+              ForEach(this.sidebarList_1, (sidebar: Resource, index: number) =&gt; {
+                Image($r('app.media.app_icon'))
+                  .width(28)
+                  .height(28)
+                  .objectFit(ImageFit.Contain)
+                if (index === 1) {
+                  Divider()
+                    .vertical(false)
+                    .height(1)
+                    .width(22)
+                    .color($r('app.color.COLOR_FFFFFF'))
+                    .margin({ right: 4 })
+                }
+-             })
++             }, (sidebar: Resource, index: number) =&gt; index)
+            } else if (this.recordingStatus === 2) {
+              ForEach(this.sidebarList_2, (sidebar: Resource, index: number) =&gt; {
+                Image($r('app.media.app_icon'))
+                  .width(28)
+                  .height(28)
+                  .objectFit(ImageFit.Contain)
+                if (index === 0) {
+                  Divider()
+                    .vertical(false)
+                    .height(1)
+                    .width(22)
+                    .color($r('app.color.COLOR_FFFFFF'))
+                    .margin({ right: 4 })
+                }
+                if (index === 1) {
+                  Text($r('app.string.Wen'))
+                    .textAlign(TextAlign.Center)
+                    .fontColor($r('app.color.COLOR_FFFFFF'))
+                    .fontSize(22)
+                    .fontFamily($r('app.string.Font_family_medium'))
+                    .margin({ right: 4 })
+                }
+-             })
++             }, (sidebar: Resource, index: number) =&gt; index)
+            }
+          }
+          .width('100%')
+          .height('50%')
+        }
+        .width('100%')
+        .height('100%')
+      }
+      .width('100%')
+      .height('91%')
+      .borderRadius(12)
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4502,46 +6019,109 @@
 结合上述差异，修复代码样例在类型安全和明确性方面做了改进，使得代码更易读、易维护，也更符合类型检查的要求。</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Column() {
+-             ForEach(this.list, (item) =&gt; {
++             ForEach(this.list, (item: number) =&gt; {
+?                                     ++++++++
+                Text(item.toString())
+                  .width('90%')
+                  .height(72)
+                  .backgroundColor('#fff')
+                  .borderRadius(15)
+                  .fontSize(24)
+                  .textAlign(TextAlign.Center)
+                  .margin(10)
+-             }, item =&gt; item)
++             }, (item: number) =&gt; item.toString())
+            }.width('100%').backgroundColor('#F1F3F5').padding({ bottom: 10 })</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>@security/no-cycle</t>
+          <t>@performance/constant-property-referencing-check-in-loops</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>该规则禁止使用循环依赖</t>
+          <t>在循环如需频繁访问某个常量，且该属性引用常量在循环中不会改变，建议提取到循环外部，减少属性访问的次数</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>// Foo.ets
-import {} from './Bar.ets';
-// Bar.ets
-import {} from './Foo.ets';</t>
+          <t>class Time {
+  static start: number = 0;
+  static info: number[] = [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12];
+}
+function getNum(num: number): number {
+  /* Year has (12 * 29 =) 348 days at least */
+  let total: number = 348;
+  for (let year_0 = 1; year_0 &lt;= 2024; year_0++) {
+    // warning
+    for(let month_0 = 1; month_0 &lt;= 12; month_0++) {
+      for(let day_0 = 1; day_0 &lt;= 31; day_0++) {
+        total += ((Time.info[num - Time.start] &amp; day_0) !== 0) ? 1 : 0;
+      }
+    }
+  }
+  return total;
+}</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>通过复制文件来引入其它文件来避免出现循环引入</t>
+          <t>在三重循环中使用了常量Time.info[num - Time.start]，需要把常量提取出最外层循环的外面</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>// Foo.ets
-import {} from './Bar.ets';
-// Bar.ets
-import {} from './Foo1.ets';</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>在修复代码样例中，相对于问题代码样例的主要差异如下：
-1. **文件名变化**：
-   - 原问题代码中的 `Bar.ets` 依然保持不变。
-   - 原问题代码中的 `Foo.ets` 在修复代码样例中被修改为 `Foo1.ets`。
-这意味着修复过程中，`Foo.ets` 的导入路径被改成了 `Foo1.ets`，以避免相互递归的导入问题。</t>
+          <t>class Time {
+  static start: number = 0;
+  static info: number[] = [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12];
+}
+function getNum(num: number): number {
+  /* Year has (12 * 29 =) 348 days at least */
+  let total: number = 348;
+  let time_info = Time.info[num - Time.start]
+  for (let year_0 = 1; year_0 &lt;= 2024; year_0++) {
+    // warning
+    for(let month_0 = 1; month_0 &lt;= 12; month_0++) {
+      for(let day_0 = 1; day_0 &lt;= 31; day_0++) {
+        total += ((time_info &amp; day_0) !== 0) ? 1 : 0;
+      }
+    }
+  }
+  return total;
+}</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Time {
+    static start: number = 0;
+    static info: number[] = [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12];
+  }
+  function getNum(num: number): number {
+    /* Year has (12 * 29 =) 348 days at least */
+    let total: number = 348;
++   let time_info = Time.info[num - Time.start]
+    for (let year_0 = 1; year_0 &lt;= 2024; year_0++) {
+      // warning
+      for(let month_0 = 1; month_0 &lt;= 12; month_0++) {
+        for(let day_0 = 1; day_0 &lt;= 31; day_0++) {
+-         total += ((Time.info[num - Time.start] &amp; day_0) !== 0) ? 1 : 0;
+?                    ^   ^    ------------------
++         total += ((time_info &amp; day_0) !== 0) ? 1 : 0;
+?                    ^   ^
+        }
+      }
+    }
+    return total;
+  }</t>
         </is>
       </c>
     </row>
@@ -4610,6 +6190,27 @@
    - 在问题代码中，使用了严格不等于运算符 `!==` 进行比较。
    - 在修复代码中，使用了非严格不等于运算符 `!=` 进行比较。尽管在这个特定上下文中没有实际影响，但这种变更可视为风格或偏好问题。
 总结：修复后的代码通过引入局部变量来优化性能，并且采用了更直观的条件判断方式，使得代码更易于理解和维护。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Time {
+    static start: number = 0;
+    static info: number[] = [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12];
+  }
+  function getNum(num: number): number {
+    /* Year has (12 * 29 =) 348 days at least */
+    let total: number = 348;
++   const info = Time.info[num- Time.start];  
+    for (let index: number = 0x8000; index &gt; 0x8; index &gt;&gt;= 1) {
+-     // warning
+-     total += ((Time.info[num - Time.start] &amp; index) !== 0) ? 1 : 0;
++     if ((info &amp; index) != 0) {
++       total++;
++     }
+    }
+    return total;
+  }</t>
         </is>
       </c>
     </row>
@@ -4686,6 +6287,24 @@
 总结一下，修复代码样例相较于问题代码样例在逻辑清晰度和简洁性上进行了改进，通过直接使用 `i` 来计算索引，避免了对 `positionValue` 的依赖。这些改动使得代码更简洁、更易读，而不改变最终的逻辑功能。</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Config {
+    static settings: number[] = [5, 10, 15, 20, 25, 30];
+  }
+  function calculateSum(length: number): number {
+    let sum: number = 0;
+-   let positionValue: number = 1;
+    for (let i = 0; i &lt; 5; i++) {
+-     sum += Config.settings[length - positionValue];
+-     positionValue++;
++     const index = length - (i + 1);  // 提取到循环外部
++     sum += Config.settings[index];
+    }
+    return sum;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4751,6 +6370,25 @@
 总结来说，修复代码通过将重复引入的数组元素提取为一个常量，提升了性能与可读性。</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Record {
+    static data: number[] = [11, 12, 13, 14, 15];
+  }
+  function processValues(pointer: number, limit: number): number {
+    let result: number = 1;
++   const fixedValue = Record.data[pointer - 1]; // 提取到循环外部
+    for (let j = 0; j &lt; limit; j++) {
+-     if (Record.data[pointer - 1] &gt; Record.data[j]) {
+-       result *= Record.data[pointer - 1]; // 重复引用
++     if (fixedValue &gt; Record.data[j]) {
++       result *= fixedValue;
+      }
+    }
+    return result;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4811,6 +6449,24 @@
 修复代码样例通过将计算中的重复访问提取到循环外部，优化了代码的性能和可读性，避免了不必要的多次数组访问。</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Constants {
+    static values: number[] = [100, 200, 300, 400, 500];
+  }
+  function calculateDifference(start: number): number {
+    let difference: number = 0;
++   const baseValue = Constants.values[start]; // 提取到循环外
+    for (let k = 0; k &lt; Constants.values.length; k++) {
+-     difference += Constants.values[k] - Constants.values[start];
+?                                         ^^^ ^^^^^^^    --------
++     difference += Constants.values[k] - baseValue;
+?                                         ^^ ^^
+    }
+    return difference;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4871,6 +6527,23 @@
    - 修复后的代码在可读性上有所提升，因为它清楚地表明了一个重要的中间值（`configurationValue`），使得后续的计算逻辑更为明确。
    - 这种做法也提高了代码的可维护性，若将来需要更改这个值的计算方式，只需在一个地方进行修改，而不是在循环中多次进行修改。
 总的来说，修复代码通过优化计算方式和提升代码可读性，使得整体性能和可维护性得到了改善。</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Database {
+    static configurations: number[] = [22, 33, 44, 55, 66];
+  }
+  function updateSum(offset: number): number {
+    let sum: number = 0;
+    let key: number = 2;
++   const configurationValue = Database.configurations[key - offset]; // 提取到循环外
+    for (let i = 0; i &lt; 4; i++) {
+-     sum += Database.configurations[key - offset];  // 多次访问相同值
++     sum += configurationValue;
+    }
+    return sum;
+  }</t>
         </is>
       </c>
     </row>
@@ -4934,6 +6607,23 @@
 3. **性能优化**：
    - 修复后的代码在性能上也有一定的优化，因为在循环中减少了对数组元素的重复访问。
 总结来说，修复代码通过提取和存储固定组件的引用，提高了代码的性能、可读性，并减少了不必要的重复计算。</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Settings {
+    static components: string[] = ["ComponentA", "ComponentB", "ComponentC"];
+  }
+  function checkComponents(fixedIndex: number): boolean {
++   const targetComponent = Settings.components[fixedIndex]; // 提取到循环外
+    for (let i = 0; i &lt; Settings.components.length; i++) {
+-     if (Settings.components[i] === Settings.components[fixedIndex]) {  // 不必要的重复引用
++     if (Settings.components[i] === targetComponent) {
+        return true;
+      }
+    }
+    return false;
+  }</t>
         </is>
       </c>
     </row>
@@ -4985,6 +6675,16 @@
    - 在问题代码样例中，只获取了‘zone_offset’，即时区的固定偏移量。
    - 在修复代码样例中，新增获取‘dst_offset’的功能，可能是为了处理与夏令时相关的额外时间偏移，确保时间计算的准确性。
 总之，修复代码通过增加获取夏令时偏移量的操作，使得时间计算更加全面和准确。</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import i18n from '@ohos.i18n';
+  let timeZone1 = '123';
+  let calendar1 = i18n.getCalendar(i18n.getSystemLocale());
+  calendar1.setTimeZone(timeZone1);
+  calendar1.get('zone_offset'); 
++ calendar1.get('dst_offset');</t>
         </is>
       </c>
     </row>
@@ -5035,6 +6735,15 @@
    - 问题代码没有显示系统时区的获取过程，因此可能导致设置不准确或无效。
    - 修复代码优先获取系统的时区信息，并确保在调用时区设置方法时使用了该信息，这样可以确保处理更为准确。
 综上所述，修复代码通过引入不同的模块和采用更合适的方法来处理时区设置，保证了更高的准确性和适应性。</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- import systemDateTime from '@ohos.systemDateTime';
+- systemDateTime.setTimezone();
++ import i18n from '@ohos.i18n';
++ let calendar = i18n.getCalendar(i18n.getSystemLocale());
++ calendar.setTimeZone(i18n.getTimeZone().getID()); </t>
         </is>
       </c>
     </row>
@@ -5134,6 +6843,32 @@
 综上所述，修复代码样例在引入数据源、数据结构、遍历方法及数据项类型等方面进行了改进，使得代码更加模块化和灵活。</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>+ import { MyDataSource } from './MyDataSource';
+  @Entry
+  @Component
+  struct MyComponent {
+-   @State arr: number[] = [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21]
++   private arr: MyDataSource = new MyDataSource()
+    build() {
+      List() {
+        // List中建议使用LazyForEach
+-       ForEach(this.arr, (item: number) =&gt; {
+?                                 ^^^^^
++       LazyForEach(this.arr, (item: string) =&gt; {
+?       ++++                         ++++ ^
+          ListItem() {
+            Text(`item value: ${item}`)
+          }
+        }, (item: number) =&gt; item.toString())
+      }
+      .width('100%')
+      .height('100%')
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5235,6 +6970,45 @@
 3. **ItemComponent 引用的参数**:
    - 这部分代码在两个样例中没有变化，依旧是 `ItemComponent({ introduce: item }).reuseId(item)`。这个部分保持一致，说明组件的用法没有改变。
 总体来说，修复代码的主要目的是将数据源从一个静态数组替换为一个更动态或复杂的数据源，并且更改了遍历的方式以提高性能。</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import { MyDataSource } from './MyDataSource';
+  @Reusable
+  @Component
+  struct ItemComponent {
+    @State introduce: string = ''
+    aboutToReuse(params: Record&lt;string, ESObject&gt;) {
+      this.introduce = params.introduce
+    }
+    build() {
+      Text(this.introduce)
+        .fontSize(14)
+        .padding({ left: 5, right: 5 })
+        .margin({ top: 5 })
+    }
+  }
+  @Entry
+  @Component
+  struct MyComponent {
+-   private data: number[] = [1,2,3,4,5,6,7]
++   private data: MyDataSource = new MyDataSource()
+    build() {
+      List() {
+-       ForEach(this.data, (item: string) =&gt; {
++       LazyForEach(this.data, (item: string) =&gt; {
+?       ++++
+          ListItem() {
+            // 使用reuseId对不同的自定义组件实例分别标注复用组，以达到最佳的复用效果
+            ItemComponent({ introduce: item }).reuseId(item)
+          }
+        }, (item: string) =&gt; item)
+      }
+      .width('100%')
+      .height('100%')
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -5369,6 +7143,70 @@
 总结：修复代码通过引入数据源的概念，改善了数据管理的方式，同时也对数据的内容进行了调整。这样做提高了代码的可维护性和可读性。</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>+ export class DataSource implements IDataSource{
++   private dataArray: string[] = []
++   private listeners: DataChangeListener[] = []
++   constructor() {
++     for(let i=0; i&lt; 26; i++) {
++       this.dataArray.push(i + 'a')
++     }
++   }
++   public getData(index: number): string {
++     return this.dataArray[index]
++   }
++   public totalCount(): number {
++     return this.dataArray.length
++   }
++   registerDataChangeListener(listener: DataChangeListener): void {
++     if (this.listeners.indexOf(listener) &lt; 0) {
++       this.listeners.push(listener)
++     }
++   }
++   unregisterDataChangeListener(listener: DataChangeListener): void {
++     const pos = this.listeners.indexOf(listener)
++     if (pos &gt;= 0) {
++       this.listeners.splice(pos, 1)
++     }
++   }
++ }
+  @Entry
+  @Component
+  struct AlphabetIndexerSample {
+    scroller: Scroller = new Scroller()
+    private value: string[] = ['A', 'B', 'C', 'D', 'E', 'F', 'G', 'H', 'I', 'J', 'K', 'L', 'M', 'N', 'O', 'P', 'Q', 'R', 'S', 'T', 'U', 'V', 'W', 'X', 'Y', 'Z']
+-   private listValue: string[] = ['A', 'B', 'C', 'D', 'E', 'F', 'G', 'H', 'I', 'J', 'K', 'L', 'M', 'N', 'O', 'P', 'Q', 'R', 'S', 'T', 'U', 'V', 'W', 'X', 'Y', 'Z']
++   // private listValue: string[] = ['A', 'B', 'C', 'D', 'E', 'F', 'G', 'H', 'I', 'J', 'K', 'L', 'M', 'N', 'O', 'P', 'Q', 'R', 'S', 'T', 'U', 'V', 'W', 'X', 'Y', 'Z']
+?  +++
++   private listValue: DataSource = new DataSource()
+    @State index: number = 0
+    @State selectedColor: string = '#00ffff'
+    @State popupColor: string = '#00ffff'
+    @State selectedBackgroundColor: string = '#ff0000'
+    @State popupBackground: string = '#ff0000'
+    @State usingPopup: boolean = true
+    @State itemSize: number = 13
+    @State location: boolean = true
+    build() {
+      Flex({ direction: FlexDirection.Column }) {
+        Row() {
+          NavigationBar({ title: 'AlphabetIndexer' })
+        }.padding({ left: '3%' })
+        Flex({ direction: this.location ? FlexDirection.Row : FlexDirection.RowReverse }) {
+          List({ space: 10, initialIndex: 0, scroller: this.scroller }) {
+-           LazyForEach(this.listValue, (item) =&gt; {
++           LazyForEach(this.listValue, (item: string) =&gt; {
+?                                            ++++++++
+              ListItem() {
+                Column() {
+                  Text('     ' + item)
+                    .height(30)
+                    .fontSize(16)
+                    .width('100%')
+                    .textAlign(TextAlign.Start)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5448,6 +7286,31 @@
    - 问题代码样例中的 `arr` 是 `@State`，表示组件状态的一部分并能触发 UI 的更新。
    - 修复代码样例中的 `arr` 是 `private`，这意味着它不会直接影响用户界面的状态更新，需要其他方式来处理状态变化。
 总结而言，修复代码对数据来源和类型处理做了较大改变，尤其在性能优化和数据展示方面进行了增强。</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>+ import { MyDataSource } from './MyDataSource';
+  @Entry
+  @Component
+  struct MyComponent {
+-   @State arr: number[] = [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21]
++   private arr: MyDataSource = new MyDataSource()
+    build() {
+      List() {
+-       ForEach(this.arr, (item: number) =&gt; {
+?                                 ^^^^^
++       LazyForEach(this.arr, (item: string) =&gt; {
+?       ++++                         ++++ ^
+          ListItem() {
+            Text(`item value: ${item}`)
+          }
+        }, (item: number) =&gt; item.toString())
+      }
+      .width('100%')
+      .height('100%')
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -5563,6 +7426,44 @@
 这些差异表明，修复代码样例旨在更改数据的来源和迭代逻辑，以适应可能更大或更复杂的数据结构，同时提供懒加载的支持。</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import { MyDataSource } from './MyDataSource';
+  @Reusable
+  @Component
+  struct ItemComponent {
+    @State introduce: string = ''
+    aboutToReuse(params: Record&lt;string, ESObject&gt;) {
+      this.introduce = params.introduce
+    }
+    build() {
+      Text(this.introduce)
+        .fontSize(14)
+        .padding({ left: 5, right: 5 })
+        .margin({ top: 5 })
+    }
+  }
+  @Entry
+  @Component
+  struct MyComponent {
+-   private data: number[] = [1,2,3,4,5,6,7]
++   private data: MyDataSource = new MyDataSource()
+    build() {
+      List() {
+-       ForEach(this.data, (item: string) =&gt; {
++       LazyForEach(this.data, (item: string) =&gt; {
+?       ++++
+          ListItem() {
+            ItemComponent({ introduce: item }).reuseId(item)
+          }
+        }, (item: string) =&gt; item)
+      }
+      .width('100%')
+      .height('100%')
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5674,6 +7575,59 @@
 总之，修复代码样例通过引入`DataSource`类来封装和管理数据，增强了性能、可维护性，同时提供了更清晰的接口以供未来的扩展或修改。</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>+ export class DataSource implements IDataSource {
++   private dataArray: string[] = []
++   constructor() {
++     for(let i = 0; i &lt; 26; i++) {
++       this.dataArray.push(String.fromCharCode(65 + i)) // A - Z
++     }
++   }
++   registerDataChangeListener(listener: DataChangeListener): void {
++     throw new Error("Method not implemented.")
++   }
++   unregisterDataChangeListener(listener: DataChangeListener): void {
++     throw new Error("Method not implemented.")
++   }
++   public getData(index: number): string {
++     return this.dataArray[index]
++   }
++   public totalCount(): number {
++     return this.dataArray.length
++   }
++ }
+  @Entry
+  @Component
+  struct AlphabetIndexerSample {
++   private value: DataSource = new DataSource()
+-   scroller: Scroller = new Scroller()
+-   private value: string[] = ['A', 'B', 'C', 'D', 'E', 'F', 'G', 'H', 'I', 'J', 'K', 'L', 'M', 'N', 'O', 'P', 'Q', 'R', 'S', 'T', 'U', 'V', 'W', 'X', 'Y', 'Z']
+-   @State index: number = 0
+    build() {
+      Flex({ direction: FlexDirection.Column }) {
+        Row() {
+-         Navigation()
++         Navigation() {
+?                     ++
++         }
+        }
+        Flex({ direction: FlexDirection.Row }) {
+          List() {
+-           ForEach(this.value, (item: string) =&gt; {
++           LazyForEach(this.value, (item: string) =&gt; {
+?           ++++
+              ListItem() {
+                Text(item)
+              }
+            })
+          }
+        }
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5768,6 +7722,48 @@
 综上所述，主要差异体现在模块化设计、数据处理方式、访问方式、数据初始化方式、以及对未来扩展的准备上，增强了代码的可维护性和可扩展性。</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>+ export class MyDataSource implements IDataSource {
++   registerDataChangeListener(listener: DataChangeListener): void {
++     throw new Error("Method not implemented.")
++   }
++   unregisterDataChangeListener(listener: DataChangeListener): void {
++     throw new Error("Method not implemented.")
++   }
++   private items: number[] = [] //  = Array.from({ length: 1000 }, (_, index) =&gt; index)
++   constructor() {
++     for(let i=0; i&lt; 1000; i++) {
++       this.items.push(i)
++     }
++   }
++   public getData(index: number): number {
++     return this.items[index]
++   }
++   public totalCount(): number {
++     return this.items.length
++   }
++ }
+  @Entry
+  @Component
+  struct MyComponent {
+-   private items: number[] = Array.from({ length: 1000 }, (_, index) =&gt; index)
++   private dataSource: MyDataSource = new MyDataSource()
+    build() {
+      List() {
+-       ForEach(this.items, (item: number) =&gt; {
+?                    ^  --
++       LazyForEach(this.dataSource, (item: number) =&gt; {
+?       ++++             ^^ ++++++
+          ListItem() {
+            Text(`Item: ${item}`)
+          }
+        })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5852,6 +7848,43 @@
 5. **数据源的直接实例化**:
    - 在修复代码中，`MyStringDataSource` 被实例化为 `this.dataSource`，而在问题代码中，数据项是直接在组件内部定义的。
 在整体结构上，修复代码通过引入数据源类和接口使得数据处理更加模块化和可扩展，同时优化了性能（使用 `LazyForEach`）。这些变更使得代码更加面向对象，并提供了更清晰的数据访问方式。</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>+ export class MyStringDataSource implements IDataSource {
++   registerDataChangeListener(listener: DataChangeListener): void {
++     throw new Error("Method not implemented.")
++   }
++   unregisterDataChangeListener(listener: DataChangeListener): void {
++     throw new Error("Method not implemented.")
++   }
++   private items: string[] = ["Apple", "Banana", "Cherry", "Date"]
++   public getData(index: number): string {
++     return this.items[index]
++   }
++   public totalCount(): number {
++     return this.items.length
++   }
++ }
+  @Entry
+  @Component
+  struct MyComponent {
+-   private items: string[] = ["Apple", "Banana", "Cherry", "Date"]
++   private dataSource: MyStringDataSource = new MyStringDataSource()
+    build() {
+      List() {
+-       ForEach(this.items, (item: string) =&gt; {
+?                    ^  --
++       LazyForEach(this.dataSource, (item: string) =&gt; {
+?       ++++             ^^ ++++++
+          ListItem() {
+            Text(item)
+          }
+        })
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -6000,6 +8033,105 @@
 总结来说，修复代码样例通过引入状态管理和可重用组件，使得代码更清晰、模块化、易于维护和提升性能。</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import { MyDataSource } from './MyDataSource';
+  import { GoodItems } from './data/DataEntry';
++ @Reusable
++ @Component
++ struct GoodItemComponent {
++   @State introduce: string = ''
++   @State price: string = ''
++   @State numb: string = ''
++   aboutToReuse(params: Record&lt;string, ESObject&gt;) {
++     this.introduce = params.introduce
++     this.price = params.price
++     this.numb = params.numb
++   }
++   build() {
++     Column() {
++       Text(this.introduce)
++         .fontSize(14)
++         .padding({ left: 5, right: 5 })
++         .margin({ top: 5 })
++       Row() {
++         Text('￥')
++           .fontSize(10)
++           .fontColor(Color.Red)
++           .baselineOffset(-4)
++         Text(this.price)
++           .fontSize(16)
++           .fontColor(Color.Red)
++         Text(this.numb)
++           .fontSize(10)
++           .fontColor(Color.Gray)
++           .baselineOffset(-4)
++           .margin({ left: 5 })
++       }
++       .width('100%')
++       .justifyContent(FlexAlign.SpaceBetween)
++       .padding({ left: 5, right: 5 })
++       .margin({ top: 15 })
++     }
++   }
++ }
+  @Entry
+  @Component
+  struct MyComponent{
+    private data: MyDataSource = new MyDataSource();
+    build() {
+      Column() {
+-       LazyForEach(this.data, (item: GoodItems) =&gt; {
++       LazyForEach(this.data, (item: GoodItems, index) =&gt; {
+?                                              +++++++
+          GridItem() {
+-           Column() {
++           GoodItemComponent({
+-             Text(item.introduce)
+?             ^ ^^^              ^
++             introduce: item.introduce,
+?             ^^^^^^^^ ^^              ^
+-               .fontSize(14)
+-               .padding({ left: 5, right: 5 })
+-               .margin({ top: 5 })
+-             Row() {
+-               Text('￥')
+-                 .fontSize(10)
+-                 .fontColor(Color.Red)
+-                 .baselineOffset(-4)
+-               Text(item.price)
+?              ------          ^
++             price: item.price,
+?             ++++++           ^
+-                 .fontSize(16)
+-                 .fontColor(Color.Red)
+-               Text(item.numb)
+?              ------         ^
++             numb: item.numb,
+?             +++++          ^
++           }).reuseId(item.numb)
+-                 .fontSize(10)
+-                 .fontColor(Color.Gray)
+-                 .baselineOffset(-4)
+-                 .margin({ left: 5 })
+-             }
+-             .width('100%')
+-             .justifyContent(FlexAlign.SpaceBetween)
+-             .padding({ left: 5, right: 5 })
+-             .margin({ top: 15 })
+-           }
+-           .borderRadius(10)
+-           .backgroundColor(Color.White)
+-           .clip(true)
+-           .width('100%')
+-           .height(290)
+          }
+        }, (item: GoodItems) =&gt; item.index)
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6134,6 +8266,109 @@
 总结来说，修复代码样例通过采取组件化的设计模式，提升了可维护性、可复用性和清晰度，并实现了一个更为规范的状态管理方式。</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>- List({ space: 10, initialIndex: 0, scroller: this.scroller }) {
+-           LazyForEach(this.listValue, (item) =&gt; {
+-             ListItem() {
+-               Column() {
++ @Reusable
++ @Component
++ struct ListItemComponent {
++   @State item: string = ''
++   @State listData: string[] = []
++   build() {
++     Column() {
+-                 Text('     ' + item)
+? ----------
++       Text('     ' + this.item)
+?                      +++++
+-                   .height(30)
+? ----------
++         .height(30)
++         .fontSize(16)
++         .width('100%')
++         .textAlign(TextAlign.Start)
++       // 这里使用一个内部 ForEach 遍历 listData
++       ForEach(this.listData, (ele: string) =&gt; {
++         if (ele.substr(0, 1) === this.item.toUpperCase() || ele.substr(0, 1) === this.item.toLowerCase()) {
++           Text('' + ele)
+-                   .fontSize(16)
+? ------
++             .fontSize(16)
+-                   .width('100%')
+? ------
++             .width('100%')
+-                   .textAlign(TextAlign.Start)
+-                 Column() {
+-                   ForEach(listData, (ele) =&gt; {
+-                     if (ele.substr(0, 1) == item.toUpperCase() || ele.substr(0, 1) == item.toLowerCase()) {
+-                       Text('' + ele)
+-                         .fontSize(16)
+-                         .width('100%')
+-                         .textAlign(TextAlign.Center)
+? ------------
++             .textAlign(TextAlign.Center)
+-                         .margin({ top: 5, bottom: 5 })
+? ------------
++             .margin({ top: 5, bottom: 5 })
+-                         .height(72)
+? ------------
++             .height(72)
+-                         .borderRadius(24)
+? ------------
++             .borderRadius(24)
+-                         .backgroundColor('#ffffff')
+? ------------
++             .backgroundColor('#ffffff')
+-                     }
+-                   })
+-                 }
+-               }
+-             }
+-             .editable(true)
+-           }, item =&gt; item)
+          }
++       })
++     }
++   }
++ }
++ class FruitValue implements IDataSource {
++   public fruit: string[] = ["A", "B", "C", "D"]
++   totalCount(): number {
++     return this.fruit.length
++   }
++   getData(index: number): string {
++     return this.fruit[index]
++   }
++   registerDataChangeListener(listener: DataChangeListener): void {
++     throw new Error('Method not implemented.')
++   }
++   unregisterDataChangeListener(listener: DataChangeListener): void {
++     throw new Error('Method not implemented.')
++   }
++ }
++ @Entry
++ @Component
++ struct MyComponent {
++   private listValue: FruitValue = new FruitValue()
++   private listData: string[] = ["Apple", "Avocado", "Banana", "Blueberry", "Cherry", "Date"]
++   build() {
++     List() {
++       LazyForEach(this.listValue, (item: string) =&gt; {
++         ListItem() {
++           // 使用 reusable component 传递 item 和 listData
++           ListItemComponent({
++             item: item,
++             listData: this.listData
++           })
++         }
++       }, (item: string) =&gt; item)
++     }
++   }
++ }</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6228,6 +8463,71 @@
 5. **起始和结束列的处理**：
    - 在修复代码中设置 `AlbumGridItemComponent` 的过程更为灵活，但没有显式地显示起始和结束列设置（如 `.columnStart(0).columnEnd(1)`）的处理，假定利用组件内部逻辑来设置，这也为意图上提供了一定的提升。
 综上，修复代码样例引入组件化、状态管理、简化逻辑、封装功能等多种改进，使得代码更具可维护性、可读性和重用性。</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>- Grid(this.scroller) {
++ @Reusable
++ @Component
++ struct AlbumGridItemComponent {
++   @State item: AlbumDataItem = new AlbumDataItem("1", 0, "", 0, "", 0, 0)
++   @State isBigCard: boolean = false
++   build() {
++     GridItem() {
++       AlbumSelectGridItemNewStyle({
++         item: this.item,
++         isBigCard: this.isBigCard,
++       })
++     }
++   }
++ }
+-           LazyForEach(this.albumsDataSource, (item: LazyItem&lt;AlbumDataItem&gt;): void =&gt; {
++ Grid(this.scroller) {          LazyForEach(this.albumsDataSource, (item: LazyItem&lt;AlbumDataItem&gt;): void =&gt; {
+? +++++++++++++++++++++
+-             if ((item != undefined &amp;&amp; item != null) &amp;&amp; (item.get() != undefined &amp;&amp; item.get() != null)) {
++             if (item &amp;&amp; item.get()) {
+-               if (item.index === 0){
++               if (item.index === 0) {
+?                                    +
++                 // 处理第一个专辑项
+-                 GridItem() {
+?                          --
++                 AlbumGridItemComponent({
+?                 +++++        +++++++++
+-                   AlbumSelectGridItemNewStyle({
+-                     item: item.get(),
+? --
++                   item: item.get(),
+-                     isBigCard: true,
+? --
++                   isBigCard: true,
+-                   })
+-                 }.columnStart(0).columnEnd(1)
+-               } else if (item != null) {
++                 }); // 设置网格的起始和结束列
++               } else {
++                 // 处理普通的专辑项
+-                 GridItem() {
+?                          --
++                 AlbumGridItemComponent({
+?                 +++++        +++++++++
+-                   AlbumSelectGridItemNewStyle({
+-                     item: item.get(),
+? --
++                   item: item.get(),
+-                     isBigCard: false,
+? --
++                   isBigCard: false,
+-                   })
+-                 }
++                 });
+?                  ++
+                }
+              }
+            }, (item: LazyItem&lt;AlbumDataItem&gt;): string =&gt; (item != undefined &amp;&amp; item != null) &amp;&amp; (item.get() != undefined &amp;&amp; item.get() != null) ?
+              item.getHashCode() : JSON.stringify(item))
+          }</t>
         </is>
       </c>
     </row>
@@ -6348,6 +8648,68 @@
 这些差异表明修复代码通过使用更好的组件设计和状态管理，使得代码更可读、可维护和灵活，同时增强了功能性和用户体验。</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>+ @Reusable
++ @Component
++ struct ImageGridItem {
++   @State lazyItem: LazyItem&lt;UserFileDataItem&gt; = new LazyItem&lt;UserFileDataItem&gt;(
++     new UserFileDataItem("initial_selection", ["arg1", "arg2"], "device123", 0), // 创建 UserFileDataItem 实例
++     0
++   );
++   @State mediaItem: UserFileDataItem | undefined = undefined; // 初始化为 undefined
++   @State pageName: string = Constants.PHOTO_TRANSITION_ALBUM; // 直接使用常量初始化
++   @State isSelectUpperLimited: boolean = false; // 设置初始值为 false
++   constructor(lazyItem: LazyItem&lt;UserFileDataItem&gt;, pageName?: string, isSelectUpperLimited?: boolean) {
++     super()
++     // 使用 defaults 处理可选参数
++     this.lazyItem = lazyItem;
++     this.mediaItem = lazyItem.item; // 从 lazyItem 初始化 mediaItem
++     // 如果提供了，才使用来自参数的 pageName 和 isSelectUpperLimited
++     if (pageName) {
++       this.pageName = pageName;
++     }
++     if (isSelectUpperLimited !== undefined) {
++       this.isSelectUpperLimited = isSelectUpperLimited;
++     }
++   }
++   build() {
++     if (this.lazyItem &amp;&amp; this.mediaItem) {
++       ImageGridItemComponent({
++         lazyItem: this.lazyItem,
++         mediaItem: this.mediaItem,
++         pageName: Constants.PHOTO_TRANSITION_ALBUM,
++         isSelectUpperLimited: $isSelectUpperLimited
++       })
++     }
++   }
++ }
+  Grid(this.scroller) {
+              LazyForEach(this.groupDataSource, (item: LazyItem&lt;UserFileDataItem&gt;): void =&gt; {
+                GridItem() {
+-                 ImageGridItemComponent({
+?                              --------- ^
++                 ImageGridItem()
+?                               ^
+-                   lazyItem: item,
+-                   mediaItem: item.get(),
+-                   pageName: Constants.PHOTO_TRANSITION_ALBUM,
+-                   isSelectUpperLimited: $isSelectUpperLimited
+-                 })
+                }
+                .aspectRatio(1)
+                .columnStart(item.get().index % this.gridRowCount)
+                .columnEnd(item.get().index % this.gridRowCount)
+              }, (item: LazyItem&lt;AlbumDataItem&gt;): string =&gt; item.getHashCode())
+            }
++           .columnsTemplate('1fr '.repeat(this.gridRowCount))
++           .columnsGap(Constants.GRID_GUTTER)
++           .rowsGap(Constants.GRID_GUTTER)
++           .cachedCount(Constants.GRID_CACHE_ROW_COUNT)
++           GridScrollBar({ scroller: this.scroller, isHideScrollBar: $isHideScrollBar });
++         }</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6482,6 +8844,60 @@
 2. **其他代码结构**：
    - 除了加上 `@Reuse` 注解外，修复代码样例与问题代码样例在其他方面没有显著变化，组件的逻辑、样式、布局等均保持一致。
 整体来看，修复主要是通过引入 `@Reuse` 注解来优化 `FileListItemComponent` 的性能。</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LazyForEach(this.fileList, (listItem: fileAccess.FileInfo) =&gt; {
+              ListItem() {
+                FileListItemComponent({
+                  fileListItem: listItem,
+                  itemFileList: $fileList,
+                  itemShowDeleteButton: $showDeleteButton,
+                  itemIsNoFile: $isNoFile
+                })
+              }
+            }, (listItem: fileAccess.FileInfo) =&gt; listItem.fileName)
++ @Reuse
+  @Component
+  struct FileListItemComponent {
+    @Link itemFileList: DocumentDataSource;
+    @Link itemShowDeleteButton: boolean;
+    @Link itemIsNoFile: boolean;
+    private fileListItem: fileAccess.FileInfo = {} as fileAccess.FileInfo;
+    private itemClickFunction: (fileAsset: fileAccess.FileInfo) =&gt; void = () =&gt; {
+      prompt.showToast({
+        duration: ONE_SECOND,
+        message: $r('app.string.not_supported_tip')
+      })
+    }
+    @Styles
+    itemPressedStyles() {
+      .backgroundColor($r('app.color.item_pressed'))
+      .borderRadius(10)
+    }
+    build() {
+      Column() {
+        Row() {
+          Image($r('app.media.default_document'))
+            .objectFit(ImageFit.Fill)
+            .width(40)
+            .height(40)
+            .margin({ left: 20 })
+          Column() {
+            Text(this.fileListItem.fileName)
+              .maxLines(1)
+              .width('75%')
+              .textOverflow({ overflow: TextOverflow.Ellipsis })
+              .fontSize(16)
+              .fontColor($r('app.color.black'))
+            Text(this.fileListItem.mtime + ' - ' + this.fileListItem.size + 'B')
+              .fontSize(12)
+              .margin({ top: 5 })
+              .fontColor($r('app.color.font_gray'))
+          }
+          .margin({ left: 10 })
+          .alignItems(HorizontalAlign.Start)</t>
         </is>
       </c>
     </row>
@@ -6635,6 +9051,113 @@
 通过以上的变化，修复的代码样例不仅解决了问题代码中的复杂性和冗余，同时也增强了代码的可用性和可维护性。</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>- LazyForEach(this.data, item =&gt; {
++         LazyForEach(this.data, item =&gt; {
+? ++++++++
+            GridItem() {
+-             Column() {
++             ProductGridItemComponent({
+-               Image(this.productData[item % 14].uri)
+?               ^^^^^^                               ^
++               uri: this.productData[item % 14].uri,
+?               ^^^^^                               ^
+-                 .width('100%')
+-                 .height('40%')
+-                 .objectFit(ImageFit.Contain)
+-                 .margin({ bottom: 40 })
+-               Text(this.productData[item % 14].title)
+?               ^ ^^^                                 ^
++               title: this.productData[item % 14].title,
+?               ^^^^ ^^                                 ^
+-                 .fontSize(16 * this.ratio)
+-                 .fontWeight(600)
+-                 .margin({ bottom: 10, left: 10 })
+-               Row() {
+-                 Text(this.productData[item % 14].labels)
+?                ------                                  ^
++               labels: this.productData[item % 14].labels,
+?               +++++++                                   ^
++               price: item + 1,
++               ratio: this.ratio // 你可能需要传递这个比例计算
+-                   .fontSize(10 * this.ratio)
+-                   .border({ width: 1, color: '#FA808080' })
+-                   .margin({ bottom: 2, left: 10 })
+-                   .padding(2)
+-               }
+-               .margin({ bottom: 2 })
+-               Text(￥${item + 1})
+-                 .fontSize(16 * this.ratio)
+-                 .fontColor(Color.Red)
+-                 .margin({ left: 10 })
+-             }
++             })
+?              +
+-             .alignItems(HorizontalAlign.Start)
+            }
+            .width('95%')
+            .height(300)
+            .border({ width: 1, color: '#70808080', radius: 10 })
+            .margin({ top: 3, bottom: 3 })
+            .backgroundColor(Color.White)
+          }, item =&gt; item.toString())
+        }
++       .columnsTemplate('1fr 1fr')
++       .padding({ bottom: 60 })
++       .onScrollIndex((e) =&gt; {
++         this.GridIndex = Number(e)
++       })
++     }
++     .width('100%')
++     .backgroundColor('#10000000')
++   }
++ }
++ @Reusable
++ @Component
++ struct ProductGridItemComponent {
++   @State uri: string = "";
++   @State title: string = "";
++   @State labels: string = "";
++   @State price: number = 0;
++   @State ratio: number = 0;
++   constructor(uri: string, title: string, labels: string, price: number, ratio: number) {
++     super()
++     this.uri = uri;
++     this.title = title;
++     this.labels = labels;
++     this.price = price;
++     this.ratio = ratio;
++   }
++   build() {
++     Column() {
++       Image(this.uri)
++         .width('100%')
++         .height('40%')
++         .objectFit(ImageFit.Contain)
++         .margin({ bottom: 40 });
++       Text(this.title)
++         .fontSize(16 * this.ratio)
++         .fontWeight(600)
++         .margin({ bottom: 10, left: 10 });
++       Row() {
++         Text(this.labels)
++           .fontSize(10 * this.ratio)
++           .border({ width: 1, color: '#FA808080' })
++           .margin({ bottom: 2, left: 10 })
++           .padding(2);
++       }
++       .margin({ bottom: 2 });
++       Text(`￥${this.price}`)
++         .fontSize(16 * this.ratio)
++         .fontColor(Color.Red)
++         .margin({ left: 10 });
++     }
++     .alignItems(HorizontalAlign.Start);
++   }
++ }</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6686,6 +9209,27 @@
    - 修复代码的循环体结构在逻辑上保持一致，但因状态的存储方式不同，可能对循环的执行结果产生影响，尤其是在状态可能动态变化的情况下。
 总结：
 - 修复代码通过引入局部变量 `state`，使得循环的条件判断更加稳定，避免了因外部状态变化导致的潜在逻辑错误。</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>+ let state = this.hotspotLoopState
+-     for ( this.openHotspotNumber ; this.openHotspotNumber &lt; this.testNumbers ; this.openHotspotNumber ++ ) {
+? ----
++ for ( this.openHotspotNumber ; this.openHotspotNumber &lt; this.testNumbers ; this.openHotspotNumber ++ ) {
+-       if ( !this.hotspotLoopState ) {
++   if ( !state ) {
+-         console.log(TAG , "测试结束------------")
+? ----
++     console.log(TAG , "测试结束------------")
+-         break;
+? ----
++     break;
+-       } else {
+? ----
++   } else {
++   }
++ }</t>
         </is>
       </c>
     </row>
@@ -6781,6 +9325,42 @@
    - 在修复代码样例中，循环内调用 `hilog.info` 的参数是 `logMessage`。这样做可以确保在循环执行期间 `this.message` 的值不会发生变化，从而保证打印的日志是正确的。
 总结：
 修复代码的关键在于引入了一个局部变量 `logMessage`，以保存 `this.message` 的值，从而避免在循环中对 `this.message` 的直接引用，这可能会导致不一致的日志输出。</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import hilog from '@ohos.hilog'
+  @Entry
+  @Component
+  struct MyComponent{
+    @State message: string = '';
+    build() {
+      Column() {
+        Button('点击打印日志')
+          .onClick(() =&gt; {
+            this.message = 'click';
++           let logMessage: string = this.message;
+            for (let i = 0; i &lt; 10; i++) {
+-             hilog.info(0x0000, 'TAG', '%{public}s', this.message);
+?                                                     ^^^^^^
++             hilog.info(0x0000, 'TAG', '%{public}s', logMessage);
+?                                                     ^^^^
+            }
+          })
+          .width('90%')
+          .backgroundColor(Color.Blue)
+          .fontColor(Color.White)
+          .margin({
+            top: 10
+          })
+      }
+      .justifyContent(FlexAlign.Start)
+      .alignItems(HorizontalAlign.Center)
+      .margin({
+        top: 15
+      })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -6979,6 +9559,170 @@
 总的来说，修复代码样例主要进行了变量作用域管理的优化，通过引入局部变量减少对对象属性的频繁访问，使得代码的性能和可读性得到了提升。同时，修复后的代码依然保持了原逻辑的完整性。</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>+     let hotspotLoopState = this.hotspotLoopState
++     let openHotspotNumber = this.openHotspotNumber
++     let open_StartTime = this.open_StartTime
++     let open_EndTime = this.open_EndTime
++     let open_SpendTime = this.open_SpendTime
++     let openSuccessNumber = this.openSuccessNumber
++     let closeHotspotNumber = this.closeHotspotNumber
++     let close_StartTime = this.close_StartTime
++     let close_SpendTime = this.close_SpendTime
++     let close_EndTime = this.close_EndTime
++     let hotspotMessage = this.hotspotMessage
++     let closeSuccessNumber = this.closeSuccessNumber
++     let closeFailNumber = this.closeFailNumber
++     let openFailNumber = this.openFailNumber
+- for ( this.openHotspotNumber ; this.openHotspotNumber &lt; this.testNumbers ; this.openHotspotNumber ++ ) {
++     for ( this.openHotspotNumber ; this.openHotspotNumber &lt; this.testNumbers ; this.openHotspotNumber ++ ) {
+? ++++
+-       if ( !this.hotspotLoopState ) {
+?             -----
++       if ( !hotspotLoopState ) {
+          console.log(TAG , "测试结束------------")
+          break;
+        } else {
+          let wifiState = wifiManager.isWifiActive()
+          if ( wifiState ) {
+            wifi.disableWifi()
+            console.log(TAG , "wifi当前已使能，已经去使能，正常开始测试------")
+          } else {
+            console.log(TAG , "wifi当前未使能，正常开始测试------")
+          }
+          await sleep(3)
+          funcMessage = wifi.enableHotspot()
+          // 打时间戳
+          this.open_StartTime = new Date().getTime()
+-         console.log(TAG , "第" + (this.openHotspotNumber + 1) + "次热点使能-----")
+?                                  -----
++         console.log(TAG , "第" + (openHotspotNumber + 1) + "次热点使能-----")
+-         console.log(TAG , "第" + (this.openHotspotNumber + 1) + "次热点使能开始时间: " + this.open_StartTime + "ms")
+?                                  -----                                         -----
++         console.log(TAG , "第" + (openHotspotNumber + 1) + "次热点使能开始时间: " + open_StartTime + "ms")
+-         this.hotspotMessageLog += "第" + (this.openHotspotNumber + 1) + "次热点使能结果：" + funcMessage + "\n"
+?                                          -----
++         this.hotspotMessageLog += "第" + (openHotspotNumber + 1) + "次热点使能结果：" + funcMessage + "\n"
+-         console.log(TAG , "第" + (this.openHotspotNumber + 1) + "次热点使能结果：" + funcMessage)
+?                                  -----
++         console.log(TAG , "第" + (openHotspotNumber + 1) + "次热点使能结果：" + funcMessage)
+          await sleep(10)
+          this.hotspotMessage = AppStorage.get("hotspotMessage") ! //非空断言操作符
+          // prompt.showToast( { message : funcMessage } )
+-         if ( this.hotspotMessage == "active" ) {
+?              -----
++         if ( hotspotMessage == "active" ) {
+-           this.open_SpendTime = this.open_EndTime - this.open_StartTime
+?           -----                 -----               -----
++           open_SpendTime = open_EndTime - open_StartTime
+-           this.hotspotMessageLog += "第" + (this.openHotspotNumber + 1) + "次热点使能耗时: " + this.open_SpendTime + "ms" + "\n"
+?                                            -----                                       -----
++           this.hotspotMessageLog += "第" + (openHotspotNumber + 1) + "次热点使能耗时: " + open_SpendTime + "ms" + "\n"
+-           console.log(TAG , "第" + (this.openHotspotNumber + 1) + "次热点使能耗时: " + this.open_SpendTime + "ms")
+?                                    -----                                       -----
++           console.log(TAG , "第" + (openHotspotNumber + 1) + "次热点使能耗时: " + open_SpendTime + "ms")
+-           this.openSuccessNumber = this.openSuccessNumber + 1
+?           -----                    -----
++           openSuccessNumber = openSuccessNumber + 1
+-           this.hotspotMessageLog += "热点使能成功的次数：" + this.openSuccessNumber + "\n"
+?                                                    -----
++           this.hotspotMessageLog += "热点使能成功的次数：" + openSuccessNumber + "\n"
+-           console.log(TAG , "热点使能成功的次数：" + this.openSuccessNumber)
+?                                            -----
++           console.log(TAG , "热点使能成功的次数：" + openSuccessNumber)
+            funcMessage = wifi.disableHotspot()
+-           this.closeHotspotNumber = this.closeHotspotNumber + 1
+?           -----                     -----
++           closeHotspotNumber = closeHotspotNumber + 1
+-           this.close_StartTime = new Date().getTime()
+?           -----
++           close_StartTime = new Date().getTime()
+-           console.log(TAG , "第" + this.closeHotspotNumber + "次热点去使能-----")
+?                                   -----
++           console.log(TAG , "第" + closeHotspotNumber + "次热点去使能-----")
+-           console.log(TAG , "第" + this.closeHotspotNumber + "次热点去使能开始时间: " + this.close_StartTime + "ms")
+?                                   -----                                      -----
++           console.log(TAG , "第" + closeHotspotNumber + "次热点去使能开始时间: " + close_StartTime + "ms")
+-           this.hotspotMessageLog += "第" + this.closeHotspotNumber + "次热点去使能结果：" + funcMessage + "\n"
+?                                           -----
++           this.hotspotMessageLog += "第" + closeHotspotNumber + "次热点去使能结果：" + funcMessage + "\n"
+-           console.log(TAG , "第" + this.closeHotspotNumber + "次热点去使能结果：" + funcMessage)
+?                                   -----
++           console.log(TAG , "第" + closeHotspotNumber + "次热点去使能结果：" + funcMessage)
+-           console.log(TAG , "closeHotspotNumber: " + this.closeHotspotNumber)
+?                                                      -----
++           console.log(TAG , "closeHotspotNumber: " + closeHotspotNumber)
+            await sleep(10)
+-           this.hotspotMessage = AppStorage.get("hotspotMessage") ! //非空断言操作符
+?           -----
++           hotspotMessage = AppStorage.get("hotspotMessage") ! //非空断言操作符
+-           if ( this.hotspotMessage == "inactive" ) {
+?                -----
++           if ( hotspotMessage == "inactive" ) {
+-             this.close_SpendTime = this.close_EndTime - this.close_StartTime
+?             -----                  -----                -----
++             close_SpendTime = close_EndTime - close_StartTime
+-             this.hotspotMessageLog += "第" + this.closeHotspotNumber + "次热点去使能耗时: " + this.close_SpendTime + "ms" + "\n"
+?                                             -----                                    -----
++             this.hotspotMessageLog += "第" + closeHotspotNumber + "次热点去使能耗时: " + close_SpendTime + "ms" + "\n"
+-             console.log(TAG , "第" + this.closeHotspotNumber + "次热点去使能耗时: " + this.close_SpendTime + "ms")
+?                                     -----                                    -----
++             console.log(TAG , "第" + closeHotspotNumber + "次热点去使能耗时: " + close_SpendTime + "ms")
+-             this.closeSuccessNumber = this.closeSuccessNumber + 1
+?             -----                     -----
++             closeSuccessNumber = closeSuccessNumber + 1
+-             this.hotspotMessageLog += "热点去使能成功的次数：" + this.closeSuccessNumber + "\n"
+?                                                       -----
++             this.hotspotMessageLog += "热点去使能成功的次数：" + closeSuccessNumber + "\n"
+-             console.log(TAG , "热点去使能成功的次数：" + this.closeSuccessNumber)
+?                                               -----
++             console.log(TAG , "热点去使能成功的次数：" + closeSuccessNumber)
+              await sleep(7)
+            } else {
+-             this.closeFailNumber = this.closeFailNumber + 1
+?             -----                  -----
++             closeFailNumber = closeFailNumber + 1
+-             console.log(TAG , "热点去使能失败的次数：" + this.closeFailNumber)
+?                                               -----
++             console.log(TAG , "热点去使能失败的次数：" + closeFailNumber)
+-             console.log(TAG , "第" + this.closeHotspotNumber + "次热点去使能失败")
+?                                     -----
++             console.log(TAG , "第" + closeHotspotNumber + "次热点去使能失败")
+            }
+          } else if ( this.hotspotMessage == "inactive" ) {
+-           this.openFailNumber = this.openFailNumber + 1
+?           -----                 -----
++           openFailNumber = openFailNumber + 1
+-           console.log(TAG , "热点使能失败的次数：" + this.openFailNumber)
+?                                            -----
++           console.log(TAG , "热点使能失败的次数：" + openFailNumber)
+-           console.log(TAG , "第" + (this.openHotspotNumber + 1) + "次热点使能失败")
+?                                    -----
++           console.log(TAG , "第" + (openHotspotNumber + 1) + "次热点使能失败")
+          } else {
+-           console.log("第" + (this.openHotspotNumber + 1) + "次开热点后状态不清楚");
+?                              -----
++           console.log("第" + (openHotspotNumber + 1) + "次开热点后状态不清楚");
+          }
+        }
+      }
++     this.hotspotLoopState = hotspotLoopState
++     this.openHotspotNumber = openHotspotNumber
++     this.open_StartTime = open_StartTime
++     this.open_EndTime = open_EndTime
++     this.open_SpendTime = open_SpendTime
++     this.openSuccessNumber = openSuccessNumber
++     this.closeHotspotNumber = closeHotspotNumber
++     this.close_StartTime = close_StartTime
++     this.close_SpendTime = close_SpendTime
++     this.close_EndTime = close_EndTime
++     this.hotspotMessage = hotspotMessage
++     this.closeSuccessNumber = closeSuccessNumber
++     this.closeFailNumber = closeFailNumber
++     this.openFailNumber = openFailNumber</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7036,6 +9780,27 @@
 3. **逻辑上的先后顺序**：
    - 通过在修复代码中引入一个局部变量，可以在循环中维持独立状态，避免了潜在的副作用，确保 `this.currentIndex` 在循环体执行期间不被直接修改，从而可能带来的不可预测行为。
 总结一下，修复代码样例通过引入局部变量 `currentIndex`，使得 `this.currentIndex` 的值不再在循环中被直接修改，从而提高了代码的可读性和可维护性。</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>+ let currentIndex = this.currentIndex
+- for ( let indexNumber = 1 ; indexNumber &lt; 101 ; indexNumber ++ ) {
++           for ( let indexNumber = 1 ; indexNumber &lt; 101 ; indexNumber ++ ) {
+? ++++++++++
+              let message: string = apiItem.api!();
+              apiItem.result = message;
+              prompt.showToast({ message : message });
+-             this.currentIndex += 1;
+?             -----
++             currentIndex += 1;
+-             this.changeIndex = this.currentIndex;
+?                                -----
++             this.changeIndex = currentIndex;
+              AppStorage.setOrCreate('stressNumber' , indexNumber);
+              console.log(TAG , apiItem.method + "indexNumber is ------: " + indexNumber);
+            }
++           this.currentIndex = currentIndex</t>
         </is>
       </c>
     </row>
@@ -7288,6 +10053,116 @@
 - 修复代码的主要改进是在渲染列表项时生成唯一 `key` 的方式。由此改善了性能表现，尤其是在处理较大数据时，避免了使用 `JSON.stringify` 的高开销。</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import { MyDataSource } from './MyDataSource';
+  // 此处为复用的自定义组件
+  @Reusable
+  @Component
+  struct ChildComponent {
+    @State desc: string = '';
+    @State sum: number = 0;
+    @State avg: number = 0;
+    aboutToReuse(params: Record&lt;string, Object&gt;): void {
+      this.desc = params.desc as string;
+      this.sum = params.sum as number;
+      this.avg = params.avg as number;
+    }
+    build() {
+      Column() {
+        Text('子组件' + this.desc)
+          .fontSize(30)
+          .fontWeight(30)
+        Text('结果' + this.sum)
+          .fontSize(30)
+          .fontWeight(30)
+        Text('平均值' + this.avg)
+          .fontSize(30)
+          .fontWeight(30)
+      }
+    }
+  }
+  class Item {
+    advertInfos: Model[] = []
+    productPrice: PriceInfo[] = []
+    addresses: string[] = []
+    id: string = ''
+  }
+  class Model {
+    pictureUrl: string = ""
+    name: string = ""
+    comments: string = ""
+    desc: string = ""
+    linkParam: string = ""
+    mcInfo: string = ""
+    label: string = ""
+    cgType: string = ""
+    constructor(pictureUrl: string, name: string, comments: string, desc: string, linkParam: string, mcInfo: string,
+      label: string, cgType: string) {
+      this.pictureUrl = pictureUrl;
+      this.name = name;
+      this.comments = comments;
+      this.desc = desc;
+      this.linkParam = linkParam;
+      this.mcInfo = mcInfo;
+      this.label = label;
+      this.cgType = cgType;
+    }
+  }
+  class PriceInfo {
+    price: number = 0;
+    level: number = 1;
+    constructor(price: number, level: number) {
+      this.price = price;
+      this.level = level;
+    }
+  }
+  @Entry
+  @Component
+  struct MyComponent {
+    private data: MyDataSource = new MyDataSource();
+    aboutToAppear(): void {
+      for (let index = 0; index &lt; 20; index++) {
+        let item = new Item()
+        for (let i = 0; i &lt; 1000; i++) {
+          item.advertInfos.push(new Model("Product A", "Product A", "Product A", "Product A", "Product A", "Product A", "Product A", "Product A"));
+          item.productPrice.push(new PriceInfo(1.99, 123456));
+          item.addresses.push("Beijing")
+        }
+        item.id = index.toString();
+        this.data.pushData(item.productPrice[0].price)
+      }
+    }
+    build() {
+      Column() {
+        Text('Use the time-consuming function `JSON.stringify (item)` to generate a key')
+          .fontSize(12)
+          .height('16')
+          .margin({
+            top: 5,
+            bottom: 10
+          })
+        List() {
+          LazyForEach(this.data, (item: Item) =&gt; {
+            ListItem() {
+              ChildComponent({ desc: item.id, sum: 0, avg: 0 })
+            }
+            .width('100%')
+            .height('10%')
+            .border({ width: 1 })
+            .borderStyle(BorderStyle.Dashed)
+-         }, (item: Item) =&gt; JSON.stringify(item))
+?                            ^ ----     --- ----
++         }, (item: Item) =&gt; item.id.toString())
+?                            ^^^^^^^^^^
+        }
+        .height('100%')
+        .width('100%')
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7338,6 +10213,21 @@
 2. **条件简化**：
    - 在修复的代码中，虽然保留了对 `item` 和 `item.get()` 的检查，但在返回值的选择上，变得更为简单和直接。使用了 `item.item.id` 作为默认值，提供了更明确的数据访问方式，而不是使用较为复杂的 `JSON.stringify`。
 总结来说，修复代码样例相对于问题代码样例的主要不同，在于它改变了对 `item` 处理的逻辑，从之前可能会引入复杂性和潜在性能问题的 `JSON.stringify(item)` 改为直接访问 `item.item.id`，让代码更清晰、可读性更高。</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Grid(this.scroller) {
+            LazyForEach(this.albumsDataSource, (item: LazyItem&lt;AlbumDataItem&gt;): void =&gt; {
+              if (item &amp;&amp; item.get()) {
+                Text()
+              }
+            }, (item: LazyItem&lt;AlbumDataItem&gt;): string =&gt; (item != undefined &amp;&amp; item != null) &amp;&amp; (item.get() != undefined &amp;&amp; item.get() != null) ?
+-             item.getHashCode() : JSON.stringify(item))
+?                                  ---------------     -
++             item.getHashCode() : item.item.id)
+?                                      ++++++++
+          }</t>
         </is>
       </c>
     </row>
@@ -7399,6 +10289,26 @@
    - 在问题代码样例中，如果 `listItem.displayName` 是复杂对象，则使用 `JSON.stringify` 可能会产生一个包含整个对象信息的字符串，而不仅仅是 `name` 属性。
    - 在修复代码样例中，直接访问 `name` 属性使得排序逻辑更加明确和直接，且避免了潜在的对象转字符串时的复杂性。
 综上所述，修复代码样例相对于问题代码样例的差异主要在于如何获取用于排序的值，修复后的版本直接获取了 `name` 属性，使得代码的意图更加清晰。</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LazyForEach(this.fileList, (listItem: userFileManager.FileAsset) =&gt; {
+              ListItem() {
+                FileListItemComponent({
+                  itemFileList: $fileList,
+                  fileListItem: listItem,
+                  itemClickFunction: this.itemClickFunction,
+                  uri: listItem.uri,
+                  itemShowDeleteButton: $showDeleteButton,
+                  itemIsNoFile: $isNoFile
+                })
+              }
+-           }, (listItem: userFileManager.FileAsset) =&gt; JSON.stringify(listItem.displayName))
+?                                                       ---------------                     -
++           }, (listItem: userFileManager.FileAsset) =&gt; listItem.displayName.name)
+?                                                                           +++++
+</t>
         </is>
       </c>
     </row>
@@ -7455,6 +10365,16 @@
 2. **潜在的性能和准确性的影响**：
    - 使用 `JSON.stringify` 可能导致性能问题，特别是当 `user` 对象很大时。而 `user.id.toString()` 则明确且往往更加高效，能够直接生成预期的唯一键。
 总结来说，修复代码相对于问题代码的关键改进是在生成唯一键的逻辑上，使用更简单、有效的 Id 字符串而不是整个对象的字符串表示。这种改变有助于提高性能和减少潜在的渲染错误。</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LazyForEach(this.userList, (user: User) =&gt; {
+    ListItem() {
+      UserComponent({ name: user.name, age: user.age });
+    }
+- }, (user: User) =&gt; JSON.stringify(user));
++ }, (user: User) =&gt; user.id.toString());</t>
         </is>
       </c>
     </row>
@@ -7514,6 +10434,16 @@
 总结：修复代码的主要差异在于第三个参数，从返回一个 JSON 字符串转变为返回 `product.id` 的字符串表示，这简化了代码的复杂性，并可能提高性能。</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LazyForEach(this.productList, (product: Product) =&gt; {
+    ListItem() {
+      ProductComponent({ productName: product.name });
+    }
+- }, (product: Product) =&gt; JSON.stringify({ id: product.id, name: product.name }));
++ }, (product: Product) =&gt; product.id.toString());</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7561,6 +10491,16 @@
 - 修复代码样例提升了代码效率和清晰度，专注于返回每个任务的唯一标识符，而不是序列化整个任务对象。</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LazyForEach(this.taskList, (task: Task) =&gt; {
+    ListItem() {
+      TaskComponent({ title: task.title });
+    }
+- }, (task: Task) =&gt; JSON.stringify(task));
++ }, (task: Task) =&gt; task.taskId.toString());</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7605,6 +10545,19 @@
    - **问题代码样例**使用的是 `JSON.stringify(notification.details)` 作为最后一个参数。这意味着它试图将 `notification.details` 对象序列化为字符串，可能导致某些复杂的对象结构在处理时产生问题。
    - **修复代码样例**则改为使用 `notification.id.toString()` 作为最后一个参数。这表示它将 `notification.id` 转换为字符串格式，通常是更简单、且更可靠的标识符，减少了潜在的错误。
 综上所述，主要的差异是最后一个参数的类型和处理方式的变化，从复杂的对象序列化变为简单的 ID 转换，可能使得代码在性能和稳定性上得到提升。</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LazyForEach(this.notificationList, (notification: Notification) =&gt; {
+    ListItem() {
+      NotificationComponent({ message: notification.message });
+    }
+- }, (notification: Notification) =&gt; JSON.stringify(notification.details));
+?                                    ---------------              ^ ^ ^^
++ }, (notification: Notification) =&gt; notification.id.toString());
+?                                                 + ^ ^^^^ ^^^
+</t>
         </is>
       </c>
     </row>
@@ -7665,6 +10618,22 @@
 总结而言，修复代码通过去掉了日志记录，从而使得代码更加简洁，但也失去了一些调试信息的记录能力。</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Home {
+    build() {
+      TextInput()
+        .onTextChange(() =&gt; {
+-         hilog.debug(5001, 'Home', 'onTextChange')
++         const TAG = 'onTextChange';
+        })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7723,6 +10692,22 @@
 总体来说，修复代码样例去掉了日志记录的功能，添加了一个常量定义，但并没有显示使用这个常量进行任何操作。</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct Dashboard {
+    build() {
+      ScrollView()
+        .onItemMove() =&gt; {
+-         hilog.info(6002, 'Dashboard', 'onScroll')
++         const LABEL = 'onScroll';
+        })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7781,6 +10766,22 @@
 总结来说，修复代码的修改专注于去掉了错误日志的记录，并引入了一个事件常量的定义，但未对事件处理逻辑进行其他更改。</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct UserInterface {
+    build() {
+      List()
+        .onItemMove(() =&gt; {
+-         hilog.error(7003, 'UserInterface', 'onItemMove')
++         const EVENT = 'onItemMove';
+        })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7833,6 +10834,22 @@
 1. **删除了日志记录行**：在问题代码样例中，使用了 `hilog.warn(8004, 'ControlPanel', 'onValueChange')` 来记录警告日志。而在修复代码样例中，这一行被删除了。
 2. **新增了常量定义**：在修复代码样例中，添加了一个常量 `const ACTION = 'onValueChange';`。这个常量的定义并未在问题代码样例中出现。
 总结：修复代码样例删除了日志记录的操作，并引入了一个常量定义，虽然常量 `ACTION` 在修复代码中定义，但并未在后续的代码逻辑中使用。</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct ControlPanel {
+    build() {
+      DatePicker()
+        .onDateChange(() =&gt; {
+-         hilog.warn(8004, 'ControlPanel', 'onValueChange')
++         const ACTION = 'onValueChange';
+        })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -7891,6 +10908,22 @@
    - 修复代码中引入了一个常量 `const STATUS = 'onChange';`，但并没有实际使用这个常量。
    - 这一常量的引入没有改变程序的逻辑或功能。
 总结来说，修复代码样例移除了日志记录功能，并增加了一个未使用的常量 `STATUS`。这可能是为了减少调试信息的输出，并可能为后续的代码扩展留出空间。</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct MainScreen {
+    build() {
+      Swipe()
+        .onChange(() =&gt; {
+-         hilog.debug(9005, 'MainScreen', 'onChange')
++         const STATUS = 'onChange';
+        })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -7972,6 +11005,35 @@
    - 该方法中调用了 `this.animateItem?.destroy()`，用于销毁动画实例（如果存在的话）。
    - `this.animateItem` 被设置为 `undefined`，以确保引用被清空。
 通过新增 `onDeactivate` 方法，修复代码实现了更好的资源管理，确保在组件不再需要时可以正确释放相关的动画资源。</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  @Entry
+  @Component
+  struct AnimationComponentFixed {
+    private renderContext: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private animateItem?: AnimationItem;
+    build() {
+      Canvas(this.renderContext)
+        .width(120)
+        .height(120)
+        .onReady(() =&gt; {
+          this.animateItem = lottie.loadAnimation({
+            container: this.renderContext,
+            renderer: 'canvas',
+            autoplay: true,
+            path: 'anim.json'
+          });
+        });
+    }
++   onDeactivate() {
++     this.animateItem?.destroy();
++     this.animateItem = undefined;
++   }
+  }</t>
         </is>
       </c>
     </row>
@@ -8078,6 +11140,39 @@
 总结：修复代码通过引入 `currentAnimation` 属性以及在组件消失时销毁动画实例，解决了可能存在的内存泄漏问题，从而提高了代码的健壮性和资源管理。</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  @Entry
+  @Component
+  struct FinishAnimation {
+    private animationCtx: CanvasRenderingContext2D = new CanvasRenderingContext2D();
++   private currentAnimation?: AnimationItem;
+    build() {
+      Canvas(this.animationCtx)
+        .width(160)
+        .height(160)
+        .onReady(() =&gt; {
+          // 无动画销毁
+          lottie.loadAnimation({
+            container: this.animationCtx,
+            renderer: 'svg',
+            loop: false,
+            autoplay: true,
+            path: 'finish_anim.json'
+          });
+-       });
+?         -
++       })
++       .onDisAppear(() =&gt; {
++         this.currentAnimation?.destroy();
++         this.currentAnimation = undefined;
++       })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8161,6 +11256,39 @@
 4. **安全访问动画实例**:
    - 修复代码使用可选链操作符 `?.` 来安全地调用 `destroy()` 方法，以防止在实例未定义时出现错误。这是一个良好的编程实践，但在问题代码中未实现。
 总结来说，修复代码增强了对动画实例的管理，确保在不需要时能够正确销毁动画，从而提高了资源管理的可靠性。</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  @Entry
+  @Component
+- struct PersistentAnimation {
++ struct PersistentAnimationFixed {
+?                           +++++
+    private animationCtx: CanvasRenderingContext2D = new CanvasRenderingContext2D();
++   private animationInstance?: AnimationItem;
+    build() {
+      Canvas(this.animationCtx)
+        .width(100)
+        .height(100)
+        .onReady(() =&gt; {
++         this.animationInstance = lottie.loadAnimation({
+-         // 页面隐藏时未执行销毁
+-         lottie.loadAnimation({
+            container: this.animationCtx,
+            renderer: 'canvas',
+            autoplay: true,
+            path: 'persistent.json'
+          });
+        });
+    }
++   onHidePage() {
++     this.animationInstance?.destroy();
++     this.animationInstance = undefined;
++   }
+  }</t>
         </is>
       </c>
     </row>
@@ -8249,6 +11377,44 @@
 这些改进使得修复后的代码在资源管理方面更加完善，确保了组件在生命周期结束时能够清理掉不再需要的动画，从而提高了代码的健壮性。</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  @Entry
+  @Component
+- struct MultipleAnimationsComponent {
++ struct MultipleAnimationsComponentFixed {
+?                                   +++++
+    private animationContext: CanvasRenderingContext2D = new CanvasRenderingContext2D();
++   private runningAnimations: AnimationItem[] = [];
+    build() {
+      Canvas(this.animationContext)
+        .width(200)
+        .height(200)
+        .onReady(() =&gt; {
+-         // 未销毁多余动画
+-         lottie.loadAnimation({
++         const loadedAnim = lottie.loadAnimation({
+?        +++++++++++++++++++
+            container: this.animationContext,
+            renderer: 'svg',
+            loop: true,
+            autoplay: true,
+            path: 'multi_anim.json'
+          });
++         this.runningAnimations.push(loadedAnim);
+-       });
+?         -
++       })
++       .onDisAppear(() =&gt; {
++         this.runningAnimations.forEach(anim =&gt; anim.destroy());
++         this.runningAnimations = [];
++       })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8332,6 +11498,39 @@
 总体来说，修复代码样例通过引入对动画实例的管理，实现了在页面隐藏时销毁动画的功能，避免了资源泄漏的问题，而问题代码样例中没有这部分逻辑。</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  import { AnimationItem } from '@ohos/lottie';
+  @Entry
+  @Component
+- struct LifecycleAnimation {
++ struct LifecycleAnimationFixed {
+?                          +++++
+    private animationSurface: CanvasRenderingContext2D = new CanvasRenderingContext2D();
++   private activeAnimation?: AnimationItem;
+    build() {
+      Canvas(this.animationSurface)
+        .width(150)
+        .height(150)
+        .onReady(() =&gt; {
++         this.activeAnimation = lottie.loadAnimation({
+-         // 没有销毁操作
+-         lottie.loadAnimation({
+            container: this.animationSurface,
+            renderer: 'html',
+            autoplay: true,
+            path: 'lifecycle.json'
+          });
+        });
+    }
++   onPageHide() {
++     this.activeAnimation?.destroy();
++     this.activeAnimation = undefined;
++   }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8388,6 +11587,27 @@
 - `max` 从 **180** 降低到 **60**</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  function initializeFrame() {
+    let syncConfig = {
+-     expected: 180,
+?               ^^
++     expected: 60,
+?               ^
+-     min: 180,
+?          ^^
++     min: 30,
+?          ^
+-     max: 180
+?          ^^
++     max: 60
+?          ^
+    };
+    frameManager.setSync(syncConfig);
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8442,6 +11662,27 @@
    - 问题代码样例中，`max` 的值为 `200`。
    - 修复代码样例中，`max` 的值更改为 `60`。
 总结来说，修复代码将 `frameRate` 的 `min`、`expected` 和 `max` 的值都降低，以使其更加适合于需求。问题代码的所有 `frameRate` 值都设置为 `200`，而修复代码将这些值修改为 `30`、`60` 和 `60`。</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  var config = {
+    frameRate: {
+-     min: 200,
+?          ^^
++     min: 30,
+?          ^
+-     expected: 200,
+?               ^^
++     expected: 60,
+?               ^
+-     max: 200
+?          ^ -
++     max: 60
+?          ^
+    }
+  };
+  display.setConfig(config);</t>
         </is>
       </c>
     </row>
@@ -8507,6 +11748,29 @@
 综合来看，修复代码样例中三个参数（expected、min 和 max）的值都被调整到了较低的水平，反映了对原代码中设定的不同标准或要求。</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Widget
+  class FrameWidget {
+    configure() {
+      setRates({
+-       expected: 120,
+?                 ^^
++       expected: 60,
+?                 ^
+-       min: 120,
+?            ^^
++       min: 30,
+?            ^
+-       max: 120
+?            ^^
++       max: 60
+?            ^
+      });
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8547,6 +11811,15 @@
    - 第二个参数从 `160` 降低到 `30`。
    - 第三个参数从 `160` 降低到 `60`。
 总结来看，修复代码通过将所有三个参数的值显著降低，以适应新的设置需求。这些更改可能是为了优化性能、降低资源消耗或适应其他设计考量。</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>- const settings = new FrameSettings(160, 160, 160);
+?                                    -    ^^   -
++ const settings = new FrameSettings(60, 30, 60);
+?                                        ^
+  frameManager.applySettings(settings);</t>
         </is>
       </c>
     </row>
@@ -8612,6 +11885,29 @@
 总结：修复代码将视频配置中的最小、期望和最大帧率都降低至 30 和 60 的合适范围，这可能是为了确保视频播放更流畅，符合一般视频播放的标准帧率。</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  function processFrame() {
+    videoConfig = {
+      fps: {
+-       min: 210,
+?            ^^
++       min: 30,
+?            ^
+-       expected: 210,
+?                 ^^
++       expected: 60,
+?                 ^
+-       max: 210
+?            ^^
++       max: 60
+?            ^
+      }
+    };
+    videoPlayer.configure(videoConfig);
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8648,6 +11944,13 @@
 2. **数据类型影响**：
    - 在问题代码样例中，`width` 被赋值为一个小数（`5.6`），而在修复代码样例中，它被赋值为一个整数（`6`）。这可能暗示在上下文中，整数值更适合或更符合预期的要求。
 因此，修复代码的关键差异在于将 `width` 的值从 `5.6` 更改为 `6`，这可能是为了确保代码的逻辑或功能在执行时能满足特定的要求或期望。</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>- let width = 10; width = 5.6;
+?                         --
++ let width = 10; width = 6;</t>
         </is>
       </c>
     </row>
@@ -8695,6 +11998,14 @@
 总结：修复过程主要是通过将整数 `20` 改为浮点数 `20.0` 来修正问题代码，以保持类型的一致性。</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let speed = 15.0; speed = 20;
++ let speed = 15.0; speed = 20.0;
+?                             ++
+</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8737,6 +12048,15 @@
 综合上述分析，修复代码样例对价格和税率进行了调整，使其在逻辑上可能更加合理。具体而言，修复代码将价格小幅上调至 90，并将税率下调至 7.0。</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let price = 99; let tax = 7.5; price = 89.9; tax = 8;
+?                                        - ^^        ^
++ let price = 99; let tax = 7.5; price = 90; tax = 7.0;
+?                                         ^        ^^^
+</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8778,6 +12098,15 @@
 总结：修复代码样例在 `height` 和 `weight` 的赋值中都将小数值改为了整数值，从而确保了与`number`类型的定义一致。</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let height: number = 180, weight: number = 70; height = 175.5; weight = 68.8;
+?                                                           ^^^            ^^^
++ let height: number = 180, weight: number = 70; height = 176; weight = 69;
+?                                                           ^            ^
+</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8816,6 +12145,14 @@
 3. **一致性**：
    - 修复代码样例使得所有数值类型都保持为浮点数格式，这可能在某些上下文中有助于提高代码的清晰度和一致性，确保所有数值计算在相同的数据类型下进行。
 总结而言，修复代码样例通过将整数转换为浮点数来统一数值类型的表示，提升了代码的一致性和潜在的准确性。</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let accuracy: number = 0.8, improvement: number = 2.0; accuracy = 1; improvement = 3;
++ let accuracy: number = 0.8, improvement: number = 2.0; accuracy = 1.0; improvement = 3.0;
+?                                                                    ++                 ++
+</t>
         </is>
       </c>
     </row>
@@ -8859,6 +12196,14 @@
    - **问题代码**: 由于使用了不连续的索引，使得数组变得稀疏且难以管理，不易理解。
    - **修复代码**: 结构明确，很清楚数组的内容。
 总结：修复代码样例通过直接初始化数组并赋予一个有效的值，避免了问题代码中因为高索引赋值造成的不必要复杂性和稀疏性。这种方式使得数组更易于理解和维护。</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>- let scores: number[] = [];
++ let scores: number[] = [50];
+?                         ++
+- scores[999] = 50;</t>
         </is>
       </c>
     </row>
@@ -8907,6 +12252,13 @@
 总结来说，修复代码样例通过减少数组长度、简化初始化方式和提高可读性，有效地修复了问题代码样例的不必要复杂性。</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>+ let items: string[] = ['item'];
+- let items: string[] = new Array(3000);
+- items[2999] = 'item';</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8950,6 +12302,14 @@
 综上所述，修复代码通过直接初始化数组并避免使用高索引填充，提升了代码的可读性、可靠性，并防止了潜在的错误。</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>- let flags: boolean[] = [];
++ let flags: boolean[] = [true];
+?                         ++++
+- flags[1000] = true;</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8993,6 +12353,13 @@
 综合来看，修复代码通过简化数组的初始化方式，减少了不必要的复杂性，同时避免了潜在的操作错误。</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>+ let temps: number[] = [22.5];
+- let temps: number[] = new Array(50);
+- temps[49] = 22.5;</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9036,6 +12403,14 @@
 总结：修复代码通过直接初始化数组，避免了高索引赋值的问题，确保了数组的结构合理，提升了代码的清晰度和可维护性。</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>- let colors: string[] = [];
++ let colors: string[] = ['blue'];
+?                         ++++++
+- colors[500] = 'blue';</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9075,6 +12450,12 @@
 3. **内存和性能**：
    - 类型化数组如 `Int32Array` 在性能上通常优于普通数组，尤其是在大规模数据和数值计算时，因为它们在内存中占用固定空间，并且能够利用更高效的机器指令。
 综上所述，修复代码样例通过创建类型化数组（`Int32Array`）来改进了数据存储的方法，相比于普通的数字数组，提供了更好的性能和内存管理。</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>- let distances: number[] = [10, 20, 30, 40, 50];
++ let distances = new Int32Array([10, 20, 30, 40, 50]);</t>
         </is>
       </c>
     </row>
@@ -9119,6 +12500,12 @@
 综上所述，修复代码通过使用 `Float32Array` 代替普通数组和使用 `for` 循环进行显式赋值，从而提升了存储效率和代码的可读性。</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>- const temperatures: number[] = Array.from({length: 6}, (_, i) =&gt; i * 5 + 10);
++ const temperatures = new Float32Array(6); for (let i = 0; i &lt; 6; i++) { temperatures[i] = i * 5 + 10; }</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9161,6 +12548,12 @@
 - 修复代码通过将普通数字数组转换为类型化数组（`Int16Array`），改变了数据存储的方式和类型，同时有可能提高了性能和内存使用。</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>- let vector: number[] = [3, 6, 9];
++ let vector = new Int16Array([3, 6, 9]);</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9200,6 +12593,12 @@
 3. **内存管理和性能**：
    - `Uint8ClampedArray` 在处理图像数据或需要进行色彩处理的场景中性能较好，因为它限制了数组元素的范围并且通常会在低级别实现中得到优化。
 综上所述，修复代码样例通过改变数据类型和数组构造方法，使得代码在特定应用场景（尤其是处理图像或亮度值）中更加安全和高效。</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>- const brightnessLevels: number[] = [100, 200, 150, 50];
++ const brightnessLevels = new Uint8ClampedArray([100, 200, 150, 50]);</t>
         </is>
       </c>
     </row>
@@ -9245,6 +12644,12 @@
    - 问题代码的设计虽然可以解决简单的需求，但在处理大量浮点数时，普通数组的性能和内存管理可能不够理想。
    - 修复代码提供了更高效的处理方式，适合在需要频繁进行数学运算的场合，能够提高性能和精度。
 总结：修复代码相比问题代码样例，使用了更适合处理数值的 `Float64Array`，并通过不同的初始化和填充方式，提供了更高效的解决方案。</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>- let weights: number[] = Array(4).fill(2.5);
++ let weights = new Float64Array(4); weights.fill(2.5);</t>
         </is>
       </c>
     </row>
@@ -9341,6 +12746,45 @@
 修复代码通过将数据加载逻辑从列表底部滑动触发改为逐项出现触发，使得用户在查看数据时能够更加平滑地加载额外数据，从而改善了用户体验。</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+      Column({ space: 2 }) {
+        WaterFlow() {
+          LazyForEach(this.dataSource, (item: number) =&gt; {
+            FlowItem() {
+              ReusableFlowItem({ item: item })
+            }
++           .onAppear(() =&gt; {
++             if (item + 10 == this.dataSource.totalCount()) {
++               for (let i = 0; i &lt; 50; i++) {
++                 this.dataSource.addLastItem()
++               }
++             }
++           })
+            .width('100%')
+            .height(this.itemHeightArray[item % 20])
+            .backgroundColor(this.colors[item % 2])
+          }, (item: string) =&gt; item)
+        }
+-       .onReachEnd(() =&gt; {
+-         console.info("Adding more data")
+-         setTimeout(() =&gt; {
+-           for (let i = 0; i &lt; 50; i++) {
+-             this.dataSource.addLastItem()
+-           }
+-         }, 800)
+-       })
+        .columnsTemplate("1fr 1fr")
+        .columnsGap(10)
+        .rowsGap(5)
+        .backgroundColor(0xFAEEE0)
+        .width('100%')
+        .height('100%')
+      }
+    }</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9414,6 +12858,33 @@
 总结来说，修复代码通过引入 `.onAppear()` 方法和一个条件判断，以更灵活和条件化的方式来下载更多数据，提高了性能和用户体验。</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.sourceData, (item: number) =&gt; {
+      FlowItem() {
+        CustomFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 8 == this.sourceData.totalCount()) {
++         for (let i = 0; i &lt; 40; i++) {
++           this.sourceData.updateCollection()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.sizeArray[item % 50])
+      .backgroundColor(this.hues[item % 2])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Triggering more load")
+-   for (let i = 0; i &lt; 40; i++) {
+-     this.sourceData.updateCollection()
+-   }
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9488,6 +12959,35 @@
 总体而言，修复代码样例采用了一种更精确的触发方式来加载更多数据，利用 `.onAppear()` 方法增强了用户体验，而不只是依赖于列表末尾的到达。</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.listData, (item: number) =&gt; {
+      FlowItem() {
+        CustomReusableItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 13 == this.listData.totalCount()) {
++         for (let i = 0; i &lt; 30; i++) {
++           this.listData.extendItems()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.dimensionArray[item % 45])
+      .backgroundColor(this.colorPatterns[item % 3])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Loading additional items")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 30; i++) {
+-       this.listData.extendItems()
+-     }
+-   }, 600)
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9556,6 +13056,33 @@
 3. **移除了 onReachEnd 事件**：
    修复代码中的 `.onReachEnd(...)` 块被移除。这意味着不再在滚动到底部时主动添加更多元素，而是通过在某些特定项出现时进行添加，这可能旨在优化性能或减少不必要的加载。
 总结起来，修复代码的主要改动在于通过使用 `onAppear` 事件来动态管理元素的加载，而不再依赖于达到视图的底部。这样可以更灵活和高效地加载更多数据。</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.elements, (item: number) =&gt; {
+      FlowItem() {
+        ComponentFlow({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 3 == this.elements.totalCount()) {
++         for (let i = 0; i &lt; 20; i++) {
++           this.elements.addMore()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.heightMap[item % 35])
+      .backgroundColor(this.colorMap[item % 4])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Queueing additional entries")
+-   for (let i = 0; i &lt; 20; i++) {
+-     this.elements.addMore()
+-   }
+- })</t>
         </is>
       </c>
     </row>
@@ -9649,6 +13176,35 @@
 - 修复代码将数据加载的触发条件从列表到底部的检查（`onReachEnd`）改为在每个 `FlowItem` 出现时，检查特定条件（`onAppear`），这可能帮助实现更灵活的加载数据策略。</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.itemSource, (item: number) =&gt; {
+      FlowItem() {
+        BaseFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 9 == this.itemSource.totalCount()) {
++         for (let i = 0; i &lt; 60; i++) {
++           this.itemSource.bringMoreData()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.configHeight[item % 40])
+      .backgroundColor(this.palette[item % 5])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Enlarging data load")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 60; i++) {
+-       this.itemSource.bringMoreData()
+-     }
+-   }, 1100)
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9776,6 +13332,67 @@
 4. **更新了 `build` 方法中的逻辑**:
    - 在 `NotificationComp` 和 `AlertComp` 的 `build` 方法中，使用 `localNotificationsEnabled` 替代直接使用 `profile.notificationsEnabled` 进行条件渲染。这使得组件可以使用局部状态来决定要显示的内容，而不是直接依赖于父组件中的 `profile` 状态。
 总的来说，修复代码样例通过引入局部状态和观察机制，解决了在组件中对全局状态的直接依赖，增加了组件的灵活性和可维护性。这样，组件可以根据其自身的需求来响应变化，而不必每次都直接查询全局状态。</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class ProfileSettings {
+    notificationsEnabled: boolean = true;
+  }
+  @Entry
+  @Component
+  struct DemoF {
+    @State profile: ProfileSettings = new ProfileSettings();
+    build() {
+      Row() {
+        NotificationComp({ profile: this.profile })
+        AlertComp({ profile: this.profile })
+        Text('Toggle Notifications')
+          .onClick(() =&gt; {
+            this.profile.notificationsEnabled = !this.profile.notificationsEnabled;
+          })
+      }
+    }
+  }
+  @Component
+  struct NotificationComp {
+-   @Link profile: ProfileSettings;
++   @Link @Watch('onNotifyChange') profile: ProfileSettings;
++   @State localNotificationsEnabled: boolean = true;
++   onNotifyChange() {
++     this.localNotificationsEnabled = this.profile.notificationsEnabled;
++   }
+    build() {
+-     if (this.profile.notificationsEnabled) {
+?              ^^ ^^ ^^^
++     if (this.localNotificationsEnabled) {
+?              ^ ^^ ^
+        Text('Notifications On')
+      } else {
+        Text('Notifications Off')
+      }
+    }
+  }
+  @Component
+  struct AlertComp {
+-   @Link profile: ProfileSettings;
++   @Link @Watch('onNotifyChange') profile: ProfileSettings;
++   @State localNotificationsEnabled: boolean = true;
++   onNotifyChange() {
++     this.localNotificationsEnabled = this.profile.notificationsEnabled;
++   }
+    build() {
+-     if (this.profile.notificationsEnabled) {
+?              ^^ ^^ ^^^
++     if (this.localNotificationsEnabled) {
+?              ^ ^^ ^
+        Text('Alerts Enabled')
+      } else {
+        Text('Alerts Disabled')
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -9896,6 +13513,63 @@
 修复代码样例引入了局部状态管理和变化监听机制，以确保 `Navbar` 和 `Sidebar` 组件在 `darkMode` 状态变化时能够更有效和准确地反映这些变化，从而优化了代码的响应性和性能。</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class DisplaySettings {
+    darkMode: boolean = false;
+  }
+  @Entry
+  @Component
+- struct DemoG {
++ struct DemoGFixed {
+?             +++++
+    @State display: DisplaySettings = new DisplaySettings();
+    build() {
+      Column() {
+        Navbar({ display: this.display })
+        Sidebar({ display: this.display })
+        Text('Toggle Dark Mode')
+          .onClick(() =&gt; {
+            this.display.darkMode = !this.display.darkMode;
+          })
+      }
+    }
+  }
+  @Component
+  struct Navbar {
+-   @Link display: DisplaySettings;
++   @Link @Watch('onModeChange') display: DisplaySettings;
++   @State localDarkMode: boolean = false;
++   onModeChange() {
++     this.localDarkMode = this.display.darkMode;
++   }
+    build() {
+      Text('Navbar')
+-       .backgroundColor(this.display.darkMode ? '#333333' : '#eeeeee')
+?                             ----  ^^^
++       .backgroundColor(this.localDarkMode ? '#333333' : '#eeeeee')
+?                              ++ ^^
+    }
+  }
+  @Component
+  struct Sidebar {
+-   @Link display: DisplaySettings;
++   @Link @Watch('onModeChange') display: DisplaySettings;
++   @State localDarkMode: boolean = false;
++   onModeChange() {
++     this.localDarkMode = this.display.darkMode;
++   }
+    build() {
+      Text('Sidebar')
+-       .backgroundColor(this.display.darkMode ? '#333333' : '#eeeeee')
+?                             ----  ^^^
++       .backgroundColor(this.localDarkMode ? '#333333' : '#eeeeee')
+?                              ++ ^^
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10013,6 +13687,63 @@
 总结：修复代码样例通过引入局部状态和观察机制，使组件在更新时能够更有效地与状态管理进行交互，确保UI的响应性和可维护性。</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class AudioState {
+    mute: boolean = false;
+  }
+  @Entry
+  @Component
+- struct DemoH {
++ struct DemoHFixed {
+?             +++++
+    @State audio: AudioState = new AudioState();
+    build() {
+      Row() {
+        VolumeControl({ audio: this.audio })
+        MuteIndicator({ audio: this.audio })
+        Text('Mute/Unmute')
+          .onClick(() =&gt; {
+            this.audio.mute = !this.audio.mute;
+          })
+      }
+    }
+  }
+  @Component
+  struct VolumeControl {
+-   @Link audio: AudioState;
++   @Link @Watch('onMuteChange') audio: AudioState;
++   @State localMute: boolean = false;
++   onMuteChange() {
++     this.localMute = this.audio.mute;
++   }
+    build() {
+      Text('Volume Control')
+-       .opacity(this.audio.mute ? 0.5 : 1.0)
+?                      ^^^^^^
++       .opacity(this.localMute ? 0.5 : 1.0)
+?                     +++ ^^
+    }
+  }
+  @Component
+  struct MuteIndicator {
+-   @Link audio: AudioState;
++   @Link @Watch('onMuteChange') audio: AudioState;
++   @State localMute: boolean = false;
++   onMuteChange() {
++     this.localMute = this.audio.mute;
++   }
+    build() {
+      Text('Mute Status')
+-       .opacity(this.audio.mute ? 1.0 : 0.5)
+?                      ^^^^^^
++       .opacity(this.localMute ? 1.0 : 0.5)
+?                     +++ ^^
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10130,6 +13861,63 @@
 总结来说，修复代码样例通过引入本地状态和监听机制，使得 `BatteryIcon` 和 `BatteryInfo` 组件能更动态地响应 `BatteryStatus` 对象状态的变化，提升了组件间的交互和状态同步能力。</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class BatteryStatus {
+    isCharging: boolean = true;
+  }
+  @Entry
+  @Component
+- struct DemoI {
++ struct DemoIFixed {
+?             +++++
+    @State battery: BatteryStatus = new BatteryStatus();
+    build() {
+      Column() {
+        BatteryIcon({ battery: this.battery })
+        BatteryInfo({ battery: this.battery })
+        Text('Toggle Charging')
+          .onClick(() =&gt; {
+            this.battery.isCharging = !this.battery.isCharging;
+          })
+      }
+    }
+  }
+  @Component
+  struct BatteryIcon {
+-   @Link battery: BatteryStatus;
++   @Link @Watch('onChargeChange') battery: BatteryStatus;
++   @State localIsCharging: boolean = true;
++   onChargeChange() {
++     this.localIsCharging = this.battery.isCharging;
++   }
+    build() {
+      Text('Battery Icon')
+-       .text(this.battery.isCharging ? 'Charging' : 'Discharging')
+?                  ^ ^^^^^^^
++       .text(this.localIsCharging ? 'Charging' : 'Discharging')
+?                  ^^^ ^^
+    }
+  }
+  @Component
+  struct BatteryInfo {
+-   @Link battery: BatteryStatus;
++   @Link @Watch('onChargeChange') battery: BatteryStatus;
++   @State localIsCharging: boolean = true;
++   onChargeChange() {
++     this.localIsCharging = this.battery.isCharging;
++   }
+    build() {
+      Text('Battery Info')
+-       .text(this.battery.isCharging ? 'Power Source Connected' : 'Running on Battery')
+?                  ^ ^^^^^^^
++       .text(this.localIsCharging ? 'Power Source Connected' : 'Running on Battery')
+?                  ^^^ ^^
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10245,6 +14033,63 @@
 4. **文本显示的改动**：
    - 虽然 `Text` 的内容在模板中保持一致，但其更新机制从直接依赖共享状态`this.network.isConnected` 转变为依赖组件的本地状态 `this.localIsConnected`，提高了组件的响应性和独立性。
 综上所述，修复代码主要增强了组件的适应性和解耦性，使用了本地状态和观察者模式来管理网络状态变化。这种方式避免了直接修改共享状态可能带来的不一致性问题。</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class NetworkConfig {
+    isConnected: boolean = true;
+  }
+  @Entry
+  @Component
+- struct DemoJ {
++ struct DemoJFixed {
+?             +++++
+    @State network: NetworkConfig = new NetworkConfig();
+    build() {
+      Row() {
+        StatusIndicator({ network: this.network })
+        DataUsage({ network: this.network })
+        Text('Connect/Disconnect')
+          .onClick(() =&gt; {
+            this.network.isConnected = !this.network.isConnected;
+          })
+      }
+    }
+  }
+  @Component
+  struct StatusIndicator {
+-   @Link network: NetworkConfig;
++   @Link @Watch('onConnectionChange') network: NetworkConfig;
++   @State localIsConnected: boolean = true;
++   onConnectionChange() {
++     this.localIsConnected = this.network.isConnected;
++   }
+    build() {
+      Text('Status Indicator')
+-       .text(this.network.isConnected ? 'Connected' : 'Disconnected')
+?                  ^^^^ ^^^^
++       .text(this.localIsConnected ? 'Connected' : 'Disconnected')
+?                  ^ ^^^^
+    }
+  }
+  @Component
+  struct DataUsage {
+-   @Link network: NetworkConfig;
++   @Link @Watch('onConnectionChange') network: NetworkConfig;
++   @State localIsConnected: boolean = true;
++   onConnectionChange() {
++     this.localIsConnected = this.network.isConnected;
++   }
+    build() {
+      Text('Data Usage')
+-       .text(this.network.isConnected ? 'Tracking Usage' : 'Offline Mode')
+?                  ^^^^ ^^^^
++       .text(this.localIsConnected ? 'Tracking Usage' : 'Offline Mode')
+?                  ^ ^^^^
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -10305,6 +14150,17 @@
 修复后的代码通过传入一个唯一标识符提取函数，使得在渲染产品列表时能够更有效地管理和更新DOM元素。这是相较于问题代码样例的主要改进。</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build() {
+      Column() {
+        ForEach(this.products, (product: Product) =&gt; {
+-       });
++       }, (product: Product) =&gt; product.productCode);
+      }
+    } }</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10346,6 +14202,14 @@
 总结来说，修复代码样例相对于问题代码样例的主要差异在于增加了一个用于获取 `orderNumber` 的函数，这可能增强了代码的灵活性和可维护性。</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { List() { ForEach(this.orders, (order, i) =&gt; { OrderItem(order); }); } }
++ build() { List() { ForEach(this.orders, (order, i) =&gt; { OrderItem(order); }, (order) =&gt; order.orderNumber); } }
+?                                                                            ++++++++++++++++++++++++++++++
+</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10383,6 +14247,14 @@
    - 问题代码样例的 `ForEach` 仅仅遍历 `this.comments` 并对每个 `comment` 调用 `CommentView(comment)`。
    - 修复代码样例的 `ForEach` 为每个 `comment` 调用 `CommentView(comment)` 的同时，还提供了一个用于标识每个评论的回调函数 `commentID`。这可能意味着修复后的代码引入了评论的唯一标识，可能提高了评论视图的处理效率或准确性。
 总结来说，修复代码通过增加一个用于唯一标识评论的函数，使得 `ForEach` 的实现更具灵活性和可能增强其功能。</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { Grid() { ForEach(this.comments, (comment, idx) =&gt; { CommentView(comment); }); } }
++ build() { Grid() { ForEach(this.comments, (comment, idx) =&gt; { CommentView(comment); }, (comment) =&gt; comment.commentID); } }
+?                                                                                      ++++++++++++++++++++++++++++++++
+</t>
         </is>
       </c>
     </row>
@@ -10429,6 +14301,14 @@
 总结：修复代码样例增加了一个用于唯一标识每个书籍的参数，目的在于提供更好的管理和识别机制。</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { Stack() { ForEach(this.books, (book) =&gt; { BookItem(book); }); } }
++ build() { Stack() { ForEach(this.books, (book) =&gt; { BookItem(book); }, (book) =&gt; book.isbn); } }
+?                                                                      +++++++++++++++++++++
+</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10466,6 +14346,14 @@
    - 问题代码在处理数组中的元素时，没有提供唯一的标识符。
    - 修复代码通过添加一个闭包 `(photo) =&gt; photo.uniqueID` 作为第三个参数，指定了每个 `photo` 的唯一标识符。这有助于优化视图更新和避免重复元素的渲染，提高性能和准确性。
 总结：修复代码通过提供每个 photo 的唯一标识符来增强 `ForEach` 的功能，使得渲染过程能够更有效地跟踪和管理列表中的元素。</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { VStack() { ForEach(this.photos, (photo, index) =&gt; { PhotoThumbnail(photo); }); } }
++ build() { VStack() { ForEach(this.photos, (photo, index) =&gt; { PhotoThumbnail(photo); }, (photo) =&gt; photo.uniqueID); } }
+?                                                                                       +++++++++++++++++++++++++++
+</t>
         </is>
       </c>
     </row>
@@ -10517,6 +14405,17 @@
 - 修复代码样例相对于问题代码样例的主要差异是对 `FileX.ets` 中的导入进行了更改，从导入 `FileY.ets` 变更为导入 `FileZ.ets`，从而避免了循环导入的问题。`FileY.ets` 的导入保持不变。</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // FileX.ets
+- import {} from './FileY.ets';
+?                       ^
++ import {} from './FileZ.ets';
+?                       ^
+  // FileY.ets
+  import {} from './FileX.ets';</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10562,6 +14461,17 @@
    - 问题代码和修复代码保持一致：`import {} from './Object1.ets';`
    `Object2.ets` 仍然导入 `Object1.ets`，但由于 `Object1.ets` 不再导入 `Object2.ets`，因此这部分的潜在循环依赖问题已经解决。
 总结来说，修复代码样例的差异主要在于 `Object1.ets` 中的导入修改，避免了循环依赖，从而使得整个代码更加稳定。</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // Object1.ets
+- import {} from './Object2.ets';
+?                         ^
++ import {} from './Object3.ets';
+?                         ^
+  // Object2.ets
+  import {} from './Object1.ets';</t>
         </is>
       </c>
     </row>
@@ -10623,6 +14533,17 @@
 总结：主要的差异是在 `Element1.ets` 文件中的导入目标发生了改变，从 `Element2.ets` 修改为 `Element4.ets`，而 `Element2.ets` 中的导入保持不变。</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // Element1.ets
+- import {} from './Element2.ets';
+?                          ^
++ import {} from './Element4.ets';
+?                          ^
+  // Element2.ets
+  import {} from './Element1.ets';</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10666,6 +14587,17 @@
    - 在问题代码样例中，`import` 语句是从 `'./PackageA.ets'` 进行导入。
    - 在修复代码样例中，这部分保持不变，依然是从 `'./PackageA.ets'` 进行导入。
 综上所述，修复的重点在于将 `PackageA.ets` 中的导入目标从 `PackageB.ets` 更改为 `PackageC.ets`，以解决循环依赖问题，而 `PackageB.ets` 的导入保持不变。</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // PackageA.ets
+- import {} from './PackageB.ets';
+?                          ^
++ import {} from './PackageC.ets';
+?                          ^
+  // PackageB.ets
+  import {} from './PackageA.ets';</t>
         </is>
       </c>
     </row>
@@ -10715,6 +14647,17 @@
 整体上，修复实际上是将 `Node1.ets` 文件中与 `Node2.ets` 间的循环依赖通过引入 `Node3.ets` 进行了解决，这样能够避免潜在的依赖冲突或加载顺序的问题。</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // Node1.ets
+- import {} from './Node2.ets';
+?                       ^
++ import {} from './Node3.ets';
+?                       ^
+  // Node2.ets
+  import {} from './Node1.ets';</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10776,6 +14719,23 @@
 总的来说，修复代码通过在循环外部提取 `searchItem` 而避免了不必要的多次数组访问，使得代码更高效，易读且性能更佳。</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Catalog {
+    static items: string[] = ['book', 'pen', 'notebook'];
+  }
+  function locateItem(searchIndex: number): boolean {
++   const searchItem = Catalog.items[searchIndex]; // 提取到循环外
+    for (let k = 0; k &lt; Catalog.items.length; k++) {
+-     if (Catalog.items[k] === Catalog.items[searchIndex]) { // 不必要的重复访问
++     if (Catalog.items[k] === searchItem) {
+        return true;
+      }
+    }
+    return false;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10832,6 +14792,22 @@
    - 问题代码样例中的循环体为 `sum += Metrics.data[factor] + m;`，每次循环都需要重新从 `Metrics.data` 中获取同一个值。
    - 修复代码样例中的循环体修改为 `sum += factorValue + m;`，使用之前存储的 `factorValue` 来计算总和，简化了加法的计算过程。
 通过上述两点的调整，修复后的代码样例提高了性能，减少了不必要的数组访问。</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Metrics {
+    static data: number[] = [3, 6, 9, 12];
+  }
+  function computeSum(factor: number): number {
+    let sum: number = 0;
++   const factorValue = Metrics.data[factor]; // 提取到循环外
+    for (let m = 0; m &lt; Metrics.data.length; m++) {
+-     sum += Metrics.data[factor] + m; // 每次循环重复访问
++     sum += factorValue + m;
+    }
+    return sum;
+  }</t>
         </is>
       </c>
     </row>
@@ -10900,6 +14876,23 @@
 以上是修复代码样例相对于问题代码样例的主要差异。通过这个修复，代码变得更加简洁且高效。</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Collection {
+    static entries: string[] = ['one', 'two', 'three'];
+  }
+  function isEntryMatch(refIndex: number): boolean {
++   const refEntry = Collection.entries[refIndex]; // 提取到循环外
+    for (const entry of Collection.entries) {
+-     if (Collection.entries[refIndex] === entry) { // 固定值重复使用
++     if (refEntry === entry) {
+        return true;
+      }
+    }
+    return false;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10963,6 +14956,23 @@
 总结来看，修复代码样例通过简化访问方式，提高了性能和可读性，这是一个很好的编码实践。</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Values {
+    static list: number[] = [100, 200, 300, 400];
+  }
+  function checkHighValue(ref: number): boolean {
++   const refValue = Values.list[ref]; // 提取到循环外
+    for (let v of Values.list) {
+-     if (Values.list[ref] &lt; v) { // 无效的反复访问
++     if (refValue &lt; v) {
+        return false;
+      }
+    }
+    return true;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11020,6 +15030,23 @@
 2. **可读性**:
    - 虽然这不是明显的技术差异，但提取变量 `checkBound` 使得代码在逻辑上更清晰。读者更容易理解该变量在循环中的用途，而不是将访问 `Range.bounds[index]` 的逻辑分散在循环内部。
 总结来说，修复代码样例通过预先计算并存储 `Range.bounds[index]` 的值，减小了重复计算的开销，并提高了代码的可读性。</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Range {
+    static bounds: number[] = [8, 16, 24, 32];
+  }
+  function detectBound(index: number): boolean {
++   const checkBound = Range.bounds[index]; // 提取到循环外
+    for (let b = 0; b &lt; Range.bounds.length; b++) {
+-     if (Range.bounds[index] === Range.bounds[b]) { // 不变的值重复访问
++     if (checkBound === Range.bounds[b]) {
+        return true;
+      }
+    }
+    return false;
+  }</t>
         </is>
       </c>
     </row>
@@ -11083,6 +15110,23 @@
 总结而言，修复代码样例相对于问题代码样例的主要变化是删除了调试日志的记录，并引入了一个新的常量，但没有给出该常量的实际用途。</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct App {
+    build() {
+      List() {
+        Text('Item')
+      }.onItemDragMove(() =&gt; {
+-       hilog.debug(1001, 'App', 'onItemDragMove')
++       const TAG = 'onItemDragMove';
+      })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11092,7 +15136,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>不建议在高频函数中使用Hilog。</t>
+          <t>不建议在高频函数中使用Hilog或者其它打印日志的方式。</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11141,6 +15185,24 @@
 2. **引入了常量TAG**:
    - 在修复代码中，增加了一行 `const TAG = 'onAreaChange';` 作为常量的定义，这可能是为了后续使用，但在目前的代码中并没有后续使用的体现。
 总结来说，修复代码主要是去掉了错误日志记录功能，并增加了一个常量定义。这样可能是为了简化代码，或是准备在后续代码逻辑中使用该常量，但目前其作用还不明确。</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct App {
+    build() {
+      Canvas(()=&gt;{})
+        .width('100%')
+        .height('100%')
+        .onAreaChange(() =&gt; {
+-         hilog.error(1001, 'App', 'onAreaChange')
++         const TAG = 'onAreaChange';
+      })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -11200,6 +15262,22 @@
 总结来说，修复代码样例删除了日志记录的实现并添加了一个常量声明，但未对程序的功能或行为进行显著的更改。</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct App {
+    build() {
+      Slider()
+        .onActionUpdate(() =&gt; {
+-         hilog.warn(1001, 'App', 'onActionUpdate')
++         const TAG = 'onActionUpdate';
+      })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11255,6 +15333,22 @@
 2. **TAG 常量的引入**：  
    - 修复代码中引入了 `const TAG = 'onMouse';` ，但在修复代码中并没有使用这个常量，可能是为了后续的扩展或使用而添加的。
 总结来说，修复代码样例主要的变化是移除了日志记录的功能，并引入了一个 TAG 常量，但没有在实际逻辑中体现该常量的用途。</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct App {
+    build() {
+      ListItem()
+        .onMouse(() =&gt; {
+-         hilog.info(2001, 'App', 'onMouse')
++         const TAG = 'onMouse';
+      })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -11314,6 +15408,22 @@
 3. **代码逻辑的简化**：
    - 修复后的代码逻辑更简单，仅是声明了一个变量而没有执行额外的操作（如日志输出），这可能是为了简化或优化代码。
 总的来说，修复代码去掉了日志记录，并仅保留了一个基于字符串的变量声明，这改变了原本的日志记录行为。</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>- import hilog from '@ohos.hilog';
+  @Entry
+  @Component
+  struct App {
+    build() {
+      Toggle()
+        .onActionUpdate(() =&gt; {
+-         hilog.debug(3001, 'App', 'Toggle Action Update')
++         const state = 'Toggle Action Update';
+      })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -11396,6 +15506,37 @@
    - 在问题代码样例中，并没有对动画进行销毁的处理，导致在组件消失时可能会存在内存泄漏或者不必要的动画继续运行的情况。
    - 修复代码样例通过对 `this.animation` 的管理，确保了在组件消失时可以安全释放相关资源。
 总之，修复代码样例通过添加 `onDisAppear` 方法及其中对动画的清理逻辑，提升了组件的资源管理与性能。</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  @Entry
+  @Component
+- struct ExampleComponent {
++ struct ExampleComponentFixed {
+?                        +++++
+    private myController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private animation?: AnimationItem;
+    build() {
+      Canvas(this.myController)
+        .width(150)
+        .height(150)
+        .onReady(() =&gt; {
+-         // 未在页面消失时销毁动画
+          this.animation = lottie.loadAnimation({
+            container: this.myController,
+            renderer: 'svg',
+            autoplay: true,
+            path: 'example.json'
+          });
+        });
+    }
++   onDisAppear() {
++     this.animation?.destroy();
++     this.animation = null;
++   }
+  }</t>
         </is>
       </c>
     </row>
@@ -11488,6 +15629,41 @@
 总结来说，修复代码通过添加 `onPageHide` 方法以及在其中处理动画的销毁与清理，有效地解决了原始代码中可能导致的资源管理问题。</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  @Entry
+  @Component
+- struct MultipleAnimations {
++ struct MultipleAnimationsFixed {
+?                          +++++
+    private controller: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private animations: AnimationItem[] = [];
+    build() {
+      Canvas(this.controller)
+        .width(180)
+        .height(180)
+        .onReady(() =&gt; {
+-         // 加载多个动画但未销毁
+          for (let i = 0; i &lt; 3; i++) {
+            const anim = lottie.loadAnimation({
+              container: this.controller,
+              renderer: 'canvas',
+              loop: true,
+              autoplay: true,
+              path: `animation_${i}.json`
+            });
+            this.animations.push(anim);
+          }
+        });
+    }
++   onPageHide() {
++     this.animations.forEach(anim =&gt; anim.destroy());
++     this.animations = [];
++   }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11574,6 +15750,38 @@
 总结来说，修复代码样例通过引入 `aboutToDisappear` 方法和相应的逻辑，实现了对动画资源的正确管理，提高了代码的健壮性。</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  @Entry
+  @Component
+- struct SingleAnimation {
++ struct SingleAnimationFixed {
+?                       +++++
+    private context: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private animation: AnimationItem | undefined;
+    build() {
+      Canvas(this.context)
+        .width(100)
+        .height(100)
+        .onReady(() =&gt; {
+-         // 无销毁逻辑
+          this.animation = lottie.loadAnimation({
+            container: this.context,
+            renderer: 'svg',
+            loop: false,
+            autoplay: true,
+            path: 'simple_anim.json'
+          });
+        });
+    }
++   aboutToDisappear() {
++     this.animation?.destroy();
++     this.animation = undefined;
++   }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11652,6 +15860,36 @@
 2. **功能增强**:
    - 通过添加 `onPageHide` 方法，修复代码样例显著增强了组件在页面生命周期管理上的处理，特别是与动画资源的管理相关，使得组件能够更好地释放不再需要的资源。
 总结而言，修复代码样例通过新增 `onPageHide` 方法并添加 `lottie.destroy()` 来解决问题代码样例中未能释放动画资源的问题，从而提升了代码的健壮性和内存管理能力。</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  @Entry
+  @Component
+- struct MissedDestroy {
++ struct MissedDestroyFixed {
+?                     +++++
+    private renderController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    build() {
+      Canvas(this.renderController)
+        .width(180)
+        .height(180)
+        .onReady(() =&gt; {
+-         // 未销毁动画
+          lottie.loadAnimation({
+            container: this.renderController,
+            renderer: 'svg',
+            loop: true,
+            autoplay: true,
+            path: 'missed_destroy.json'
+          });
+        });
+    }
++   onPageHide() {
++     lottie.destroy();
++   }
+  }</t>
         </is>
       </c>
     </row>
@@ -11747,6 +15985,39 @@
 总结：修复代码通过增加 `onPageHide` 方法来增强资源管理，确保在页面隐藏时适当地处理动画资源。</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import lottie from '@ohos/lottie';
+  @Entry
+  @Component
+- struct IncompleteDestroy {
++ struct IncompleteDestroyFixed {
+?                         +++++
+    private drawingController: CanvasRenderingContext2D = new CanvasRenderingContext2D();
+    private animationItem: AnimationItem | null = null;
+    build() {
+      Canvas(this.drawingController)
+        .width(200)
+        .height(200)
+        .onReady(() =&gt; {
+          this.animationItem = lottie.loadAnimation({
+            container: this.drawingController,
+            renderer: 'canvas',
+            loop: true,
+            autoplay: true,
+            path: 'incomplete.json'
+          });
+        });
+    }
++   onPageHide() {
++     if (this.animationItem) {
++       this.animationItem.destroy();
++       this.animationItem = null;
++     }
++   }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11804,6 +16075,27 @@
    - 修复代码：`max: 60`
    - 差异：最大帧率从144减少到60。
 综上所述，修复代码通过将期望、最小和最大帧率都降低，目的是可能为了解决某些与高帧率相关的兼容性或性能问题。</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  function setupSync() {
+    const frameSync = displaySync.create();
+    frameSync.configureRateRange({
+-     expected: 144,
+?               ^^^
++     expected: 60,
+?               ^^
+-     min: 144,
+?          ^^^
++     min: 30,
+?          ^^
+-     max: 144
+?          ^^^
++     max: 60
+?          ^^
+    });
+  }</t>
         </is>
       </c>
     </row>
@@ -11862,6 +16154,25 @@
 这些更改降低了`rateConfig`的期望值及其范围（最小值和最大值），使配置更加合理。</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  const rateConfig = {
+-   expected: 150,
+?             ^^
++   expected: 60,
+?             ^
+-   min: 150,
+?        ^^
++   min: 30,
+?        ^
+-   max: 150
+?        ^^
++   max: 60
+?        ^
+  };
+  displaySync.setRateRange(rateConfig);</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11923,6 +16234,33 @@
    - 修复代码样例中，`frameRate`的`expected`设置为`60`，`min`设置为`30`，`max`设置为`60`。这意味着期望帧率降至60帧/秒，最小帧率为30帧/秒，最大帧率保持在60帧/秒。
 ### 总结：
 - 问题代码的帧率设置相对较高（144帧/秒），可能对性能要求太高，而修复代码将帧率调整到一个更合理的范围（30至60帧/秒），从而提升了代码的可执行性与兼容性。</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct AnimationComponent {
+    setup() {
+      animate({
+        duration: 5000,
+        frameRate: {
+-         expected: 144,
+?                   ^^^
++         expected: 60,
+?                   ^^
+-         min: 144,
+?              ^^^
++         min: 30,
+?              ^^
+-         max: 144
+?              ^^^
++         max: 60
+?              ^^
+        }
+      });
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -11983,6 +16321,25 @@
 - `maxFrameRate`由200变为60</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let videoSettings = {
+-   expectedFrameRate: 200,
+?                      ^^
++   expectedFrameRate: 60,
+?                      ^
+-   minFrameRate: 200,
+?                 ^^
++   minFrameRate: 30,
+?                 ^
+-   maxFrameRate: 200
+?                 ^ -
++   maxFrameRate: 60
+?                 ^
+  };
+  mediaPlayer.setRateOptions(videoSettings);</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12027,6 +16384,16 @@
 - **主要差异**是 `setRange` 方法中参数的具体值变化，导致了最高帧率从 240 降至 60，最低帧率从 240 降至 30，目标帧率保持在 60。这一改变旨在提升系统的性能和稳定性。</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  const frameController = new FrameRateController();
+- frameController.setRange(240, 240, 240);
+?                          ^^   ^^   ^^
++ frameController.setRange(60, 30, 60);
+?                          ^   ^   ^
+</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12066,6 +16433,15 @@
 综上所述，修复代码样例中，`minValue` 变量最后的值从 `0.5` 变更为 `1`。这意味着修复代码将 `minValue` 的值提升到了更高的数值。</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let minValue = 0; minValue = 0.5;
+?                              ^^^
++ let minValue = 0; minValue = 1;
+?                              ^
+</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12103,6 +16479,15 @@
    - 问题代码样例中的值 `1` 明显低于原始值 `3.2`，可能导致 `maxRate` 变得不符合预期或有效范围。
    - 修复代码样例中的值 `2.8` 则仍然保持在 `3.2` 的有效范围内，且接近原始值，可能更符合系统对 `maxRate` 的要求。
 总结：修复代码样例通过将 `maxRate` 的值从 `1` 改为 `2.8`，保持了更接近原始值 `3.2` 的设置，确保了 `maxRate` 处于合理的范围内。</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let maxRate = 3.2; maxRate = 1;
+?                              ^
++ let maxRate = 3.2; maxRate = 2.8;
+?                              ^^^
+</t>
         </is>
       </c>
     </row>
@@ -12147,6 +16532,15 @@
 综上所述，修复代码样例相对于问题代码样例的主要差异在于 `average` 和 `yearCount` 变量的赋值发生了变化。</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let yearCount = 5; let average = 7.9; average = 5; yearCount = 5.5;
+?                                                 ^              ^^^
++ let yearCount = 5; let average = 7.9; average = 6.3; yearCount = 4;
+?                                                 ^^^              ^
+</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -12184,6 +16578,13 @@
    - 问题代码样例中，`grade` 被设置为 `8.4`。
    - 修复代码样例中，`grade` 被改为 `8`，即将其值从 `8.4` 修改为 `8`。
 总结来说，修复代码通过将 `fullMarks` 和 `grade` 的值分别调整为整数（`9` 和 `8`），以确保它们在问题代码的浮点数值调整中修复为符合整数标准的正确值。这种变化可能与某种业务规则或数据验证有关，旨在确保两个变量的值均为整数。</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>- let fullMarks: number = 10, grade: number = 5; fullMarks = 9.5; grade = 8.4;
+?                                                             --           --
++ let fullMarks: number = 10, grade: number = 5; fullMarks = 9; grade = 8;</t>
         </is>
       </c>
     </row>
@@ -12225,6 +16626,15 @@
    - 修复代码：`bonus` 被赋值为 `1.7`。
    - 变化：值从 `2` 改为 `1.7`。
 总结来说，修复后的代码样例更改了 `halfValue` 和 `bonus` 的赋值，分别降低了这两个变量的值。</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let halfValue: number = 0.5, bonus: number = 1.5; halfValue = 1; bonus = 2;
+?                                                               ^          ^
++ let halfValue: number = 0.5, bonus: number = 1.5; halfValue = 0.8; bonus = 1.7;
+?                                                               ^^^          ^^^
+</t>
         </is>
       </c>
     </row>
@@ -12274,6 +16684,14 @@
 修复代码通过直接将元素 `7` 加入数组，避免了产生稀疏数组的问题，使得代码更加清晰且有效。</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>- let points: number[] = [];
++ let points: number[] = [7];
+?                         +
+- points[1500] = 7;</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -12317,6 +16735,13 @@
 总体而言，修复代码样例通过简单化数组的创建和初始化，避免了冗余的数组长度和不必要的 `undefined` 元素，使代码更为清晰和有效。</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>+ let data: boolean[] = [true];
+- let data: boolean[] = new Array(20000);
+- data[19999] = true;</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -12356,6 +16781,14 @@
    - 修复代码没有使用高索引，而是使用了默认的 `0` 索引（数组的第一项）。
 总结：
 - 修复代码样例通过直接初始化数组并赋值于合理的索引位置，改进了内存使用和性能，避免了不必要的初始化与潜在错误。</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>- let values: number[] = [];
++ let values: number[] = [10];
+?                         ++
+- values[3333] = 10;</t>
         </is>
       </c>
     </row>
@@ -12401,6 +16834,13 @@
 总的来说，修复代码样例使得代码更加简洁和高效，同时避免了不必要的内存占用和潜在的错误。</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>+ let chars: string[] = ['z'];
+- let chars: string[] = new Array(500);
+- chars[499] = 'z';</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12442,6 +16882,14 @@
    - **问题代码**: 没有给数组定义初始长度，导致在尝试访问未定义索引时出现问题。
    - **修复代码**: 明确初始化一个具有一个元素的数组，避免了索引越界的问题。
 综上所述，修复代码通过正确初始化数组，确保了在操作该数组时不会出现越界或未定义元素的问题。</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>- let flags: boolean[] = [];
++ let flags: boolean[] = [false];
+?                         +++++
+- flags[200] = false;</t>
         </is>
       </c>
     </row>
@@ -12488,6 +16936,12 @@
 总结来说，修复代码样例更明确地指定了数据类型，使用了传统的方法填充数组，可能在性能方面更具优势，而问题代码样例则在可读性和简洁性上优于修复代码。</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>- const dataPoints: number[] = Array.from({length: 5}, (_, i) =&gt; i * 10);
++ const dataPoints = new Int16Array(5); for (let i = 0; i &lt; 5; i++) { dataPoints[i] = i * 10; }</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12528,6 +16982,12 @@
    - 使用 `number[]`，数组可以包含负数、浮点数等各种数字类型。
    - 使用 `Uint8Array`，数组对象只允许包含有效的无符号整数（0-255）。
 总结：修复代码样例通过引入 `Uint8Array` 提供了更严格的类型限制和可能更好的性能，但同时减少了数组可以存储的数据范围。</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>- const squareArray: number[] = [1, 4, 9, 16, 25];
++ const squareArray = new Uint8Array([1, 4, 9, 16, 25]);</t>
         </is>
       </c>
     </row>
@@ -12575,6 +17035,12 @@
 总结：修复代码样例采用了更高效且类型安全的方式来初始化数组，同时避免了不必要的中间步骤，从而优化了性能。</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>- let multipliers: number[] = Array(10).fill(1).map((_, index) =&gt; index * 1.5);
++ let multipliers = new Float64Array(10); for (let i = 0; i &lt; 10; i++) { multipliers[i] = i * 1.5; }</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12616,6 +17082,12 @@
 综上所述，修复代码样例通过使用 `Uint8ClampedArray` 改变了数据的类型和处理方式，以确保适用于特定的使用场景（如图像像素值），增强了代码的健壮性和安全性。</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>- const pixelValues: number[] = [255, 128, 64, 32, 16];
++ const pixelValues = new Uint8ClampedArray([255, 128, 64, 32, 16]);</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12653,6 +17125,15 @@
    - 原代码使用了字面量方式直接初始化数组。
    - 修复代码使用了 `new Int32Array([...])` 的构造函数来创建数组，这种方式为数组提供了固定的类型和更好的性能。
 总的来说，修复代码样例通过使用 `Int32Array` 替代普通的数字数组，确保了数组中元素的类型为32位整数，这可以在某些应用中提供更好的内存管理和性能。</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- let fibonacci: number[] = [0, 1, 1, 2, 3, 5, 8, 13, 21];
+?              ----------
++ let fibonacci = new Int32Array([0, 1, 1, 2, 3, 5, 8, 13, 21]);
+?                 +++++++++++++++                             +
+</t>
         </is>
       </c>
     </row>
@@ -12731,6 +17212,35 @@
 总结来说，修复代码引入了在`FlowItem` 每次出现时的动态数据加载逻辑，并且移除了基于整体视图的底部触发加载的逻辑，使得数据获取可能更加即时和灵活。</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 18 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 60; i++) {
++           this.dataSource.fetchNewData()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 30])
+      .backgroundColor(this.colors[item % 3])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Fetching more data")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 60; i++) {
+-       this.dataSource.fetchNewData()
+-     }
+-   }, 700)
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12802,6 +17312,33 @@
 - 主要的差异在于修复方案通过 `.onAppear()` 方法在特定条件下动态加载数据项，增强了数据加载的灵活性，而问题代码则是在列表到达末尾时进行数据加载。修复代码使得在列表中某个项接近底部（即`item + 15 == totalCount`）时就可以提前加载数据，从而提升用户体验。</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 15 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 70; i++) {
++           this.dataSource.addBatchItem()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 60])
+      .backgroundColor(this.colors[item % 3])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Load end")
+-   for (let i = 0; i &lt; 70; i++) {
+-     this.dataSource.addBatchItem()
+-   }
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12874,6 +17411,35 @@
 总结：修复代码样例通过将加载更多项的逻辑从 `.onReachEnd()` 位置转移到 `.onAppear()`，并增加了条件判断，使得数据加载更加灵活和高效。</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 12 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 80; i++) {
++           this.dataSource.loadItems()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 70])
+      .backgroundColor(this.colors[item % 4])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("More items coming")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 80; i++) {
+-       this.dataSource.loadItems()
+-     }
+-   }, 1200)
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12944,6 +17510,33 @@
 总体来说，修复代码样例通过引入了 `.onAppear()` 事件，使得增加数据的时机更早，并增加了具体的条件判断，这样可以更高效地管理数据源的更新。</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 22 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 90; i++) {
++           this.dataSource.increaseCollection()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 90])
+      .backgroundColor(this.colors[item % 5])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Appending items")
+-   for (let i = 0; i &lt; 90; i++) {
+-     this.dataSource.increaseCollection()
+-   }
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13018,6 +17611,35 @@
 总体来说，修复代码样例将数据扩展从滚动结束事件改为了流项出现事件，并增加了条件判断，使得数据扩展的行为更为灵活和适应当前的渲染情况。</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WaterFlow() {
+    LazyForEach(this.dataSource, (item: number) =&gt; {
+      FlowItem() {
+        ReusableFlowItem({ item: item })
+      }
++     .onAppear(() =&gt; {
++       if (item + 5 == this.dataSource.totalCount()) {
++         for (let i = 0; i &lt; 110; i++) {
++           this.dataSource.expandList()
++         }
++       }
++     })
+      .width('100%')
+      .height(this.itemHeightArray[item % 25])
+      .backgroundColor(this.colors[item % 6])
+    }, (item: string) =&gt; item)
+  }
+- .onReachEnd(() =&gt; {
+-   console.info("Scroll end detected")
+-   setTimeout(() =&gt; {
+-     for (let i = 0; i &lt; 110; i++) {
+-       this.dataSource.expandList()
+-     }
+-   }, 1500)
+- })</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13133,6 +17755,63 @@
 4. **布局状态的更新逻辑变化**：
    - 在修复代码样例中，`build` 方法使用 `localLayoutType` 来决定文本对齐方式，而不是直接使用 `this.layout.layoutType`。这种设计允许组件在状态变化时通过 `onLayoutChange` 方法进行更新，而不直接依赖于父组件的状态。
 综上所述，修复代码样例通过引入局部状态和观察者模式，避免了在父组件状态变化时，子组件不能正确渲染的问题，从而实现了更为健壮的状态管理。</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class UIConfig {
+    layoutType: string = 'grid';
+  }
+  @Entry
+  @Component
+- struct DemoA {
++ struct DemoAFixed {
+?             +++++
+    @State config: UIConfig = new UIConfig();
+    build() {
+      Column() {
+        HeaderComp({ layout: this.config })
+        FooterComp({ layout: this.config })
+        Text('Switch Layout')
+          .onClick(() =&gt; {
+            this.config.layoutType = 'list';
+          })
+      }
+    }
+  }
+  @Component
+  struct HeaderComp {
+-   @Link layout: UIConfig;
++   @Link @Watch('onLayoutChange') layout: UIConfig;
++   @State localLayoutType: string = 'grid';
++   onLayoutChange() {
++     this.localLayoutType = this.layout.layoutType;
++   }
+    build() {
+      Text('Header')
+-       .textAlign(this.layout.layoutType === 'grid' ? 'center' : 'left')
+?                         -----
++       .textAlign(this.localLayoutType === 'grid' ? 'center' : 'left')
+?                        ++  +
+    }
+  }
+  @Component
+  struct FooterComp {
+-   @Link layout: UIConfig;
++   @Link @Watch('onLayoutChange') layout: UIConfig;
++   @State localLayoutType: string = 'grid';
++   onLayoutChange() {
++     this.localLayoutType = this.layout.layoutType;
++   }
+    build() {
+      Text('Footer')
+-       .textAlign(this.layout.layoutType === 'grid' ? 'center' : 'left')
+?                         -----
++       .textAlign(this.localLayoutType === 'grid' ? 'center' : 'left')
+?                        ++  +
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -13267,6 +17946,69 @@
 总结来说，修复代码样例通过使用本地状态 (`localFullScreen`) 和监听变化 (`@Watch` 和 `onStyleChange` 方法)，提高了组件的状态管理，使得全屏切换的逻辑更为可靠和健壮。</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class WindowStyle {
+    isFullScreen: boolean = false;
+  }
+  @Entry
+  @Component
+- struct DemoB {
++ struct DemoBFixed {
+?             +++++
+    @State style: WindowStyle = new WindowStyle();
+    build() {
+      Row() {
+        SideBar({ style: this.style })
+        MainContent({ style: this.style })
+        Text('Toggle Full Screen')
+          .onClick(() =&gt; {
+            this.style.isFullScreen = !this.style.isFullScreen;
+          })
+      }
+    }
+  }
+  @Component
+  struct SideBar {
+-   @Link style: WindowStyle;
++   @Link @Watch('onStyleChange') style: WindowStyle;
++   @State localFullScreen: boolean = false;
++   onStyleChange() {
++     this.localFullScreen = this.style.isFullScreen;
++   }
+    build() {
+-     if (this.style.isFullScreen) {
+?              --- ^^^^
++     if (this.localFullScreen) {
+?               ^^^^
+        Text('SideBar Hidden')
+      } else {
+        Text('SideBar Visible')
+      }
+    }
+  }
+  @Component
+  struct MainContent {
+-   @Link style: WindowStyle;
++   @Link @Watch('onStyleChange') style: WindowStyle;
++   @State localFullScreen: boolean = false;
++   onStyleChange() {
++     this.localFullScreen = this.style.isFullScreen;
++   }
+    build() {
+-     if (this.style.isFullScreen) {
+?              --- ^^^^
++     if (this.localFullScreen) {
+?               ^^^^
+        Text('FullScreen Mode')
+      } else {
+        Text('Normal Mode')
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -13382,6 +18124,63 @@
 3. **代码结构**：
    - 修复代码样例通过引入 `@Watch` 和 `onThemeChange` 方法，使得代码的逻辑更加清晰，同时增加了对主题变化的响应能力。这种方式提供了一种更自然的状态管理方式，使组件能够在数据变化时进行反应。
 总结来说，修复代码样例通过引入状态监听和本地状态管理，提升了组件对主题变化的响应能力，避免了直接依赖外部状态，增强了代码的可维护性和可扩展性。</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class ThemeSettings {
+    themeColor: string = 'light';
+  }
+  @Entry
+  @Component
+- struct DemoC {
++ struct DemoCFixed {
+?             +++++
+    @State theme: ThemeSettings = new ThemeSettings();
+    build() {
+      Column() {
+        Header({ theme: this.theme })
+        Footer({ theme: this.theme })
+        Text('Switch Theme')
+          .onClick(() =&gt; {
+            this.theme.themeColor = 'dark';
+          })
+      }
+    }
+  }
+  @Component
+  struct Header {
+-   @Link theme: ThemeSettings;
++   @Link @Watch('onThemeChange') theme: ThemeSettings;
++   @State localThemeColor: string = 'light';
++   onThemeChange() {
++     this.localThemeColor = this.theme.themeColor;
++   }
+    build() {
+      Text('Header')
+-       .backgroundColor(this.theme.themeColor === 'light' ? '#ffffff' : '#000000')
+?                             ^^^^^^^
++       .backgroundColor(this.localThemeColor === 'light' ? '#ffffff' : '#000000')
+?                             ^^^^^^
+    }
+  }
+  @Component
+  struct Footer {
+-   @Link theme: ThemeSettings;
++   @Link @Watch('onThemeChange') theme: ThemeSettings;
++   @State localThemeColor: string = 'light';
++   onThemeChange() {
++     this.localThemeColor = this.theme.themeColor;
++   }
+    build() {
+      Text('Footer')
+-       .backgroundColor(this.theme.themeColor === 'light' ? '#ffffff' : '#000000')
+?                             ^^^^^^^
++       .backgroundColor(this.localThemeColor === 'light' ? '#ffffff' : '#000000')
+?                             ^^^^^^
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -13505,6 +18304,63 @@
 总结来说，修复代码样例通过引入局部状态和事件处理，使得组件能够更好地响应和管理 `ViewMode` 的变化，提升了程序的可靠性和可维护性。</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class ViewMode {
+    displayMode: string = 'card';
+  }
+  @Entry
+  @Component
+- struct DemoD {
++ struct DemoDFixed {
+?             +++++
+    @State view: ViewMode = new ViewMode();
+    build() {
+      Column() {
+        ListView({ mode: this.view })
+        GridView({ mode: this.view })
+        Text('Switch Display Mode')
+          .onClick(() =&gt; {
+            this.view.displayMode = 'list';
+          })
+      }
+    }
+  }
+  @Component
+  struct ListView {
+-   @Link mode: ViewMode;
++   @Link @Watch('onModeChange') mode: ViewMode;
++   @State localDisplayMode: string = 'card';
++   onModeChange() {
++     this.localDisplayMode = this.mode.displayMode;
++   }
+    build() {
+      Text('ListView')
+-       .visible(this.mode.displayMode === 'list')
+?                     ^ ^^^^
++       .visible(this.localDisplayMode === 'list')
+?                     ^ ^^^^
+    }
+  }
+  @Component
+  struct GridView {
+-   @Link mode: ViewMode;
++   @Link @Watch('onModeChange') mode: ViewMode;
++   @State localDisplayMode: string = 'card';
++   onModeChange() {
++     this.localDisplayMode = this.mode.displayMode;
++   }
+    build() {
+      Text('GridView')
+-       .visible(this.mode.displayMode === 'card')
+?                     ^ ^^^^
++       .visible(this.localDisplayMode === 'card')
+?                     ^ ^^^^
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13634,6 +18490,69 @@
 这些改动共同提高了代码的可维护性和灵活性，使得每个组件更加独立，能够处理自己的状态，同时监听和响应父组件传入的状态变化。</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class NotificationSettings {
+    enableSound: boolean = true;
+  }
+  @Entry
+  @Component
+- struct DemoE {
++ struct DemoEFixed {
+?             +++++
+    @State settings: NotificationSettings = new NotificationSettings();
+    build() {
+      Column() {
+        SoundControl({ settings: this.settings })
+        VibrationControl({ settings: this.settings })
+        Text('Toggle Sound')
+          .onClick(() =&gt; {
+            this.settings.enableSound = !this.settings.enableSound;
+          })
+      }
+    }
+  }
+  @Component
+  struct SoundControl {
+-   @Link settings: NotificationSettings;
++   @Link @Watch('onSettingsChange') settings: NotificationSettings;
++   @State localEnableSound: boolean = true;
++   onSettingsChange() {
++     this.localEnableSound = this.settings.enableSound;
++   }
+    build() {
+-     if (this.settings.enableSound) {
+?              ^^^^^^^^^^
++     if (this.localEnableSound) {
+?              ^^^^^^
+        Text('Sound On')
+      } else {
+        Text('Sound Off')
+      }
+    }
+  }
+  @Component
+  struct VibrationControl {
+-   @Link settings: NotificationSettings;
++   @Link @Watch('onSettingsChange') settings: NotificationSettings;
++   @State localEnableSound: boolean = true;
++   onSettingsChange() {
++     this.localEnableSound = this.settings.enableSound;
++   }
+    build() {
+-     if (this.settings.enableSound) {
+?              ^^^^^^^^^^
++     if (this.localEnableSound) {
+?              ^^^^^^
+        Text('Vibration Enabled')
+      } else {
+        Text('Vibration Disabled')
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13667,6 +18586,14 @@
 1. **增加了第三个参数**：在修复代码中，`ForEach`函数增加了一个额外的参数。这一参数是一个函数 `(task) =&gt; task.id`，用于提供一个唯一的标识符，这样使得可以基于任务的 ID 来区分每个任务项。这个变化有助于提高列表渲染的性能和准确性，尤其是在处理动态数据更新时。
 2. **提高了可用性和可维护性**：通过提供一个唯一的键（在这个案例中是 `task.id`），修复后的代码可以在 React 等框架中更好地跟踪 DOM 元素的变化，从而减少不必要的重新渲染。这种做法提高了代码的可用性和可维护性。
 总结而言，修复代码通过增加一个用于唯一标识任务项的参数，改善了任务渲染的性能和准确性。</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { Grid() { ForEach(this.tasks, (task, index) =&gt; { TaskItem(task); }); } }
++ build() { Grid() { ForEach(this.tasks, (task, index) =&gt; { TaskItem(task); }, (task) =&gt; task.id); } }
+?                                                                            +++++++++++++++++++
+</t>
         </is>
       </c>
     </row>
@@ -13707,6 +18634,14 @@
 总结：修复代码样例通过增加一个用于处理成员的额外回调函数，使得 `ForEach` 能够实现更复杂的逻辑，比如在渲染时依靠成员的 `email` 属性来确保每个 `MemberItem` 的唯一性或进行排序。这是问题代码样例的改进点。</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { List() { ForEach(this.members, (member, idx) =&gt; { MemberItem(member); }); } }
++ build() { List() { ForEach(this.members, (member, idx) =&gt; { MemberItem(member); }, (member) =&gt; member.email); } }
+?                                                                                  ++++++++++++++++++++++++++
+</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13740,6 +18675,14 @@
 1. **添加了排序比较函数**：修复代码中 `ForEach` 函数有一个额外的参数 `(note) =&gt; note.timestamp`，这是一个用于排序的比较函数。它的作用是根据每个 `note` 的 `timestamp` 属性来排序，这样可以确保列表中的通知项按时间顺序排列。
 2. **代码结构**：修复后的代码在逻辑上更加清晰，因为它明确了如何处理 `this.notifications` 集合的顺序。问题代码没有对通知项进行排序的功能，因此可能导致显示的顺序不符合预期。
 总结：修复代码样例通过添加排序比较函数来改进了通知项的展示顺序。</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { Row() { ForEach(this.notifications, (note) =&gt; { NotificationItem(note); }); } }
++ build() { Row() { ForEach(this.notifications, (note) =&gt; { NotificationItem(note); }, (note) =&gt; note.timestamp); } }
+?                                                                                    ++++++++++++++++++++++++++
+</t>
         </is>
       </c>
     </row>
@@ -13800,6 +18743,14 @@
 差异在于修复代码样例中额外引入了一个通过 `msg.uuid` 确定唯一标识符的闭包，从而使得 `ForEach` 可以更有效地管理和识别每个消息项。</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { VStack() { ForEach(this.messages, (msg, index) =&gt; { MessageBubble(msg); }); } }
++ build() { VStack() { ForEach(this.messages, (msg, index) =&gt; { MessageBubble(msg); }, (msg) =&gt; msg.uuid); } }
+?                                                                                    +++++++++++++++++++
+</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13839,6 +18790,14 @@
 总体而言，修复代码样例通过增加唯一标识符参数增强了 `ForEach` 的功能，使得在处理 `this.events` 数组时更为高效。</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- build() { HStack() { ForEach(this.events, (event, idx) =&gt; { EventItem(event); }); } }
++ build() { HStack() { ForEach(this.events, (event, idx) =&gt; { EventItem(event); }, (event) =&gt; event.eventID); } }
+?                                                                                ++++++++++++++++++++++++++
+</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13884,6 +18843,17 @@
 - 直接影响的是 `FileA.ets` 中的导入路径，由原来的 `FileB.ets` 更改为 `FileC.ets`，而 `FileB.ets` 仍然依赖于 `FileA.ets`。这种变化打破了循环依赖的问题，并且确保了 `FileA.ets` 的依赖关系是指向一个没有出现循环依赖的文件。</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // FileA.ets
+- import {} from './FileB.ets';
+?                       ^
++ import {} from './FileC.ets';
+?                       ^
+  // FileB.ets
+  import {} from './FileA.ets';</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13927,6 +18897,17 @@
    - `Beta.ets` 文件在修复代码样例中保持不变，仍然是 `import {} from './Alpha.ets';`。
    - 这表明 `Beta.ets` 依然导入 `Alpha.ets`，但由于 `Alpha.ets` 不再导入 `Beta.ets`，这解决了循环依赖的问题。
 总结：主要的差异在于 `Alpha.ets` 文件中的导入语句，修复后的代码通过将 `Beta.ets` 替换为 `Gamma.ets`，成功消除了循环依赖。</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // Alpha.ets
+- import {} from './Beta.ets';
+?                   ^^^
++ import {} from './Gamma.ets';
+?                   ^^^^
+  // Beta.ets
+  import {} from './Alpha.ets';</t>
         </is>
       </c>
     </row>
@@ -13988,6 +18969,17 @@
 综上所述，修复代码样例的主要差异在于 `Module1.ets` 的导入部分，成功移除了 `Module2.ets` 的导入，改为导入 `Module3.ets`，以解除循环依赖问题。</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // Module1.ets
+- import {} from './Module2.ets';
+?                         ^
++ import {} from './Module3.ets';
+?                         ^
+  // Module2.ets
+  import {} from './Module1.ets';</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -14040,6 +19032,17 @@
      import {} from './X.ets';
      ```
 综上所述，修复过程中唯一的变化是 `X.ets` 文件中从 `Y.ets` 的导入被替换为从 `Z.ets` 的导入。这样修复了原本可能导致的循环依赖问题。</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // X.ets
+- import {} from './Y.ets';
+?                   ^
++ import {} from './Z.ets';
+?                   ^
+  // Y.ets
+  import {} from './X.ets';</t>
         </is>
       </c>
     </row>
@@ -14101,6 +19104,17 @@
 综上所述，在修复过程中，主要的变化是在 `ComponentA.ets` 中，依赖从 `ComponentB.ets` 更改为 `ComponentC.ets`，而 `ComponentB.ets` 仍然保留对 `ComponentA.ets` 的依赖。这样做的目的是避免循环依赖问题。</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // ComponentA.ets
+- import {} from './ComponentB.ets';
+?                            ^
++ import {} from './ComponentC.ets';
+?                            ^
+  // ComponentB.ets
+  import {} from './ComponentA.ets';</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -14162,6 +19176,23 @@
 总结来说，修复代码样例通过提取目标项的引用提升了性能，减少了不必要的重复计算，同时也提高了代码的可读性。</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Items {
+    static collection: string[] = ['apple', 'banana', 'cherry'];
+  }
+  function findItem(targetIndex: number): boolean {
++   const targetItem = Items.collection[targetIndex]; // 提取到循环外
+    for (let i = 0; i &lt; Items.collection.length; i++) {
+-     if (Items.collection[i] === Items.collection[targetIndex]) { // 重复引用
++     if (Items.collection[i] === targetItem) {
+        return true;
+      }
+    }
+    return false;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -14221,6 +19252,22 @@
 综上所述，修复代码样例通过提取常量到循环外部，提升了代码的性能和可读性，这是与问题代码样例之间的主要差异。</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Scores {
+    static values: number[] = [90, 80, 85, 70, 95];
+  }
+  function calculateAverage(bonus: number): number {
+    let total: number = 0;
++   const bonusValue = Scores.values[bonus];  // 提取到循环外
+    for (let j = 0; j &lt; Scores.values.length; j++) {
+-     total += Scores.values[bonus] * j;  // 每次循环都访问相同值
++     total += bonusValue * j;
+    }
+    return total / Scores.values.length;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -14282,6 +19329,23 @@
 综上所述，修复代码样例通过减少重复访问、提高可读性和优化性能解决了问题代码样例的不足之处。</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Config {
+    static limits: number[] = [10, 20, 30, 40];
+  }
+  function checkValidity(index: number): boolean {
++   const limitThreshold = Config.limits[index];  // 提取到循环外
+    for (let value of Config.limits) {
+-     if (Config.limits[index] &gt; value) {  // 不变值反复访问
++     if (limitThreshold &gt; value) {
+        return false;
+      }
+    }
+    return true;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -14339,6 +19403,22 @@
 总之，修复代码样例通过减少重复计算、提升效率和改善可读性来改进原始代码。</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Data {
+    static values: number[] = [7, 14, 21, 28];
+  }
+  function multiplyValues(multiplier: number): number {
+    let product: number = 1;
++   const multiplierValue = Data.values[multiplier];  // 提取到循环外
+    for (let n of Data.values) {
+-     product *= Data.values[multiplier] + n;  // 固定值重复使用
++     product *= multiplierValue + n;
+    }
+    return product;
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14396,6 +19476,23 @@
 2. **性能提升**：
    - 修复后的代码在循环内部只使用 `targetDimension` 进行比较，而不是每次都从 `Matrix.dimensions` 数组中获取值。这减少了数组访问的次数，从而提高了效率。
 可以总结为：修复代码通过提取变量来优化性能，避免了重复的数组访问，使代码更加高效并且可读性更强。</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Matrix {
+    static dimensions: number[] = [5, 10, 15, 20];
+  }
+  function verifyDimension(target: number): boolean {
++   const targetDimension = Matrix.dimensions[target]; // 提取到循环外
+    for (let x = 0; x &lt; Matrix.dimensions.length; x++) {
+-     if (Matrix.dimensions[target] === Matrix.dimensions[x]) { // 每次循环都访问相同值
++     if (targetDimension === Matrix.dimensions[x]) {
+        return true;
+      }
+    }
+    return false;
+  }</t>
         </is>
       </c>
     </row>
@@ -14446,6 +19543,15 @@
 总的来说，修复代码样例比问题代码样例更具适应性和灵活性，通过使用 `i18n` 模块来处理与地区和语言相关的日期时间信息，能够提供更符合目标用户的输出。</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>- var userLocale = 'en-US';
+- var dateTime = new Date().toLocaleString(userLocale);
++ import i18n from '@ohos.i18n';
++ let calendar = i18n.getCalendar('en-US');
++ calendar.getTime()</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14492,6 +19598,16 @@
    - **问题代码**：返回的是一个格式化的本地时间字符串。
    - **修复代码**：返回的是一个日历对象的时间，这可能包含更丰富的日期和时间信息，具体格式依赖于 `calendar.getTime()` 的实现。
 综上所述，修复代码通过引入国际化库并使用更为适合本地化需求的方法来获取时间，以便提供更准确、本地化的时间响应。</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>+ import i18n from '@ohos.i18n';
+  function getLocalTime() {
+-     return new Date().toLocaleString();
++     let calendar = i18n.getCalendar(i18n.getSystemLocale());
++     return calendar.getTime();
+  }</t>
         </is>
       </c>
     </row>
@@ -14543,6 +19659,15 @@
 修复代码样例增加了对国际化模块的依赖，并通过获取日历对象和设置时区来提高时间处理的准确性。这种改进使得日期和时间的处理更加专业和符合地区性需求。</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>- let regionTime = new Intl.DateTimeFormat('de-DE').format(new Date());
++ import i18n from '@ohos.i18n';
++ let calendar = i18n.getCalendar('de-DE');
++ calendar.setTimeZone(i18n.getTimeZone().getID());
++ calendar.getTime();</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14588,6 +19713,14 @@
    - 问题代码中的方法是直接调用 `new Date().toLocaleTimeString()`。
    - 修复代码中的方法是通过`i18n`库的API来获取时间，这可能会涉及不同的处理方式，比如支持更多的本地化需求。
 总结来说，修复代码通过引入`i18n`库并使用其方法，增强了代码的国际化和灵活性，而不是仅仅依赖JavaScript内置的时间格式化功能。</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>- const formattedTime = new Date().toLocaleTimeString('fr-FR');
++ import i18n from '@ohos.i18n';
++ let calendar = i18n.getCalendar('fr-FR');
++ calendar.getTime();</t>
         </is>
       </c>
     </row>
@@ -14641,6 +19774,15 @@
 - 使用的API和参数也有所变化，显示出对时区处理的更细粒度控制。</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>- let timeZoneName = new Date().toLocaleString('ja-JP', { timeZoneName: 'short' });
++ import i18n from '@ohos.i18n';
++ let calendar = i18n.getCalendar('ja-JP');
++ calendar.setTimeZone('short');
++ calendar.get('zone_offset');</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14771,6 +19913,62 @@
 主要的变化集中在 `Translate` 类的 `@Observed` 装饰器的去掉，以及对 `button_msg` 状态的处理简化上。这些改动使得修复代码更加高效并减少了不必要的状态管理。</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>- @Observed
+  class Translate {
+    translateX: number = 20;
+  }
+  @Component
+  struct Title {
+    build() {
+      Row() {
+        // 本地资源 icon.png
+-       Image($r('app.media.icon'))
++       Image($r('app.media.icon')) 
+?                                  +
+          .width(50)
+          .height(50)
+        Text("Title")
+          .fontSize(20)
+      }
+    }
+  }
+  @Entry
+  @Component
+  struct MyComponent{
+    @State translateObj: Translate = new Translate();
++   // 直接使用一般变量即可
+-   @State button_msg: string = "i am button";
+?  -------
++   button_msg: string = "i am button";
+    build() {
+      Column() {
+        Title()
+        Stack() {
+        }
+        .backgroundColor("black")
+        .width(200)
+        .height(400)
+-       // 这里只是用了状态变量button_msg的值，没有任何写的操作
+        Button(this.button_msg)
+          .onClick(() =&gt; {
+            animateTo({
+              duration: 50
+-           },()=&gt;{
++           }, () =&gt; {
+?             +  +  +
+              this.translateObj.translateX = (this.translateObj.translateX + 50) % 150
+            })
+          })
+      }
+      .translate({
+        x: this.translateObj.translateX
+      })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14857,6 +20055,37 @@
 总的来说，修复代码样例的变化主要是将 `title` 的定义从 `@State` 改为了普通变量，这是为了反映 `title` 不会在组件生命周期内发生变化，而 `position` 仍然使用状态管理来处理动态位置的变化。</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Position {
+    x: number = 0;
+    y: number = 0;
+  }
+  @Component
+  struct MyComponent {
+    @State position: Position = new Position();
++   // title 未发生变化，改为普通变量
+-   @State title: string = "Welcome";
+?  -------
++   title: string = "Welcome";
+    build() {
+      Column() {
+        Text(this.title)
+          .fontSize(24)
+        Button("Move")
+          .onClick(() =&gt; {
+            this.position.x += 10;
+            this.position.y += 10;
+          })
+      }
+      .position({
+        x: this.position.x,
+        y: this.position.y
+      })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14937,6 +20166,33 @@
 这些是修复过程中主要的代码差异，目的是简化状态管理并提高性能，尤其是在 `userName` 这个不会变化的属性上。</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Settings {
+    theme: string = "dark";
+    notificationsEnabled: boolean = true;
+  }
+  @Component
+  struct UserProfile {
+    @State userSettings: Settings = new Settings();
++   // userName 未发生变化，改为普通变量
+-   @State userName: string = "John Doe";
+?  -------
++   userName: string = "John Doe";
+    build() {
+      Column() {
+        Text("User: " + this.userName)
+          .fontSize(18)
+        Toggle("Enable Notifications", this.userSettings.notificationsEnabled)
+          .onChange((value) =&gt; {
+            this.userSettings.notificationsEnabled = value;
+          })
+      }
+      .padding(16)
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15011,6 +20267,31 @@
 2. **状态变量与普通变量的区别**：
    - 由于 `appTitle` 不再是状态变量，它在代码中的行为和更新机制将受到影响。例如，若需要动态更新 `appTitle`，将需要手动触发视图的重绘（如果涉及视图更新）。
 综上所述，主要差异在于 `appTitle` 的状态管理和视图更新机制的改变。</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class Config {
+    apiEndpoint: string = "https://api.example.com";
+    timeout: number = 5000;
+  }
+  @Entry
+  @Component
+  struct AppConfig {
+    @State config: Config = new Config();
++   // appTitle 未发生变化，改为普通变量
+-   @State appTitle: string = "My Application";
+?  -------
++   appTitle: string = "My Application";
+    build() {
+      Column() {
+        Header(this.appTitle)
+        // 配置详情显示
+        ConfigView(this.config)
+      }
+      .padding(20)
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -15098,6 +20379,31 @@
 总体来看，修复代码样例通过将 `welcomeMessage` 改为普通变量，减少了不必要的状态管理，可能提高了代码的性能和可读性。</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  class User {
+    id: number = 1;
+    email: string = "user@example.com";
+  }
+  @Component
+  struct Dashboard {
+    @State currentUser: User = new User();
++   // welcomeMessage 未发生变化，改为普通变量
+-   @State welcomeMessage: string = "Welcome to the Dashboard";
+?  -------
++   welcomeMessage: string = "Welcome to the Dashboard";
+    build() {
+      Column() {
+        Text(this.welcomeMessage)
+          .fontSize(22)
+        // 显示用户信息
+        UserInfo(this.currentUser)
+      }
+      .padding(10)
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15173,6 +20479,29 @@
 整体上，修复代码样例去掉了状态管理部分，从而与原本的逻辑和功能不同。</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct MyComponent {
+-   @State message: string = "";
+    appendMsg(newMsg: String) : string {
+      this.message += newMsg;
+      return this.message;
+    }
+    build() {
+      Column() {
+        Stack() {
+        }
+        .backgroundColor("black")
+        .width(200)
+        .height(400)
+        Button("move")
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15251,6 +20580,33 @@
    - 在问题代码样例中，由于 `notificationCount` 是个状态变量，它的变化可以直接影响 UI 组件的显示。
    - 在修复代码样例中，由于移除了 `@State` 装饰器，`notificationCount` 的变化不会引起 UI 的更新，因此它未在 `build` 方法中使用。
 总结来说，修复代码样例去掉了未使用的状态变量，从而简化了代码。这种简化可以提高代码的可读性和维护性，因为状态变量只在必要时使用。</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct NotificationComponent {
++   // notificationCount 未在 UI 中使用，移除状态变量
+-   @State notificationCount: number = 0;
+?  -------
++   notificationCount: number = 0;
+    incrementNotifications() {
+      this.notificationCount += 1;
+      // 逻辑处理，例如发送通知
+    }
+    doSomething() {
+      // 执行其他逻辑
+    }
+    build() {
+      Column() {
+        Button("Send Notification")
+          .onClick(() =&gt; this.doSomething())
+        // notificationCount 未在 UI 中使用
+      }
+      .padding(10)
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -15340,6 +20696,31 @@
 总结：修复代码样例的主要变化是移除了 `@State` 装饰器，使得 `logMessages` 不再是响应式的状态。这一更改可能简化了变量的管理，但同时也使得它失去了响应式的特性。在当前逻辑中，`logMessages` 实际上是未被使用的，可以考虑进一步改进以更好地利用日志功能。</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct LogComponent {
+-   @State logMessages: string[] = [];
+?  -------
++   logMessages: string[] = [];
+    addLog(message: string) {
+      this.logMessages.push(message);
+      // 执行日志记录操作
+    }
+    doSomething() {
+      // 一些逻辑处理
+    }
+    build() {
+      Column() {
+        Button("执行操作")
+          .onClick(() =&gt; this.doSomething())
+        // `logMessages` 未在 UI 中使用，且未在 UI 调用的函数中使用
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15432,6 +20813,37 @@
 总结：主要的差异是去掉了 `counter` 的 `@State` 装饰器，这使得 `counter` 变为一个普通的属性，不再关联 UI 的状态管理。</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct CounterComponent {
+-   @State counter: number = 0;
+?  -------
++   counter: number = 0;
+    incrementCounter() {
+      this.counter += 1;
+      // 内部逻辑处理，不关联 UI
+    }
+    resetCounter() {
+      this.counter = 0;
+      // 内部逻辑处理，不关联 UI
+    }
+    build() {
+      Column() {
+        Button("开始")
+          .onClick(() =&gt; this.doSomething())
+        Button("停止")
+          .onClick(() =&gt; this.doSomething())
+        // `counter` 未在 UI 中使用，且未在 UI 调用的函数中使用
+      }
+    }
+    doSomething() {
+      // 一些无关的逻辑
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15506,6 +20918,31 @@
 2. **行为逻辑的不变性**：
    - 除了以上变化之外，修复代码样例在 `fetchData`、`build` 和 `doSomething` 函数的逻辑上与问题代码样例保持一致。修复代码没有改变这些函数的实现，依然保留了问题代码中的相同结构和逻辑。
 总结起来，修复代码样例删除了 `@State` 标签，简化了代码结构，但未改变其他函数的实现。这样可能意味着 `data` 不再受状态管理系统的干预，但仍然保留了其作为普通属性的功能。</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct DataFetcher {
+-   @State data: any = null;
+?  -------
++   data: any = null;
+    fetchData() {
+      // 从 API 获取数据并赋值给 `data`
+      this.data = { /* 获取的数据 */ };
+    }
+    build() {
+      Column() {
+        Button("加载数据")
+          .onClick(() =&gt; this.doSomething())
+        // `data` 未在 UI 中使用，且未在 UI 调用的函数中使用
+      }
+    }
+    doSomething() {
+      // 一些无关的逻辑
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -15559,6 +20996,20 @@
 修复代码的主要改动在于明确了 `User` 类的导出，确保类能够被外部模块直接访问，而问题代码由于缺乏明确的 `export`，可能导致类不能被正确导出。修复代码提高了代码的可用性和清晰度。</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>- class User {
++ export class User {
+? +++++++
+    id?: number;
+    name?: string;
+  }
+- // 当前文件 User.ets
+- export * from './User';
+- // 当前文件 User.ets
+- export * as XX from './User';</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15607,6 +21058,19 @@
 综上所述，修复后的代码通过直接逐个导出常量，提升了代码的清晰度和可维护性，同时避免了导出时可能出现的混淆。</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 文件：Constants.ets
+- const MAX_LIMIT = 100;
++ export const MAX_LIMIT = 100;
+? +++++++
+- const MIN_LIMIT = 1;
++ export const MIN_LIMIT = 1;
+? +++++++
+- // 错误地使用了 export * 导出当前模块的定义
+- export * from './Constants';</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15661,6 +21125,23 @@
    - 在**问题代码样例**中，`calculateSum`和`calculateDifference`函数并没有被标记为导出，因此在其他模块中无法使用它们。
    - 在**修复代码样例**中，这两个函数现在可以被其他模块引用，因为它们在定义时就被导出了。
 这种变化确保了该模块的功能（即 `calculateSum` 和 `calculateDifference` 函数）可以被其他模块正确访问。</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 文件：Utility.ets
+- function calculateSum(a: number, b: number): number {
++ export function calculateSum(a: number, b: number): number {
+? +++++++
+    return a + b;
+  }
+- function calculateDifference(a: number, b: number): number {
++ export function calculateDifference(a: number, b: number): number {
+? +++++++
+    return a - b;
+  }
+- // 错误地使用了 export * 导出当前模块的定义
+- export * from './Utility';</t>
         </is>
       </c>
     </row>
@@ -15718,6 +21199,17 @@
 修复代码样例更为精确和清晰，通过显式指明导出的内容，使得代码的意图更为明显，同时去掉了不必要的命名空间导出，提升了代码的可维护性。</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 文件：index.ets
++ export { calculateSum, calculateDifference } from './Utilities';
+- export * from './Utilities';
+- export * as Utils from './Utilities';
+  class App {
+    // 应用的主要逻辑
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15768,6 +21260,19 @@
    - 两者中 `User` 类的定义是相同的，包含 `id` 和 `name` 属性，均为可选的。
 总结：
 修复过程的主要变化是减少了模块的导出方式，避免了不必要的命名空间导出，改为明确导出所需的 `Product`。这样做可以提高代码的清晰度和可管理性。</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>- export * from './Product';
+?        ^
++ export { Product } from './Product';
+?        ^^^^^^^^^^^
+- export * as XX from './Product';
+  class User {
+    id?: number;
+    name?: string;
+  }</t>
         </is>
       </c>
     </row>
@@ -15831,6 +21336,17 @@
 总结来说，修复代码样例相对于问题代码样例的主要差异在于导出的选择性和清晰度，修复代码只有特定的导出，没有导出全部的内容。</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 文件：index.ets
++ export { MAX_VALUE, MIN_VALUE } from './Constants';
+- export * from './Constants';
+- export * as Consts from './Constants';
+  interface Config {
+    // 配置接口定义
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15890,6 +21406,23 @@
 3. **逻辑组织性**：
    - 修复代码样例将输入变化的处理逻辑分离到一个独立的方法中，使得代码的结构更加清晰和可维护。问题代码样例将逻辑写在回调中，导致代码不够整洁。
 综上所述，修复代码样例通过引入 `handleInputChange` 方法，使得输入变化的处理逻辑得以定义和实现，从而改善了代码的可读性和可维护性。</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Component
+  struct TextInputComponent {
++   handleInputChange(value: string) {
++     // 处理输入变化的逻辑
++   }
+    build() {
+      TextInput()
+        .onChange((value) =&gt; {
+-         // 无业务逻辑
++         this.handleInputChange(value)
+        })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -15954,6 +21487,23 @@
 修复代码通过引入一个专门的处理函数，使得事件处理逻辑更具可拓展性和可维护性，而问题代码则缺乏这样的设计，导致无法响应滚动事件的具体业务需求。</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Component
+  struct ListComponent {
++   handleScrollEvent() {
++     // 处理滚动事件的逻辑
++   }
+    build() {
+      List()
+        .onScroll(() =&gt; {
+-         // 无业务逻辑
++         this.handleScrollEvent()
+        })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -16013,6 +21563,23 @@
 综上所述，修复代码样例通过引入一个业务逻辑方法和在事件处理中调用该方法，解决了原始代码中没有实现业务逻辑的问题。</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Component
+  struct MyComponent {
++   doSomething() {
++     //业务逻辑
++   }
+    build() {
+      Button('Click', { type: ButtonType.Normal, stateEffect: true })
+        .onClick(() =&gt; {
+-         // 无业务逻辑
++         this.doSomething()
+        })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16074,6 +21641,25 @@
 2. **方法调用**：
    - 在修复代码的 `build` 方法中，双击手势的 `onAction` 部分现在调用了 `this.handleDoubleTap()`，以便在检测到双击时执行处理逻辑。而在问题代码中，`onAction` 部分是一个空的回调函数，没有实现任何逻辑。
 总结来说，修复代码通过引入一个新的方法和在事件处理器中调用该方法，使得手势的双击事件有了实际的逻辑处理，这提高了代码的可维护性和功能性。</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Component
+  struct GestureComponent {
++   handleDoubleTap() {
++     // 处理双击手势的逻辑
++   }
+    build() {
+      Image('gesture.png')
+        .gesture(TapGesture({ count: 2 })
+          .onAction(() =&gt; {
+-           // 无业务逻辑
++           this.handleDoubleTap()
+          })
+        )
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -16139,6 +21725,23 @@
 总结而言，修复代码样例通过引入一个处理函数、明确参数类型和改进代码结构，增强了代码的可读性和可维护性，同时为后续的业务逻辑处理提供了便利。</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Component
+  struct SwiperComponent {
++   handleSwiperChange(index: number) {
++     // 处理轮播图切换的逻辑
++   }
+    build() {
+      Swiper()
+        .onChange((index) =&gt; {
+-         // 无业务逻辑
++         this.handleSwiperChange(index)
+        })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16260,6 +21863,54 @@
 2. **初始值**：
    - 在问题代码样例中，`price` 属性没有被初始化，因为是通过 `@Link` 默认处理，而在修复代码样例中，`price` 被初始化为 `0`。这在组件创建时提供了一个默认值，避免了潜在的未定义状态。
 总的来说，修复代码样例通过将 `price` 从 `@Link` 改为 `@State` 及给予其默认初始化值，从而实现了更加健壮和独立的状态管理。</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Reusable
+  @Component
+  struct ProductItem {
+    @State name: string = '';
+-   @Link price: number;
++   @State price: number = 0;
+    aboutToReuse(params: Record&lt;string, Object&gt;): void {
+      this.name = params.name as string;
+      this.price = params.price as number;
+    }
+    build() {
+      Column() {
+        Text('产品名称：' + this.name)
+        Text('价格：' + this.price)
+      }
+    }
+  }
+  interface GeneratedTypeLiteralInterface_1 {
+    name: string;
+    price: number;
+  }
+  @Entry
+  @Component
+  struct ProductList {
+    private products: Array&lt;GeneratedTypeLiteralInterface_1&gt; = [];
+    aboutToAppear(): void {
+      // 初始化产品列表
+      this.products = [
+        { name: '商品A', price: 100 },
+        { name: '商品B', price: 200 },
+      ];
+    }
+    build() {
+      Column() {
+        List() {
+          ForEach(this.products, (item: GeneratedTypeLiteralInterface_1) =&gt; {
+            ListItem() {
+              ProductItem({ name: item.name, price: item.price })
+            }
+          })
+        }
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -16406,6 +22057,66 @@
 2. **ItemComponent 的构造逻辑**:
    - 在 `aboutToReuse` 方法中，两段代码均保留了将 `params` 中的值赋给组件状态，但由于修复代码为 `avg` 添加了初始值，因此这一行的逻辑相对而言更为健壮。
 这些更改提升了 `ItemComponent` 组件中 `avg` 状态的默认行为，确保在未提供 `avg` 参数时不会出现未定义的状态。</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 源码文件，请以工程实际为准
+  import { MyDataSource } from './MyDataSource';
+  // 此处为复用的自定义组件
+  @Reusable
+  @Component
+  struct ItemComponent {
+    @State desc: string = '';
+    @State sum: number = 0;
+-   @Link avg: number;
++   @State avg: number = 0;
+    aboutToReuse(params: Record&lt;string, Object&gt;): void {
+      this.desc = params.desc as string;
+      this.sum = params.sum as number;
+      this.avg = params.avg as number;
+    }
+    build() {
+      Column() {
+        Text('子组件' + this.desc)
+          .fontSize(30)
+          .fontWeight(30)
+        Text('结果' + this.sum)
+          .fontSize(30)
+          .fontWeight(30)
+        Text('平均值' + this.avg)
+          .fontSize(30)
+          .fontWeight(30)
+      }
+    }
+  }
+  @Entry
+  @Component
+  struct MyComponent {
+    private data: MyDataSource = new MyDataSource();
+    aboutToAppear(): void {
+      for (let index = 0; index &lt; 20; index++) {
+        this.data.pushData(index.toString())
+      }
+    }
+    build() {
+      Column() {
+        List() {
+          LazyForEach(this.data, (item: string) =&gt; {
+            ListItem() {
+              ItemComponent({ desc: item, sum: 0, avg: 0 })
+            }
+            .width('100%')
+            .height(100)
+          }, (item: string) =&gt; item)
+        }
+        .width('100%')
+        .height('100%')
+      }
+      .width('100%')
+      .height('100%')
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -16540,6 +22251,54 @@
 2. **初始化状态**：
    - 在修复代码样例中，`sender` 被初始化为空字符串 (`''`)，而问题代码样例中没有对其进行初始化。这种初始化有助于避免未定义的状态引起的问题。
 通过这两个变化，修复代码样例增强了组件的状态管理，确保 `sender` 和 `content` 都是作为本地状态进行处理，有助于提高组件的稳定性和可预测性，避免可能的状态共享导致的问题。</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Reusable
+  @Component
+  struct MessageItem {
+-   @Link sender: string;
++   @State sender: string = '';
+    @State content: string = '';
+    aboutToReuse(params: Record&lt;string, Object&gt;): void {
+      this.sender = params.sender as string;
+      this.content = params.content as string;
+    }
+    build() {
+      Column() {
+        Text('发件人：' + this.sender)
+        Text('内容：' + this.content)
+      }
+    }
+  }
+  interface GeneratedTypeLiteralInterface_1 {
+    sender: string;
+    content: string;
+  }
+  @Entry
+  @Component
+  struct MessageList {
+    private messages: Array&lt;GeneratedTypeLiteralInterface_1&gt; = [];
+    aboutToAppear(): void {
+      // 获取消息列表
+      this.messages = [
+        { sender: '张三', content: '你好' },
+        { sender: '李四', content: '下午好' },
+      ];
+    }
+    build() {
+      Column() {
+        List() {
+          ForEach(this.messages, (message: GeneratedTypeLiteralInterface_1) =&gt; {
+            ListItem() {
+              MessageItem({ sender: message.sender, content: message.content })
+            }
+          })
+        }
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -16646,6 +22405,41 @@
 通过这些更改，修复代码样例提高了代码的可读性和维护性，减少了重复代码，使得动画更加流畅（在同一次点击中同时更新两个坐标）。</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct MoveComponent {
+    @State posX: number = 0;
+    @State posY: number = 0;
+-   moveRight() {
+?       -----
++   move() {
+      animateTo({ duration: 500, curve: Curve.Linear }, () =&gt; {
+        this.posX += 50;
+-     });
+-   }
+-   moveDown() {
+-     animateTo({ duration: 500, curve: Curve.Linear }, () =&gt; {
+        this.posY += 50;
+      });
+    }
+    build() {
+      Column() {
+        Image('icon.png')
+          .position({ x: this.posX, y: this.posY })
+        Button('Move')
+          .onClick(() =&gt; {
+-           this.moveRight();
+-           this.moveDown();
+?                    ----
++           this.move();
+          })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16747,6 +22541,45 @@
 总的来说，修复代码样例通过合并宽度和高度的增加逻辑，不仅减少了代码的复杂性，也使得动画处理更为简单和一致。</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct SizeChanger {
+    @State width: number = 100;
+    @State height: number = 100;
+-   increaseWidth() {
+?           ^ ^^^
++   increaseSize() {
+?           ^ ^^
+      animateTo({ duration: 800, curve: Curve.EaseInOut }, () =&gt; {
+        this.width += 50;
+-     });
+-   }
+-   increaseHeight() {
+-     animateTo({ duration: 800, curve: Curve.EaseInOut }, () =&gt; {
+        this.height += 50;
+      });
+    }
+    build() {
+      Column() {
+        Rectangle()
+          .width(this.width)
+          .height(this.height)
+          .backgroundColor(Color.Blue)
+        Button('Increase Size')
+          .onClick(() =&gt; {
+-           this.increaseWidth();
+?                        ^ ^^^
++           this.increaseSize();
+?                        ^ ^^
+-           this.increaseHeight();
+          })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16841,6 +22674,45 @@
 3. **一致性和可维护性**：
    - **修复代码样例**通过合并两个方法，提高了代码的一致性和可维护性，减少了重复代码，使得处理状态变化的逻辑集中在一个地方，改动时更容易管理。
 综上所述，修复后的代码通过整合功能和简化调用，使得代码结构更简洁、更易于理解与维护。</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct MyComponent {
+    @State textWidth: number = 200;
+    @State color: Color = Color.Red;
+-   func1() {
+?       -
++   func() {
+      animateTo({ curve: Curve.Sharp, duration: 1000 }, () =&gt; {
+        this.textWidth = (this.textWidth === 100 ? 200 : 100);
+-     });
+-   }
+-   func2() {
+-     animateTo({ curve: Curve.Sharp, duration: 1000 }, () =&gt; {
+        this.color = (this.color === Color.Yellow ? Color.Red : Color.Yellow);
+      });
+    }
+    build() {
+      Column() {
+        Row()
+          .width(this.textWidth)
+          .height(10)
+          .backgroundColor(this.color)
+        Text('click')
+          .onClick(() =&gt; {
+-           this.func1();
+?                    -
++           this.func();
+-           this.func2();
+          })
+      }
+      .width('100%')
+      .height('100%')
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -16939,6 +22811,45 @@
 综上所述，修复代码通过简化操作、合并逻辑和减少代码重复性，使得整体实现更加清晰和高效。</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct OpacityChanger {
+    @State opacity1: number = 1;
+    @State opacity2: number = 1;
+-   fadeOutFirst() {
+?          ^^^^
++   fadeOutBoth() {
+?          ^^ +
+      animateTo({ duration: 600 }, () =&gt; {
+        this.opacity1 = 0;
+-     });
+-   }
+-   fadeOutSecond() {
+-     animateTo({ duration: 600 }, () =&gt; {
+        this.opacity2 = 0;
+      });
+    }
+    build() {
+      Column() {
+        Text('First Text')
+          .opacity(this.opacity1)
+        Text('Second Text')
+          .opacity(this.opacity2)
+        Button('Fade Out')
+          .onClick(() =&gt; {
+-           this.fadeOutFirst();
+?                       ^^^^
++           this.fadeOutBoth();
+?                       ^^ +
+-           this.fadeOutSecond();
+          })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -17034,6 +22945,45 @@
 总体而言，修复代码通过合并旋转逻辑和优化方法调用，提升了代码的简洁性和可读性，同时实现了相同的功能。</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct RotateComponent {
+    @State angle1: number = 0;
+    @State angle2: number = 0;
+-   rotateFirst() {
+?         ^^^^
++   rotateBoth() {
+?         ^^ +
+      animateTo({ duration: 700, curve: Curve.Sharp }, () =&gt; {
+        this.angle1 += 45;
+-     });
+-   }
+-   rotateSecond() {
+-     animateTo({ duration: 700, curve: Curve.Sharp }, () =&gt; {
+        this.angle2 += 45;
+      });
+    }
+    build() {
+      Column() {
+        Image('image1.png')
+          .rotate(this.angle1)
+        Image('image2.png')
+          .rotate(this.angle2)
+        Button('Rotate Images')
+          .onClick(() =&gt; {
+-           this.rotateFirst();
+?                      ^^^^
++           this.rotateBoth();
+?                      ^^ +
+-           this.rotateSecond();
+          })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -17094,6 +23044,24 @@
    - 原问题代码中使用了 `syncLoad(true)`，表示同步加载大图片。
    - 修复代码中移除了这一行，改为使用默认的异步加载方式。
 这样，修复代码样例通过移除同步加载的声明，使得图片的加载方式变为异步，从而提高了性能和用户体验。</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct LargeImageComponent {
+    build() {
+      Column() {
+        // 本地高清图片 hd_image.png
+        Image($r('app.media.hd_image'))
+          .width('100%')
+          .height(200)
+-         .syncLoad(true) // 同步加载大图片
++         // 移除 syncLoad，使用异步加载
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -17156,6 +23124,25 @@
 1. **syncLoad属性的移除**：
    - 问题代码样例中包含了 `.syncLoad(true)`，而修复代码样例中则去掉了这个属性。
 综上所述，修复代码样例仅仅是移除了 `syncLoad(true)` 这一行。这可能是出于对性能或加载方式的优化。</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct MyComponent {
+    build() {
+      Row() {
+        // 本地图片4k.png
+        Image($r('app.media.4k'))
+          .border({ width: 1 })
+          .borderStyle(BorderStyle.Dashed)
+          .height(100)
+          .width(100)
+-         .syncLoad(true)
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -17231,6 +23218,27 @@
   // 移除 syncLoad，使用异步加载
   ```
 总结：修复代码样例通过移除同步加载功能，采用异步加载图片，提高了代码的效率和响应性。</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct BackgroundImageComponent {
+    build() {
+      Stack() {
+        // 网络大图片
+        Image('https://example.com/large-background.jpg')
+          .width('100%')
+          .height('100%')
+-         .syncLoad(true) // 同步加载大图片
++         // 移除 syncLoad，使用异步加载
+        Text('欢迎使用我们的应用')
+          .fontSize(24)
+          .fontColor(Color.White)
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -17369,6 +23377,59 @@
 通过这些更改，修复代码样例确保了 `ProductItem` 组件能够在重用时正确地获取到其对应的价格，从而提高了组件的灵活性和可维护性。修复后，每个 `ProductItem` 实例可以通过价格映射来查找其价格，而不是在 `ProductList` 中进行价格设置，从而简化了状态管理。</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Reusable
+  @Component
+  struct ProductItem {
+    @State name: string = '';
+    @State price: number = 0;
++   @State prices: Map&lt;string, number&gt; = new Map&lt;string, number&gt;()
+    aboutToReuse(params: Record&lt;string, Object&gt;): void {
+      this.name = params.name as string;
+-     this.price = params.price as number;
++     const prices = params.prices as Map&lt;string, number&gt;
++     this.price = prices.get(this.name) || 0
+    }
+    build() {
+      Column() {
+        Text('产品名称：' + this.name)
+        Text('价格：' + this.price)
+      }
+    }
+  }
+  @Entry
+  @Component
+  struct ProductList {
+    private products: string[] = ['商品A', '商品B', '商品C'];
+    private prices: Map&lt;string, number&gt; = new Map();
+    // 模拟一个耗时的价格计算函数
+    calculatePrice(productName: string): number {
+      let price = 0;
+      for (let i = 0; i &lt; 100000; i++) {
+        price += i;
+      }
+      return price;
+    }
+    aboutToAppear() {
+      this.products.forEach((product) =&gt; {
+        const price = this.calculatePrice(product);
+        this.prices.set(product, price);
+      });
+    }
+    build() {
+      Column() {
+        ForEach(this.products, (product: string) =&gt; {
+-         ProductItem({ name: product, price: this.prices.get(product) || 0 })
+?                                                        -------------------
++         ProductItem({ name: product, prices: this.prices})
+?                                           +
+        }, (product: string) =&gt; product)
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -17530,6 +23591,79 @@
    - 通过将`count`改为异步函数，修复代码能够在执行耗时操作时不阻塞主线程，而在工作线程中完成计算。
    - 问题代码则在组件绘制过程中，会反复进行耗时操作，可能导致用户体验不佳。
 总体而言，修复代码通过引入状态管理和异步处理来优化计算过程，提升了性能，减少了重复工作，并改善了用户体验。</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 源码文件，请以工程实际为准
+  import { MyDataSource } from './MyDataSource';
+- // 此处为复用的自定义组件
+  @Reusable
+  @Component
+  struct ChildComponent {
+    @State desc: string = '';
+    @State sum: number = 0;
+    aboutToReuse(params: Record&lt;string, Object&gt;): void {
+      this.desc = params.desc as string;
+      this.sum = params.sum as number;
+    }
+    build() {
+      Column() {
+        Text('子组件' + this.desc)
+          .fontSize(30)
+          .fontWeight(30)
+        Text('结果' + this.sum)
+          .fontSize(30)
+          .fontWeight(30)
+      }
+    }
+  }
+  @Entry
+  @Component
+  struct MyComponent{
+    private data: MyDataSource = new MyDataSource();
++   @State sum: number = 0;
+    aboutToAppear(): void {
+      for (let index = 0; index &lt; 20; index++) {
+        this.data.pushData(index.toString())
+      }
++     // 执行该异步函数
++     this.count();
+    }
+-   // 真实场景的函数中可能存在未知的耗时操作逻辑，此处用循环函数模拟耗时操作
+-   count(): number {
++   // 模拟耗时操作逻辑
++   async count() {
+      let temp: number = 0;
+      for (let index = 0; index &lt; 10000; index++) {
+        temp += index;
+      }
+-     return temp;
++     // 将结果放入状态变量中
++     this.sum = temp;
+    }
+    build() {
+      Column() {
+        List() {
+          LazyForEach(this.data, (item: string) =&gt; {
+            ListItem() {
+-             // 此处sum参数是函数获取的，实际开发场景无法预料该函数可能出现的耗时操作，每次进行组件复用都会重复触发此函数的调用
++             // 子组件的传参通过状态变量进行
+-             ChildComponent({ desc: item, sum: this.count() })
+?                                                    ^^ ^^^^
++             ChildComponent({ desc: item, sum: this.sum })
+?                                                    ^ ^
+            }
+            .width('100%')
+            .height(100)
+          }, (item: string) =&gt; item)
+        }
++       .width('100%')
+        .height('100%')
+-       .width('100%')
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -17638,6 +23772,51 @@
    - 在问题代码样例中，拖动距离的设置为 `50`，这超过了阈值 `10`。
    - 在修复代码样例中，拖动距离的设置被修改为 `5`，这在阈值 `10` 以内。
 这意味着，修复代码样例通过将拖动距离的设置从 `50` 修改为 `5`，确保了设定的距离在规定的阈值以内。其他部分的代码逻辑、结构和功能没有发生变化。</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct DraggableBox {
+    @State offsetX: number = 0;
+    @State offsetY: number = 0;
+    private panOption: PanGestureOptions = new PanGestureOptions({ direction: PanDirection.All });
+    build() {
+      Column() {
+        Rectangle()
+          .width(100)
+          .height(100)
+          .backgroundColor(Color.Blue)
+          .translate({ x: this.offsetX, y: this.offsetY })
+          .gesture(
+            PanGesture(this.panOption)
+              .onActionStart(() =&gt; {
+                console.info('Pan started');
+              })
+              .onActionUpdate((event: GestureEvent) =&gt; {
+                if (event) {
+                  this.offsetX += event.offsetX;
+                  this.offsetY += event.offsetY;
+                }
+              })
+              .onActionEnd(() =&gt; {
+                console.info('Pan ended');
+              })
+          )
+        Button('设置拖动距离')
+          .onClick(() =&gt; {
+-           // 设定的距离超过阈值10
+?                   ^^
++           // 设定的距离在阈值10以内
+?                   ^    ++
+-           this.panOption.setDistance(50);
+?                                       -
++           this.panOption.setDistance(5);
+          })
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -17771,6 +23950,66 @@
 总结，这些变化包括了增强的注释说明和对手势触发条件的具体化设置。</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import { hiTraceMeter } from '@kit.PerformanceAnalysisKit'
+  @Entry
+  @Component
+  struct PanGestureExample {
+    @State offsetX: number = 0
+    @State offsetY: number = 0
+    @State positionX: number = 0
+    @State positionY: number = 0
+    private panOption: PanGestureOptions = new PanGestureOptions({ direction: PanDirection.Left | PanDirection.Right })
+    build() {
+      Column() {
+        Column() {
+          Text('PanGesture offset:\nX: ' + this.offsetX + '\n' + 'Y: ' + this.offsetY)
+        }
+        .height(200)
+        .width(300)
+        .padding(20)
+        .border({ width: 3 })
+        .margin(50)
+-       .translate({ x: this.offsetX, y: this.offsetY, z: 0 })
++       .translate({ x: this.offsetX, y: this.offsetY, z: 0 }) // 以组件左上角为坐标原点进行移动
+?                                                             +++++++++++++++++++
+        // 左右拖动触发该手势事件
+        .gesture(
+          PanGesture(this.panOption)
+            .onActionStart((event: GestureEvent) =&gt; {
+              console.info('Pan start')
+              hiTraceMeter.startTrace("PanGesture", 1)
+            })
+            .onActionUpdate((event: GestureEvent) =&gt; {
+              if (event) {
+                this.offsetX = this.positionX + event.offsetX
+                this.offsetY = this.positionY + event.offsetY
+              }
+            })
+            .onActionEnd(() =&gt; {
+              this.positionX = this.offsetX
+              this.positionY = this.offsetY
+              console.info('Pan end')
+              hiTraceMeter.finishTrace("PanGesture", 1)
+            })
+        )
+        Button('修改PanGesture触发条件')
+          .onClick(() =&gt; {
+-           // 设定的距离超过阈值10
+?                   ^^
++           // 设定的距离在阈值10以内
+?                   ^    ++
+-           this.panOption.setDistance(100)
+?                                      ^^^
++           this.panOption.setDistance(4)
+?                                      ^
+          })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17832,6 +24071,27 @@
 3. **可读性提升**：
    - 修复后的代码提高了可读性和可维护性，结构更加扁平，避免了不必要的嵌套层级，使得理解和修改变得更加直接。
 总体来说，修复代码通过减少不必要的嵌套组件，使得代码更加简单、易懂，并且降低了复杂性。</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ExampleComponent {
+    build() {
+      Column() {
+-       // 第一层无属性的 Column
+-       Column() {
+-         // 第二层无属性的 Column
+-         Column() {
+-           Text('Hello World')
+? ----
++       Text('Hello World')
+-         }
+-       }
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -17919,6 +24179,30 @@
 总结来说，修复代码样例的主要改动是减少了多余的 `Flex()` 嵌套层级，使得代码结构更加简洁明了。</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ImageGallery {
+    build() {
+      Scroll() {
+        Flex() {
+-         Flex() {
+-           Flex() {
+-             Image($r('app.media.image1'))
+? ----
++         Image($r('app.media.image1'))
+-             Image($r('app.media.image2'))
+? ----
++         Image($r('app.media.image2'))
+-           }
+-         }
+        }
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -18003,6 +24287,29 @@
 总结来说，修复代码样例通过简化组件嵌套，提升了代码的可读性，并保持了相同的功能。</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ListExample {
+    build() {
+      List() {
+        ForEach([1, 2, 3], (item) =&gt; {
+          ListItem() {
+-           Stack() {
+-             Stack() {
+-               Text('Item ' + item)
+? ----
++           Text('Item ' + item)
+-             }
+-           }
+          }
+        })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18079,6 +24386,28 @@
 总结：修复代码通过简化嵌套结构，使代码更加清晰和简洁，同时保持了按钮的布局。</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ButtonGroup {
+    build() {
+      Row() {
+-       Row() {
+-         Row() {
+-           Button('Button 1')
+? ----
++       Button('Button 1')
+-           Button('Button 2')
+? ----
++       Button('Button 2')
+-         }
+-       }
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -18151,6 +24480,36 @@
 3. **重新排列了一些方法调用**：
    - 在修复代码样例中，`borderRadius(8)`和`backgroundColor(Color.Gray)` 方法调用从 `Column` 的外部移到 `Column` 的内部，被平移掉了，保持了简洁性。
 总结：修复代码样例优化了结构，将不必要的嵌套去掉，使得代码更简洁，同时也调整了属性的应用，使得背景颜色等样式直接应用于 `Image` 组件。</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ProfileCard {
+    build() {
+      Column() {
+-       Stack() {
+-         Stack() {
+-           Image($r('app.media.avatar'))
+? ----
++       Image($r('app.media.avatar'))
+-             .width(100)
+? ----
++         .width(100)
+-             .height(100)
+? ----
++         .height(100)
+-         }
+          .backgroundColor(Color.White)
+-       }
+-       .padding(10)
+      }
++     .padding(10)
+      .borderRadius(8)
+      .backgroundColor(Color.Gray)
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -18234,6 +24593,36 @@
 3. **代码的简洁性**：
    - 整体来看，修复代码样例更简洁、可读性更强，去掉了冗余的组件嵌套。
 总结：修复后的代码通过减少不必要的组件嵌套和调整 `padding` 的位置，提升了代码清晰度和可维护性。</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct CardList {
+    build() {
+      List() {
+        ForEach([1, 2, 3], (item) =&gt; {
+          ListItem() {
+            Column() {
+-             Column() {
+-               Column() {
+-                 Text('Card ' + item)
+? ----
++             Text('Card ' + item)
+-               }
+                .padding(10)
+-             }
+-             .backgroundColor(Color.White)
+            }
++           .backgroundColor(Color.White)
+            .borderRadius(8)
+            .margin(5)
+          }
+        })
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -18347,6 +24736,57 @@
 总结来说，修复代码样例通过去掉多层嵌套的 `Flex` 组件，使得布局更为简洁，同时提升了代码的可读性和维护性。</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct MyComponent{
+    @State number: Number[] = Array.from(Array&lt;number&gt;(1000), (val, i) =&gt; i);
+    scroller: Scroller = new Scroller()
+    build() {
+      Column() {
+        Grid(this.scroller) {
+          ForEach(this.number, (item: number) =&gt; {
+            GridItem() {
+-             Flex() {
+-               Flex() {
+-                 Flex() {
+-                   Text(item.toString())
+? ------
++             Text(item.toString())
+-                     .fontSize(16)
+? ------
++               .fontSize(16)
+-                     .backgroundColor(0xF9CF93)
+? ------
++               .backgroundColor(0xF9CF93)
+-                     .width('100%')
+? ------
++               .width('100%')
+-                     .height(80)
+? ------
++               .height(80)
+-                     .textAlign(TextAlign.Center)
+? ------
++               .textAlign(TextAlign.Center)
+-                     .border({width:1})
+? ------
++               .border({width:1})
+-                 }
+-               }
+-             }
+            }
+          }, (item:string) =&gt; item)
+        }
+        .columnsTemplate('1fr 1fr 1fr 1fr 1fr')
+        .columnsGap(0)
+        .rowsGap(0)
+        .size({ width: "100%", height: "100%" })
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -18421,6 +24861,35 @@
 以上改动简化了代码的层次结构，提高了可读性和易管理性。</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct NestedButtons {
+    build() {
+      Column() {
+        Flex() {
+-         Flex() {
+-           Flex() {
+-             Button('Button A')
+? ----
++         Button('Button A')
+-               .fontSize(16)
+? ----
++           .fontSize(16)
+-           }
+-           .justifyContent(FlexAlign.Center)
+-         }
+-         .alignItems(FlexAlign.Center)
+        }
++       .justifyContent(FlexAlign.Center)
++       .alignItems(FlexAlign.Center)
+        .backgroundColor(Color.LightGray)
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -18492,6 +24961,39 @@
 3. **去除额外的包装**：
    - 原代码中，`Rectangle` 被放置在多层 `Stack` 中，导致了美观性和可读性问题。修复代码通过去除多层嵌套，使得 `Rectangle` 的属性与其本身位置关联更加明确。
 总结来说，修复代码通过简化层次结构、直接将样式属性应用于`Rectangle`，提高了代码的可读性，同时提升了布局的清晰性。</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ComplexLayout {
+    build() {
+      Stack() {
+-       Stack() {
+-         Stack() {
+-           Rectangle()
+? ----
++       Rectangle()
+-             .width(100)
+? ----
++         .width(100)
+-             .height(100)
+? ----
++         .height(100)
+-             .backgroundColor(Color.Red)
+? ----
++         .backgroundColor(Color.Red)
+-         }
+          .padding(10)
+-       }
+-       .borderRadius(10)
++         .borderRadius(10)
+? ++
+      }
+      .shadow({ color: Color.Black, radius: 5, offset: { x: 0, y: 2 } })
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -18580,6 +25082,62 @@
 - 最大的变化是移除了冗余的 `Stack` 组件，通过直接使用 `Text` 组件提高了代码的简练和可维护性。</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>- @Entry
++ @Entry  
+?       ++
+- @Component
++ @Component  
+?           ++
+- struct MyComponent {
++ struct MyComponent {  
+?                     ++
+-     @State children: Number[] = Array.from(Array&lt;number&gt;(900), (v, k) =&gt; k);
+? --
++   @State children: Number[] = Array.from(Array&lt;number&gt;(900), (v, k) =&gt; k);  
+?                                                                           ++
+-     build() {
+? --
++   build() {  
+?            ++
+-       Scroll() {
+? --
++     Scroll() {  
+?               ++
+-       Grid() {
++       Grid() {  
+?               ++
+-         ForEach(this.children, (item: Number[]) =&gt; {
++         ForEach(this.children, (item: Number[]) =&gt; {  
+?                                                     ++
+-           GridItem() {
++           GridItem() {  
+?                       ++
+-             // 冗余Stack
+-             Stack() {  
+-               Stack() {  
+-                 Stack() {  
+-                   Text(item.toString())  
+? ------
++             Text(item.toString())  
+-                 }.size({ width: "100%"})  
+-               }.backgroundColor(Color.Yellow)  
+? ----
++           }.backgroundColor(Color.Yellow)  
+-             }.backgroundColor(Color.Pink)  
+-           }  
+          }, (item: string) =&gt; item)  
+        }  
+        .columnsTemplate('1fr 1fr 1fr 1fr')  
+        .columnsGap(0)  
+        .rowsGap(0)  
+        .size({ width: "100%", height: "100%" })  
+      }  
+    }  
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -18679,6 +25237,45 @@
 综上所述，修复代码样例通过设置 GridItem 的缓存数量来优化性能，提高了代码的效率。</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ProductGrid {
+    private products: number[] = [];
+    aboutToAppear() {
+      for (let i = 1; i &lt;= 1000; i++) {
+        this.products.push(i);
+      }
+    }
+    build() {
+      Column() {
+        Grid() {
+          LazyForEach(this.products, (product: number) =&gt; {
+            GridItem() {
+              // 自定义组件，显示产品信息
+              Text('产品编号：' + product)
+                .fontSize(16)
+                .width('100%')
+                .height(80)
+                .textAlign(TextAlign.Center)
+            }
+          }, (product: number) =&gt; product.toString())
+        }
+-       // 未设置 Grid 的缓存数量
+?          -
++       // 设置 GridItem 的缓存数量
+?                 ++++
++       .cachedCount(3)
+        .columnsTemplate('1fr 1fr 1fr')
+        .columnsGap(5)
+        .rowsGap(5)
+        .height(600)
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -18771,6 +25368,42 @@
 1. **增加了缓存数量设置**：
    - 修复代码样例中加入了 `.cachedCount(4)` 这一行，这表示在使用 `LazyForEach` 渲染图片时，设置了缓存的数量为 4。这个设置可以提高性能，减少重新渲染的频率。
 其他部分的代码结构和逻辑没有变化。总体来看，这个修改旨在提升性能，特别是在处理大量图像时通过合理的缓存配置来提高用户体验。</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 文件：ImageGallery.ets
+  @Entry
+  @Component
+  struct ImageGallery {
+    private imageList: string[] = [];
+    aboutToAppear() {
+      for (let i = 1; i &lt;= 500; i++) {
+        this.imageList.push('image_' + i + '.png');
+      }
+    }
+    build() {
+      Column() {
+        Grid() {
+          LazyForEach(this.imageList, (image: string) =&gt; {
+            GridItem() {
+              Image($r('app.media.' + image))
+                .width(100)
+                .height(100)
+            }
+          }, (image: string) =&gt; image)
+        }
+-       // 未设置缓存数量
+?          -
++       // 设置缓存数量
++       .cachedCount(4)
+        .columnsTemplate('1fr 1fr 1fr 1fr')
+        .columnsGap(5)
+        .rowsGap(5)
+        .height('100%')
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -18870,6 +25503,43 @@
 这项修改的目的是提高性能，通过设定缓存数量来优化列表的渲染和内存使用，使得在滚动或更新列表时，能够更高效地处理可见项。</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 文件：ArticleGrid.ets
+  @Entry
+  @Component
+  struct ArticleGrid {
+    private articles: { id: number; title: string }[] = [];
+    aboutToAppear() {
+      for (let i = 1; i &lt;= 800; i++) {
+        this.articles.push({ id: i, title: '文章标题 ' + i });
+      }
+    }
+    build() {
+      Column() {
+        Grid() {
+          LazyForEach(this.articles, (article) =&gt; {
+            GridItem() {
+              Text(article.title)
+                .fontSize(14)
+                .width('100%')
+                .height(60)
+            }
+          }, (article) =&gt; article.id.toString())
+        }
+-       // 未设置缓存数量
+?          -
++       // 设置缓存数量
++       .cachedCount(2)
+        .columnsTemplate('1fr 1fr')
+        .columnsGap(10)
+        .rowsGap(10)
+        .height(500)
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -18967,6 +25637,43 @@
 综上所述，修复代码样例通过增加缓存数量的设置，优化了性能，而其他部分的代码结构和逻辑保持不变。</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 文件：VideoGrid.ets
+  @Entry
+  @Component
+  struct VideoGrid {
+    private videos: string[] = [];
+    aboutToAppear() {
+      for (let i = 1; i &lt;= 600; i++) {
+        this.videos.push('video_' + i);
+      }
+    }
+    build() {
+      Column() {
+        Grid() {
+          LazyForEach(this.videos, (video: string) =&gt; {
+            GridItem() {
+              // 显示视频缩略图
+              Image($r('app.media.' + video + '_thumb'))
+                .width(150)
+                .height(100)
+            }
+          }, (video: string) =&gt; video)
+        }
+-       // 未设置缓存数量
+?          -
++       // 设置缓存数量
++       .cachedCount(3)
+        .columnsTemplate('1fr 1fr 1fr')
+        .columnsGap(8)
+        .rowsGap(8)
+        .height(600)
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -19069,6 +25776,45 @@
 其他部分的代码在结构和逻辑上没有变化。因此，主要的改动在于设置了缓存数量，以提高组件的渲染效率和性能。</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 源码文件，请以工程实际为准
+  import { MyDataSource } from './MyDataSource';
+  @Entry
+  @Component
+  struct MyComponent {
+    // 数据源
+    private data: MyDataSource = new MyDataSource();
+    aboutToAppear() {
+      for (let i = 1; i &lt; 1000; i++) {
+        this.data.pushData(i);
+      }
+    }
+    build() {
+      Column({ space: 5 }) {
+        Grid() {
+          LazyForEach(this.data, (item: number) =&gt; {
+            GridItem() {
+              // 使用可复用自定义组件
+              // 业务逻辑
+            }
+          }, (item: string) =&gt; item)
+        }
+-       // 未设置GridItem的缓存数量
+?          -
++       // 设置GridItem的缓存数量
++       .cachedCount(2)
+        .columnsTemplate('1fr 1fr 1fr')
+        .columnsGap(10)
+        .rowsGap(10)
+        .margin(10)
+        .height(500)
+        .backgroundColor(0xFAEEE0)
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -19220,6 +25966,91 @@
 总结来说，修复代码通过引入 `AVPlayerManager` 和修改播放器的管理方式，大幅度提升了资源的利用效率，避免了不必要的实例创建与释放，提高了应用的性能与响应速度。</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import media from '@ohos.multimedia.media';
+  @Entry
+  @Component
+  struct VideoPlayerComponent {
+    private avPlayer: media.AVPlayer | undefined = undefined;
++   private avPlayerManager: AVPlayerManager = AVPlayerManager.getInstance();
+    aboutToAppear(): void {
+-     // 页面创建时初始化 AVPlayer 实例
+-     media.createAVPlayer().then((player) =&gt; {
+-       this.avPlayer = player;
++     // 使用缓存的 AVPlayer 实例
++     this.avPlayerManager.switchPlayer();
++     this.avPlayer = this.avPlayerManager.getCurrentPlayer();
+-       this.avPlayer?.setDisplaySurface(this.$element('videoSurface'));
+? --
++     this.avPlayer?.setDisplaySurface(this.$element('videoSurface'));
+-       this.avPlayer?.prepare('media/video1.mp4');
+? --
++     this.avPlayer?.prepare('media/video1.mp4');
+-     });
+    }
+    aboutToDisappear(): void {
++     // 重置 AVPlayer 实例而非销毁
++     this.avPlayerManager.resetCurrentPlayer();
+-     // 离开页面时销毁 AVPlayer 实例
+-     if (this.avPlayer) {
+-       this.avPlayer.release();
+-     }
+      this.avPlayer = undefined;
+    }
+    build() {
+      Column() {
+        // 视频显示区域
+        VideoSurface()
+          .id('videoSurface')
+          .width('100%')
+          .height(200)
+        Button('播放视频')
+          .onClick(() =&gt; {
+            this.avPlayer?.play();
+          })
+      }
+    }
+  }
++ class AVPlayerManager {
++   private static instance?: AVPlayerManager;
++   private player1?: media.AVPlayer;
++   private player2?: media.AVPlayer;
++   private currentPlayer?: media.AVPlayer;
++   private constructor() {
++     // 初始化 AVPlayer 实例
++     media.createAVPlayer().then((player) =&gt; {
++       this.player1 = player;
++     });
++     media.createAVPlayer().then((player) =&gt; {
++       this.player2 = player;
++     });
++   }
++   public static getInstance(): AVPlayerManager {
++     if (!AVPlayerManager.instance) {
++       AVPlayerManager.instance = new AVPlayerManager();
++     }
++     return AVPlayerManager.instance;
++   }
++   /**
++    * 切换当前使用的 AVPlayer 实例
++    */
++   switchPlayer(): void {
++     this.currentPlayer = this.currentPlayer === this.player1 ? this.player2 : this.player1;
++   }
++   getCurrentPlayer(): media.AVPlayer | undefined {
++     return this.currentPlayer;
++   }
++   /**
++    * 重置当前的 AVPlayer 实例
++    */
++   resetCurrentPlayer(): void {
++     this.currentPlayer?.pause();
++     this.currentPlayer?.reset();
++   }
++ }</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -19341,6 +26172,73 @@
 综上所述，修复代码在多个方面优化了播放器实例的管理，提高了代码的组织结构、效率和可读性。</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import media from '@ohos.multimedia.media';
+  @Entry
+  @Component
+  struct MyComponent{
+    private avPlayer: media.AVPlayer | undefined = undefined;
++   private avPlayerManager: AVPlayerManager = AVPlayerManager.getInstance();
+    aboutToAppear(): void {
++     this.avPlayerManager.switchPlayer();
++     this.avPlayer = this.avPlayerManager.getCurrentPlayer();
+-     // 页面创建时初始化AVPlayer实例
+-     media.createAVPlayer().then((ret) =&gt; {
+-       this.avPlayer = ret;
+-     });
+    }
+    aboutToDisappear(): void {
++     this.avPlayerManager.resetCurrentPlayer();
+-     // 离开页面时销毁AVPlayer实例
+-     if (this.avPlayer) {
+-       this.avPlayer.release();
+-     }
+      this.avPlayer = undefined;
+    }
+    build() {
+      // 组件布局
+    }
+  }
++ class AVPlayerManager {
++   private static instance?: AVPlayerManager;
++   private player1?: media.AVPlayer;
++   private player2?: media.AVPlayer;
++   private currentPlayer?: media.AVPlayer;
++   public static getInstance(): AVPlayerManager {
++     if (!AVPlayerManager.instance) {
++       AVPlayerManager.instance = new AVPlayerManager();
++     }
++     return AVPlayerManager.instance;
++   }
++   async AVPlayerManager() {
++     this.player1 = await media.createAVPlayer();
++     this.player2 = await media.createAVPlayer();
++   }
++   /**
++    * 切换页面时切换AVPlayer实例
++    */
++   switchPlayer(): void {
++     if (this.currentPlayer === this.player1) {
++       this.currentPlayer = this.player2;
++     } else {
++       this.currentPlayer = this.player1;
++     }
++   }
++   getCurrentPlayer(): media.AVPlayer | undefined {
++     return this.currentPlayer;
++   }
++   /**
++    * 使用reset方法重置AVPlayer实例
++    */
++   resetCurrentPlayer(): void {
++     this.currentPlayer?.pause(() =&gt; {
++       this.currentPlayer?.reset();
++     });
++   }
++ }</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -19444,6 +26342,55 @@
 3. **引入了AVPlayerManager类**：
    - 修复代码样例中引入了 `AVPlayerManager` 类，但具体的实现细节没有在代码中展示（通过注释提到“AVPlayerManager 类同上例，不再重复”）。这表明在修复的过程中引入了一个新的管理层，增强了对播放器实例的控制。
 总的来说，修复代码样例通过引入 `AVPlayerManager` 简化并优化了 `AVPlayer` 的管理，改进了资源的管理方式。</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  import media from '@ohos.multimedia.media';
+  @Entry
+  @Component
+  struct AudioPlayerComponent {
+    private avPlayer: media.AVPlayer | undefined = undefined;
++   private avPlayerManager: AVPlayerManager = AVPlayerManager.getInstance();
+    aboutToAppear(): void {
+-     // 初始化 AVPlayer 实例
+?        ^^^
++     // 使用缓存的 AVPlayer 实例
+?        ^^^^^
+-     media.createAVPlayer().then((player) =&gt; {
+-       this.avPlayer = player;
++     this.avPlayerManager.switchPlayer();
++     this.avPlayer = this.avPlayerManager.getCurrentPlayer();
+-       this.avPlayer?.prepare('media/audio1.mp3');
+? --
++     this.avPlayer?.prepare('media/audio1.mp3');
+-     });
+    }
+    aboutToDisappear(): void {
+-     // 销毁 AVPlayer 实例
+?        ^^
++     // 重置 AVPlayer 实例
+?        ^^
++     this.avPlayerManager.resetCurrentPlayer();
+-     if (this.avPlayer) {
+-       this.avPlayer.release();
+-     }
+      this.avPlayer = undefined;
+    }
+    build() {
+      Column() {
+        Button('播放音频')
+          .onClick(() =&gt; {
+            this.avPlayer?.play();
+          })
+        Button('暂停音频')
+          .onClick(() =&gt; {
+            this.avPlayer?.pause();
+          })
+      }
+    }
+  }
++ // AVPlayerManager 类同上例，不再重复</t>
         </is>
       </c>
     </row>
@@ -19580,6 +26527,78 @@
    - **修复代码样例**：结构上将聊天信息的展示逻辑抽象到一个单独的可复用组件 `InnerRecentChat` 中，从而使 `MyComponent` 更加简洁，职责更清晰。
    - **问题代码样例**：所有逻辑都集中在一个组件内，导致代码可读性较差，设计上也不够灵活。
 总结来说，修复代码样例通过引入可复用组件和状态管理机制，提高了代码的复用性、可读性和可维护性。</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 源码文件，请以工程实际为准
+  import { MyDataSource } from './MyDataSource';
+  import { ChartInfoEntry } from './data/DataEntry';
+  import { PublicChatItem } from './component/PublicChatItem';
+  import { ChatItem } from './component/ChatItem';
+  @Entry
+  @Component
+  struct MyComponent{
+    private scroller: Scroller = new Scroller()
+    private lazyChatList: MyDataSource = new MyDataSource();
+    build() {
+      Column() {
+        List({ scroller: this.scroller }) {
+          LazyForEach(this.lazyChatList, (item: ChartInfoEntry, index: number) =&gt; {
+            ListItem() {
++             // 使用reuseId进行组件复用的控制
++             InnerRecentChat({ chatInfo: item }).reuseId(this.lazyChatList.getReuseIdByIndex(index))
+-             // ListItem里有if-else并且直接在分支里使用了自定义复用组件
+-             Button({ type: ButtonType.Normal }) {
+-               Row() {
+-                 if (item['isPublicChat']) {
+-                   // 源码文件，请以工程实际为准
+-                   PublicChatItem({ chatInfo: item as PublicChatItem })
+-                 } else {
+-                   // 源码文件，请以工程实际为准
+-                   ChatItem({ chatInfo: item as ChatItem })
+-                 }
+-               }.padding({ left: 16, right: 16 })
+-             }
+-             .type(ButtonType.Normal)
+-             .width('100%')
+-             .height('100%')
+-             .borderRadius(0)
+            }
+            .height(72)
+          }, (item: ChartInfoEntry) =&gt; item.id)
+        }
+        .cachedCount(3)
+        .width('100%')
+        .height('100%')
+      }
+    }
+  }
++ @Reusable
++ @Component
++ struct InnerRecentChat {
++   @State chatInfo: ChartInfoEntry = new ChartInfoEntry()
++   aboutToReuse(params: Record&lt;string, ESObject&gt;): void {
++     this.chatInfo = params.chatInfo as ChartInfoEntry
++   }
++   build() {
++     Button({ type: ButtonType.Normal }) {
++       Row() {
++         if (this.chatInfo['isPublicChat']) {
++           // 源码文件，请以工程实际为准
++           PublicChatItem({ chatInfo: chatInfo as ChartInfoEntry })
++         } else {
++           // 源码文件，请以工程实际为准
++           ChatItem({ chatInfo: this.chatInfo as ChatItem })
++         }
++       }.padding({ left: 16, right: 16 })
++     }
++     .type(ButtonType.Normal)
++     .width('100%')
++     .height('100%')
++     .borderRadius(0)
++   }
++ }</t>
         </is>
       </c>
     </row>
@@ -19712,6 +26731,80 @@
 6. **一致性提高**：
    - 修复代码中所有产品项都使用了相同的 `GridItem` 构造，使得布局更为一致。
 这些更改使得代码在布局方面更加灵活且一致，能够处理不规则数据并减少了条件逻辑的复杂性。</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ProductGrid {
+    private products: string[] = [];
++   private irregularData: number[] = [];
++   private layoutOptions: GridLayoutOptions = {
++     regularSize: [1, 1],
++     irregularIndexes: this.irregularData,
++     getItemSize: (index: number) =&gt; {
++       if (this.irregularData.includes(index)) {
++         return [2, 1];
++       }
++       return [1, 1];
++     }
++   };
+    aboutToAppear() {
+      for (let i = 1; i &lt;= 1000; i++) {
+        this.products.push('Product ' + i);
++       if ((i - 1) % 5 === 0) {
++         this.irregularData.push(i - 1);
++       }
+      }
+    }
+    build() {
+      Column() {
+-       Grid() {
++       Grid(undefined, this.layoutOptions) {
+-         LazyForEach(this.products, (item: string, index: number) =&gt; {
+?                                                 ---------------
++         LazyForEach(this.products, (item: string) =&gt; {
+-           if (index % 5 === 0) {
+-             GridItem() {
+? --
++           GridItem() {
+-               Text(item)
+? --
++             Text(item)
+-                 .fontSize(16)
+? --
++               .fontSize(16)
+-                 .width('100%')
+? --
++               .width('100%')
+-                 .height(120)
+-                 .backgroundColor(Color.LightGray)
+-             }
+-             .columnStart(0)
+-             .columnEnd(3)
+-           } else {
+-             GridItem() {
+-               Text(item)
+-                 .fontSize(16)
+-                 .width('100%')
+-                 .height(80)
+? --
++               .height(80)
+-                 .backgroundColor(Color.White)
+? --
++               .backgroundColor(Color.White)
+-             }
+            }
+          }, (item: string) =&gt; item)
+        }
+        .columnsTemplate('1fr 1fr 1fr')
+        .columnsGap(10)
+        .rowsGap(10)
+        .height('80%')
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -19910,6 +27003,84 @@
 综上所述，修复代码样例相对于问题代码样例作了多项改动，主要体现在组件声明、数据处理、布局选项的引入以及简化了数据渲染逻辑等方面，以增强可读性和功能性。</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  // 源码文件，请以工程实际为准
+  import { MyDataSource } from './MyDataSource';
+  @Reusable
+  @Component
+  struct TextItem {
+    @State item: string = "";
+    build() {
+      Text(this.item)
+        .fontSize(16)
+        .backgroundColor(0xF9CF93)
+        .width('100%')
+        .height(80)
+        .textAlign(TextAlign.Center)
+        .onClick(() =&gt; {
+          this.item = 'click';
+        })
+    }
+  }
+  @Entry
+  @Component
+- struct MyComponent{
++ export struct MyComponent{
+? +++++++
+    private datasource: MyDataSource = new MyDataSource();
+    scroller: Scroller = new Scroller();
++   private irregularData: number[] = [];
++   layoutOptions: GridLayoutOptions = {
++     regularSize: [1, 1],
++     irregularIndexes: this.irregularData,
++   };
+    aboutToAppear() {
+      for (let i = 1; i &lt;= 2000; i++) {
+        this.datasource.pushData(i + '');
++       if ((i - 1) % 4 === 0) {
++         this.irregularData.push(i - 1);
++       }
+      }
+    }
+    build() {
+      Column({ space: 5 }) {
+-       Text('Use columnStart and columnEnd to set the GridItem size').fontColor(0xCCCCCC).fontSize(9).width('90%')
+-       Grid(this.scroller) {
++       Text('Set GridItem size using GridLayoutOptions').fontColor(0xCCCCCC).fontSize(9).width('90%')
++       Grid(this.scroller, this.layoutOptions) {
+          LazyForEach(this.datasource, (item: string, index: number) =&gt; {
+-           if ((index % 4) === 0) {
+-             GridItem() {
+? --
++           GridItem() {
+-               TextItem({ item: item })
+? --
++             TextItem({ item: item })
+-             }
+-             .columnStart(0).columnEnd(2)
+-           } else {
+-             GridItem() {
+-               TextItem({ item: item })
+-             }
+            }
+          }, (item: string) =&gt; item)
+        }
+        .cachedCount(1)
+        .columnsTemplate('1fr 1fr 1fr')
+        .columnsGap(10)
+        .rowsGap(10)
+        .width('90%')
+        .height('40%')
+        Button("scrollToIndex:1900").onClick(() =&gt; {
+          this.scroller.scrollToIndex(1900);
+        })
+      }.width('100%')
+      .margin({ top: 5 })
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -20034,6 +27205,72 @@
 总结来说，修复代码样例在处理网格布局上做了优化，使得布局更灵活且具有可扩展性，通过引入不规则数据和动态尺寸管理简化了代码结构。</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct PhotoGallery {
+    private photos: string[] = [];
++   private irregularData: number[] = [];
++   private layoutOptions: GridLayoutOptions = {
++     regularSize: [1, 1],
++     irregularIndexes: this.irregularData,
++     getItemSize: (index: number) =&gt; {
++       if (this.irregularData.includes(index)) {
++         return [3, 1];
++       }
++       return [1, 1];
++     }
++   };
+    aboutToAppear() {
+      for (let i = 1; i &lt;= 500; i++) {
+        this.photos.push('Photo ' + i);
++       if ((i) % 7 === 0) {
++         this.irregularData.push(i - 1);
++       }
+      }
+    }
+    build() {
+      Column() {
+-       Grid() {
++       Grid(undefined, this.layoutOptions) {
+-         LazyForEach(this.photos, (photo: string, index: number) =&gt; {
+?                                                ---------------
++         LazyForEach(this.photos, (photo: string) =&gt; {
+-           if ((index + 1) % 7 === 0) {
+-             GridItem() {
+? --
++           GridItem() {
+-               Image($r('app.media.' + photo))
+? --
++             Image($r('app.media.' + photo))
+-                 .width('100%')
+? --
++               .width('100%')
+-                 .height(200)
+-             }
+-             .columnStart(0)
+-             .columnEnd(4)
+-           } else {
+-             GridItem() {
+-               Image($r('app.media.' + photo))
+-                 .width('100%')
+-                 .height(100)
+? --
++               .height(100)
+-             }
+            }
+          }, (photo: string) =&gt; photo)
+        }
+        .columnsTemplate('1fr 1fr 1fr')
+        .columnsGap(5)
+        .rowsGap(5)
+        .height('100%')
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -20113,6 +27350,31 @@
 - **状态管理**：修复代码的处理方式在某些状态管理框架中可能更受推荐，有助于更好地追踪状态的变化。</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct MyComponent {
+    @State message: string = '';
+    appendMsg(newMsg: String) {
++       let message = this.message;
+-       this.message += newMsg;
+?       -----
++       message += newMsg;
+-       this.message += ";";
+?       -----
++       message += ";";
+-       this.message += "&lt;br/&gt;";
+?       -----
++       message += "&lt;br/&gt;";
++       this.message = message;
+    }
+    build() {
+      // 业务代码...
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -20188,6 +27450,35 @@
    - **问题代码样例**：可能会导致理解上的混淆，特别是对于状态如何更新的理解。
    - **修复代码样例**：通过使用局部变量，逻辑变得更加清晰，避免了潜在的累加错误，使得每次调用 `increment()` 时都能准确增加 3。
 总结来说，修复代码样例通过使用局部变量来正确计算新的计数值，从而避免了在问题代码样例中直接修改状态造成的潜在错误。这种方式也使得状态更新的逻辑更加清晰和易于理解。</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct CounterComponent {
+    @State count: number = 0;
+    increment() {
++     let newCount = this.count;
++     newCount += 1;
++     newCount += 1;
++     newCount += 1;
+-     this.count += 1;
+?                -  ^
++     this.count = newCount;
+?                  ^^^^^^^^
+-     this.count += 1;
+-     this.count += 1;
+    }
+    build() {
+      Column() {
+        Text('计数值：' + this.count)
+          .fontSize(20)
+        Button('增加计数')
+          .onClick(() =&gt; this.increment())
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -20285,6 +27576,42 @@
 2. **计算逻辑保持一致性：**
    - 两个样例的 `calculateTax` 和 `calculateShipping` 方法没有变化，但修复代码样例通过先计算总价到局部变量 `total`，再赋值给状态，避免了直接在原状态上做运算可能引起的问题。
 这些调整确保了组件在状态变化时能够正常更新，并且能够正确显示最新的总价。</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ShoppingCart {
+    @State totalPrice: number = 0;
+    addItem(price: number) {
++     let total = this.totalPrice;
+-     this.totalPrice += price;
+?      -----    -----
++     total += price;
+-     this.totalPrice += this.calculateTax(price);
+?      -----    -----
++     total += this.calculateTax(price);
+-     this.totalPrice += this.calculateShipping(price);
+?      -----    -----
++     total += this.calculateShipping(price);
++     this.totalPrice = total;
+    }
+    calculateTax(price: number): number {
+      return price * 0.1;
+    }
+    calculateShipping(price: number): number {
+      return 5;
+    }
+    build() {
+      Column() {
+        Text('总价：' + this.totalPrice)
+          .fontSize(18)
+        Button('添加商品')
+          .onClick(() =&gt; this.addItem(100))
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -20372,6 +27699,38 @@
 2. **提高代码可读性和维护性**：
    - 将所有字符串的处理放在 `tempResult` 中，使得每一步操作都更容易理解，并且调试时避免了对 `this.result` 状态的频繁更改，这在一定程度上提高了代码的可读性和维护性。
 总结来说，修复代码样例通过引入临时变量和减少直接对状态的修改，提高了代码的清晰度和可维护性。</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct StringManipulator {
+    @State result: string = '';
+    manipulateString(input: string) {
+-     this.result = input.trim();
+?      ^^^^^
++     let tempResult = input.trim();
+?     ++ ^^^^^^
+-     this.result = this.result.toUpperCase();
+?      ^^^^^         ^^^^^
++     tempResult = tempResult.toUpperCase();
+?      ^^^^         ^^^^
++     tempResult = tempResult + '!';
+-     this.result = this.result + '!';
+?                    ^^^^^     ------
++     this.result = tempResult;
+?                    ^^^^
+    }
+    build() {
+      Column() {
+        Text('结果：' + this.result)
+          .fontSize(16)
+        Button('处理字符串')
+          .onClick(() =&gt; this.manipulateString(' hello world '))
+      }
+    }
+  }</t>
         </is>
       </c>
     </row>
@@ -20467,6 +27826,40 @@
 综上，修复代码样例通过使用临时数组和赋值操作来更安全地更新状态，确保了视图的一致性与更新。</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct ListManager {
+    @State items: string[] = [];
+    addItems(newItems: string[]) {
++     let tempItems = [...this.items];
+-     this.items.push(newItems[0]);
+?      ^^^^^
++     tempItems.push(newItems[0]);
+?      ^^^^
+-     this.items.push(newItems[1]);
+?      ^^^^^
++     tempItems.push(newItems[1]);
+?      ^^^^
+-     this.items.push(newItems[2]);
+?      ^^^^^
++     tempItems.push(newItems[2]);
+?      ^^^^
++     this.items = tempItems;
+    }
+    build() {
+      Column() {
+        ForEach(this.items, (item) =&gt; {
+          Text(item)
+        })
+        Button('添加项目')
+          .onClick(() =&gt; this.addItems(['Item A', 'Item B', 'Item C']))
+      }
+    }
+  }</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -20564,6 +27957,46 @@
 4. **对性能影响的讨论**：
    - 在修复代码样例中的注释中，明确指出了 `@ObjectLink` 对于不需要本地修改的子组件来说是更优的选择，因为它避免了深拷贝的性能开销。这使得开发者在优化代码时能够做出更明智的决定。
 综上所述，修复代码样例的主要差异是通过使用 `@ObjectLink` 来优化性能，并且提供了更明确的上下文和注释，以帮助理解这一变化的原因和影响。</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Observed
+  class ClassA {
+    public c: number = 0;
+    constructor(c: number) {
+      this.c = c;
+    }
+  }
+  @Component
+  struct PropChild {
+-   // @Prop 装饰状态变量会深拷贝
+-   @Prop testNum: ClassA;
++   // @ObjectLink 装饰状态变量不会深拷贝
++   // 当修饰为ObjectLink时 ClassA必须同时被Observed修饰
++   @ObjectLink testNum: ClassA;
+    build() {
+      Text(`PropChild testNum ${this.testNum.c}`)
+    }
+  }
+  @Entry
+  @Component
+  struct Parent {
+    @State testNum: ClassA[] = [new ClassA(1)];
+    build() {
+      Column() {
+        Text(`Parent testNum ${this.testNum[0].c}`)
+          .onClick(() =&gt; {
+            this.testNum[0].c += 1;
+          })
+-       // PropChild没有改变@Prop testNum: ClassA的值，所以这时最优的选择是使用@ObjectLink
++       // 当子组件不需要发生本地改变时，优先使用@ObjectLink，因为@Prop是会深拷贝数据，具有拷贝的性能开销，所以这个时候@ObjectLink是比@Link和@Prop更优的选择
+        PropChild({ testNum: this.testNum[0] })
+      }
+-   }
++   }}
+?    +
+- }</t>
         </is>
       </c>
     </row>
@@ -20616,6 +28049,22 @@
    - 修复代码样例中对参数 `array` 进行了类型注解 (`Array&lt;number&gt;`)，这表明该参数应该是一个数字数组。
    - 问题代码样例没有进行任何类型注解，无法保证传入参数的类型。
 这些变化使得修复后的代码在函数的设计上更加清晰、可维护，并且提高了代码的灵活性和安全性。</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  let arr = [0, 1, 2];
+- function foo() {
++ function foo(array: Array&lt;number&gt;): number {
+    // arr 尽量通过参数传递
+-   return arr[0] + arr[1];
++   return array[0] + array[1];
+?             ++         ++
+  }
+- foo();
++ foo(arr);
+?     +++
+</t>
         </is>
       </c>
     </row>
@@ -20698,6 +28147,34 @@
 综上所述，修复代码样例的主要修改是替换了顶层的 `Flex` 组件为 `Column`，并调整了注释以反映这一更改。这使得结构更加清晰和符合语义。</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  @Entry
+  @Component
+  struct MyComponent {
+    build() {
+-     // Flex Nesting
+-     Flex({ direction: FlexDirection.Column }) {
++     // Replace Flex with Column/Row
++     Column() {
+        Text('Replace Flex with Column/Row')
+          .fontSize(12)
+          .height('16')
+          .margin({
+            top: 5,
+            bottom: 10
+          })
+        Flex().width(300).height(200).backgroundColor(Color.Pink)
+        Flex().width(300).height(200).backgroundColor(Color.Yellow)
+        Flex().width(300).height(200).backgroundColor(Color.Grey)
+        Flex().width(300).height(200).backgroundColor(Color.Pink)
+        Flex().width(300).height(200).backgroundColor(Color.Yellow)
+        Flex().width(300).height(200).backgroundColor(Color.Grey)
+      }.height(200)
+    }
+  }</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
